--- a/outputs/EMS upgrade output.xlsx
+++ b/outputs/EMS upgrade output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,32 +481,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure          </t>
+          <t xml:space="preserve">Bearing Failure         </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support and enable smooth rotation of rotor shaft front end </t>
+          <t xml:space="preserve">Support rotating shaft, reduce friction and wear               </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration                </t>
+          <t xml:space="preserve">VIB - Vibration          </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">2.4 Wear                      </t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Increased vibration due to bearing surface wear       </t>
+          <t xml:space="preserve">Increased vibration indicating bearing wear                  </t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing vibration monitoring [Y/N]; Scheduled bearing lubrication [Y/N]; Timely bearing replacement [Y/N]          </t>
+          <t xml:space="preserve">Bearing vibration monitoring [Y/N]; Regular lubricant checks [Y/N]; Scheduled bearing replacement [Y/N]              </t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive             </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -533,17 +533,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure          </t>
+          <t xml:space="preserve">Bearing Failure         </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support and enable smooth rotation of rotor shaft front end </t>
+          <t xml:space="preserve">Support rotating shaft, reduce friction and wear               </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration                </t>
+          <t xml:space="preserve">VIB - Vibration          </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -553,12 +553,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Misalignment causing vibration                     </t>
+          <t xml:space="preserve">Vibration due to misalignment or clearance issues           </t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alignment and clearance inspection [Y/N]; Corrective alignment actions [Y/N]; Shaft and bearing inspection [Y/N]    </t>
+          <t xml:space="preserve">Shaft alignment verification [Y/N]; Bearing clearance inspection [Y/N]; Bearing seating inspection [Y/N]             </t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive             </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -585,32 +585,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure          </t>
+          <t xml:space="preserve">Bearing Failure         </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support and enable smooth rotation of rotor shaft front end </t>
+          <t xml:space="preserve">Support rotating shaft, reduce friction and wear               </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration                </t>
+          <t xml:space="preserve">VIB - Vibration          </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                 </t>
+          <t xml:space="preserve">2.6 Fatigue                  </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing fatigue causing vibration                     </t>
+          <t xml:space="preserve">Fatigue causing vibration due to cyclic loading              </t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibration trend analysis [Y/N]; Bearing fatigue crack inspection [Y/N]; Scheduled bearing replacement [Y/N]         </t>
+          <t xml:space="preserve">Fatigue life monitoring [Y/N]; Vibration analysis [Y/N]; Bearing load monitoring [Y/N]                              </t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive             </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -637,32 +637,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure          </t>
+          <t xml:space="preserve">Bearing Failure         </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support and enable smooth rotation of rotor shaft front end </t>
+          <t xml:space="preserve">Support rotating shaft, reduce friction and wear               </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration                </t>
+          <t xml:space="preserve">NOI - Noise              </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness               </t>
+          <t xml:space="preserve">2.4 Wear                      </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Looseness causing vibration                           </t>
+          <t xml:space="preserve">Noise caused by bearing surface degradation                   </t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspection and tightening of bearing caps [Y/N]; Lubrication maintenance [Y/N]; Adjustment or replacement [Y/N]     </t>
+          <t xml:space="preserve">Acoustic emission monitoring [Y/N]; Bearing replacement planning [Y/N]; Lubrication check [Y/N]                      </t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive             </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -689,32 +689,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure          </t>
+          <t xml:space="preserve">Bearing Failure         </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support and enable smooth rotation of rotor shaft front end </t>
+          <t xml:space="preserve">Support rotating shaft, reduce friction and wear               </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                   </t>
+          <t xml:space="preserve">NOI - Noise              </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">1.5 Looseness                </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing wear causing noise                            </t>
+          <t xml:space="preserve">Noise due to loose bearing components                         </t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acoustic noise monitoring [Y/N]; Visual inspection [Y/N]; Scheduled lubrication and replacement [Y/N]              </t>
+          <t xml:space="preserve">Tightening inspection [Y/N]; Fastener torque check [Y/N]; Visual fatigue cracks inspection [Y/N]                    </t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive             </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -741,32 +741,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure          </t>
+          <t xml:space="preserve">Bearing Failure         </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support and enable smooth rotation of rotor shaft front end </t>
+          <t xml:space="preserve">Support rotating shaft, reduce friction and wear               </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                   </t>
+          <t xml:space="preserve">NOI - Noise              </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness               </t>
+          <t xml:space="preserve">2.6 Fatigue                  </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Looseness causing noise                               </t>
+          <t xml:space="preserve">Noise due to fatigue cracks                                   </t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tightening bearing housing [Y/N]; Lubrication inspection [Y/N]; Replacement of loose components [Y/N]               </t>
+          <t xml:space="preserve">Noise and vibration analyses [Y/N]; Fatigue crack inspection [Y/N]; Vibration trend monitoring [Y/N]                </t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding         </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -793,32 +793,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure          </t>
+          <t xml:space="preserve">Bearing Failure         </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support and enable smooth rotation of rotor shaft front end </t>
+          <t xml:space="preserve">Support rotating shaft, reduce friction and wear               </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                   </t>
+          <t xml:space="preserve">FWR - Failure while running </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                 </t>
+          <t xml:space="preserve">2.4 Wear                   </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue cracks causing noise                          </t>
+          <t xml:space="preserve">Wear leading to bearing failure during operation             </t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acoustic emission monitoring [Y/N]; Visual inspection for cracks [Y/N]; Bearing replacement [Y/N]                  </t>
+          <t xml:space="preserve">Routine condition monitoring [Y/N]; Lubrication optimization [Y/N]; Bearing wear debris inspection [Y/N]            </t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding         </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure          </t>
+          <t xml:space="preserve">Bearing Failure         </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support and enable smooth rotation of rotor shaft front end </t>
+          <t xml:space="preserve">Support rotating shaft, reduce friction and wear               </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating             </t>
+          <t xml:space="preserve">FWR - Failure while running </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation            </t>
+          <t xml:space="preserve">1.6 Sticking                </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overheating due to deformation increasing friction   </t>
+          <t xml:space="preserve">Seizure caused by lubrication failure or contamination     </t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Temperature monitoring [Y/N]; Visual deformation inspection [Y/N]; Cooling performance inspection [Y/N]             </t>
+          <t xml:space="preserve">Lubricant contamination check [Y/N]; Cleaning and relubrication [Y/N]; Contamination control [Y/N]                  </t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive             </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -897,32 +897,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure          </t>
+          <t xml:space="preserve">Bearing Failure         </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support and enable smooth rotation of rotor shaft front end </t>
+          <t xml:space="preserve">Support rotating shaft, reduce friction and wear               </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating             </t>
+          <t xml:space="preserve">FWR - Failure while running </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion               </t>
+          <t xml:space="preserve">2.6 Fatigue                 </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion causing overheating                         </t>
+          <t xml:space="preserve">Fatigue fracture during operation                             </t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion inspections [Y/N]; Anti-corrosion treatments [Y/N]; Bearing replacement [Y/N]                             </t>
+          <t xml:space="preserve">Fatigue monitoring and analysis [Y/N]; Load condition evaluation [Y/N]; Scheduled bearing replacement [Y/N]        </t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive             </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -949,32 +949,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure          </t>
+          <t xml:space="preserve">Bearing Failure         </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support and enable smooth rotation of rotor shaft front end </t>
+          <t xml:space="preserve">Support rotating shaft, reduce friction and wear               </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation      </t>
+          <t xml:space="preserve">OHE - Elevated temperature </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">2.4 Wear                    </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parameter deviation from bearing wear                 </t>
+          <t xml:space="preserve">Wear causing friction and localized heating                </t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibration and temperature trending [Y/N]; Lubrication condition monitoring [Y/N]; Adjustment or replacement [Y/N]   </t>
+          <t xml:space="preserve">Temperature monitoring [Y/N]; Lubrication oil temperature check [Y/N]; Cooling system inspection [Y/N]               </t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive             </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -1001,32 +1001,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure          </t>
+          <t xml:space="preserve">Bearing Failure         </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support and enable smooth rotation of rotor shaft front end </t>
+          <t xml:space="preserve">Support rotating shaft, reduce friction and wear               </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation      </t>
+          <t xml:space="preserve">OHE - Elevated temperature </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness               </t>
+          <t xml:space="preserve">1.4 Deformation            </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assembly looseness causing parameter deviations       </t>
+          <t xml:space="preserve">Deformation causing friction and heat                       </t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspection and tightening [Y/N]; Lubrication maintenance [Y/N]; Assembly adjustment [Y/N]                         </t>
+          <t xml:space="preserve">Visual inspection for deformation [Y/N]; Dimensional checks [Y/N]; Lubrication system verification [Y/N]            </t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive             </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure          </t>
+          <t xml:space="preserve">Bearing Failure         </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support and enable smooth rotation of rotor shaft front end </t>
+          <t xml:space="preserve">Support rotating shaft, reduce friction and wear               </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation      </t>
+          <t xml:space="preserve">OHE - Elevated temperature </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parameter deviation from fatigue cracks               </t>
+          <t xml:space="preserve">Fatigue cracks causing heat buildup                         </t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibration, temperature monitoring [Y/N]; NDE bearing inspection [Y/N]; Replacement planning [Y/N]                  </t>
+          <t xml:space="preserve">Thermal monitoring [Y/N]; Vibration and temperature trend analysis [Y/N]; Bearing replacement scheduling [Y/N]     </t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive             </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -1105,32 +1105,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure          </t>
+          <t xml:space="preserve">DE Bearing Failure      </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support and enable smooth rotation of rotor shaft front end </t>
+          <t xml:space="preserve">Support axial and radial loads; reduce friction                </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running    </t>
+          <t xml:space="preserve">VIB - Vibration          </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">2.4 Wear                    </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing wear causing failure during operation         </t>
+          <t xml:space="preserve">Vibration from bearing wear                                 </t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Condition-based maintenance [Y/N]; Timely replacement [Y/N]; Lubricant filtration management [Y/N]                </t>
+          <t xml:space="preserve">Vibration monitoring [Y/N]; Visual wear inspection [Y/N]; Bearing replacement scheduling [Y/N]                     </t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive             </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -1157,32 +1157,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure          </t>
+          <t xml:space="preserve">DE Bearing Failure      </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support and enable smooth rotation of rotor shaft front end </t>
+          <t xml:space="preserve">Support axial and radial loads; reduce friction                </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running    </t>
+          <t xml:space="preserve">VIB - Vibration          </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness               </t>
+          <t xml:space="preserve">1.3 Clearance / alignment failure </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assembly looseness causing failure                     </t>
+          <t xml:space="preserve">Misalignment causing vibration                              </t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanical inspections [Y/N]; Lubrication system checks [Y/N]; Replacement or tightening [Y/N]                    </t>
+          <t xml:space="preserve">Shaft and coupling alignment checks [Y/N]; Bearing clearance inspection [Y/N]; Vibration analysis [Y/N]            </t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive             </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -1209,32 +1209,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure         </t>
+          <t xml:space="preserve">DE Bearing Failure      </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support and enable smooth rotation of rotor shaft rear end   </t>
+          <t xml:space="preserve">Support axial and radial loads; reduce friction                </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration                </t>
+          <t xml:space="preserve">VIB - Vibration          </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">2.6 Fatigue                 </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rear bearing wear causing vibration                    </t>
+          <t xml:space="preserve">Fatigue resulting in vibration                             </t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibration monitoring [Y/N]; Scheduled lubrication [Y/N]; Bearing replacement [Y/N]                               </t>
+          <t xml:space="preserve">Fatigue monitoring [Y/N]; Load analysis [Y/N]; Scheduled bearing replacement [Y/N]                                </t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive             </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -1261,32 +1261,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure         </t>
+          <t xml:space="preserve">DE Bearing Failure      </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support and enable smooth rotation of rotor shaft rear end   </t>
+          <t xml:space="preserve">Support axial and radial loads; reduce friction                </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration                </t>
+          <t xml:space="preserve">NOI - Noise              </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.3 Clearance / alignment failure </t>
+          <t xml:space="preserve">2.4 Wear                    </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing misalignment causing vibration                </t>
+          <t xml:space="preserve">Noise from bearing surface degradation                     </t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alignment verification [Y/N]; Bearing clearance measurement [Y/N]; Corrective action [Y/N]                       </t>
+          <t xml:space="preserve">Acoustic emission monitoring [Y/N]; Noise analysis [Y/N]; Bearing replacement planning [Y/N]                      </t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive             </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -1313,32 +1313,32 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure         </t>
+          <t xml:space="preserve">DE Bearing Failure      </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support and enable smooth rotation of rotor shaft rear end   </t>
+          <t xml:space="preserve">Support axial and radial loads; reduce friction                </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration                </t>
+          <t xml:space="preserve">NOI - Noise              </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                 </t>
+          <t xml:space="preserve">1.5 Looseness              </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue cracks or spalling causing vibration           </t>
+          <t xml:space="preserve">Noise due to loose bearing components                      </t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise and vibration monitoring [Y/N]; Visual bearing inspection [Y/N]; Replacement planning [Y/N]                </t>
+          <t xml:space="preserve">Fastener torque inspection [Y/N]; Bearing housing inspection [Y/N]; Assembly quality control [Y/N]                </t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive             </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -1365,32 +1365,32 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure         </t>
+          <t xml:space="preserve">DE Bearing Failure      </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support and enable smooth rotation of rotor shaft rear end   </t>
+          <t xml:space="preserve">Support axial and radial loads; reduce friction                </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                   </t>
+          <t xml:space="preserve">NOI - Noise              </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">2.6 Fatigue                 </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear causing abnormal noise                            </t>
+          <t xml:space="preserve">Noise from fatigue cracks                                  </t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acoustic noise monitoring [Y/N]; Lubrication and inspection [Y/N]; Bearing replacement [Y/N]                    </t>
+          <t xml:space="preserve">Noise analysis [Y/N]; Fatigue crack inspection [Y/N]; Bearing replacement planning [Y/N]                          </t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive             </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -1417,32 +1417,32 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure         </t>
+          <t xml:space="preserve">DE Bearing Failure      </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support and enable smooth rotation of rotor shaft rear end   </t>
+          <t xml:space="preserve">Support axial and radial loads; reduce friction                </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                   </t>
+          <t xml:space="preserve">FWR - Failure while running </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness               </t>
+          <t xml:space="preserve">2.4 Wear                   </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Looseness causing noise                                </t>
+          <t xml:space="preserve">Wear leading to bearing failure during operation           </t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspection and tightening [Y/N]; Noise assessment [Y/N]; Corrective maintenance [Y/N]                            </t>
+          <t xml:space="preserve">Bearing condition monitoring [Y/N]; Lubrication oil analysis [Y/N]; Wear debris analysis [Y/N]                    </t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding         </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -1469,32 +1469,32 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure         </t>
+          <t xml:space="preserve">DE Bearing Failure      </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support and enable smooth rotation of rotor shaft rear end   </t>
+          <t xml:space="preserve">Support axial and radial loads; reduce friction                </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                   </t>
+          <t xml:space="preserve">FWR - Failure while running </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                 </t>
+          <t xml:space="preserve">1.6 Sticking                </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue cracks causing noise                            </t>
+          <t xml:space="preserve">Bearing seizure due to lubrication failure                </t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acoustic emission testing [Y/N]; Visual crack inspection [Y/N]; Repair or replacement [Y/N]                      </t>
+          <t xml:space="preserve">Lubrication quality control [Y/N]; Bearing cleaning and relubrication [Y/N]; Contamination control [Y/N]          </t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding         </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -1521,32 +1521,32 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure         </t>
+          <t xml:space="preserve">DE Bearing Failure      </t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support and enable smooth rotation of rotor shaft rear end   </t>
+          <t xml:space="preserve">Support axial and radial loads; reduce friction                </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating             </t>
+          <t xml:space="preserve">FWR - Failure while running </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation            </t>
+          <t xml:space="preserve">2.6 Fatigue                 </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overheating due to deformation increasing friction     </t>
+          <t xml:space="preserve">Fatigue fracture during operation                          </t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Temperature monitoring [Y/N]; Visual inspection [Y/N]; Cooling performance review [Y/N]                          </t>
+          <t xml:space="preserve">Fatigue load monitoring [Y/N]; Vibration analysis [Y/N]; Scheduled bearing replacement [Y/N]                      </t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive             </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -1573,32 +1573,32 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure         </t>
+          <t xml:space="preserve">DE Bearing Failure      </t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support and enable smooth rotation of rotor shaft rear end   </t>
+          <t xml:space="preserve">Support axial and radial loads; reduce friction                </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating             </t>
+          <t xml:space="preserve">OHE - Elevated temperature </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion               </t>
+          <t xml:space="preserve">2.2 Corrosion              </t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion causing overheating                         </t>
+          <t xml:space="preserve">Corrosion leading to metal loss and temperature rise      </t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion inspection and anti-corrosion treatment [Y/N]; Replacement [Y/N]; Monitoring [Y/N]                     </t>
+          <t xml:space="preserve">Visual corrosion inspection [Y/N]; Cooling system monitoring [Y/N]; Seal integrity check [Y/N]                    </t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive             </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -1625,32 +1625,32 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure         </t>
+          <t xml:space="preserve">DE Bearing Failure      </t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support and enable smooth rotation of rotor shaft rear end   </t>
+          <t xml:space="preserve">Support axial and radial loads; reduce friction                </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation      </t>
+          <t xml:space="preserve">OHE - Elevated temperature </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">1.4 Deformation           </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parameter deviation due to wear                        </t>
+          <t xml:space="preserve">Deformation causing overheating                           </t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing parameter monitoring [Y/N]; Lubricant condition checks [Y/N]; Replacement planning [Y/N]               </t>
+          <t xml:space="preserve">Dimensional checks [Y/N]; Visual inspection [Y/N]; Cooling system maintenance [Y/N]                              </t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive             </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -1677,32 +1677,32 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure         </t>
+          <t xml:space="preserve">DE Bearing Failure      </t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support and enable smooth rotation of rotor shaft rear end   </t>
+          <t xml:space="preserve">Support axial and radial loads; reduce friction                </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation      </t>
+          <t xml:space="preserve">OHE - Elevated temperature </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness               </t>
+          <t xml:space="preserve">2.6 Fatigue                 </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parameter deviation caused by looseness                </t>
+          <t xml:space="preserve">Heat buildup due to fatigue cracks                        </t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduled maintenance checks [Y/N]; Inspections for loose components [Y/N]; Corrective actions [Y/N]            </t>
+          <t xml:space="preserve">Thermal monitoring [Y/N]; Lubrication inspection [Y/N]; Vibration analysis [Y/N]                                  </t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive             </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -1729,42 +1729,42 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure         </t>
+          <t xml:space="preserve">NDE Bearing Failure     </t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support and enable smooth rotation of rotor shaft rear end   </t>
+          <t xml:space="preserve">Support shaft radial position; reduce friction                 </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running    </t>
+          <t xml:space="preserve">VIB - Vibration          </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">2.4 Wear                    </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing wear causing failure during operation         </t>
+          <t xml:space="preserve">Vibration from bearing wear                               </t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velocity and temperature monitoring [Y/N]; Scheduled bearing replacement [Y/N]; Lubrication oil quality monitoring [Y/N] </t>
+          <t xml:space="preserve">Vibration monitoring [Y/N]; Lubrication inspection [Y/N]; Bearing replacement scheduling [Y/N]                   </t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD              </t>
+          <t xml:space="preserve">TBD                   </t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive             </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -1781,17 +1781,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure         </t>
+          <t xml:space="preserve">NDE Bearing Failure     </t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support and enable smooth rotation of rotor shaft rear end   </t>
+          <t xml:space="preserve">Support shaft radial position; reduce friction                 </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running    </t>
+          <t xml:space="preserve">VIB - Vibration          </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1801,22 +1801,22 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Looseness causing failure                              </t>
+          <t xml:space="preserve">Looseness generating vibration                           </t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Periodic bolt and assembly tightness checking [Y/N]; Visual inspection for looseness [Y/N]; Corrective bearing assembly repairs [Y/N] </t>
+          <t xml:space="preserve">Assembly inspection [Y/N]; Fastener torque checks [Y/N]; Bearing seating inspection [Y/N]                         </t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD              </t>
+          <t xml:space="preserve">TBD                   </t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding         </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -1833,32 +1833,32 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotor Failure              </t>
+          <t xml:space="preserve">NDE Bearing Failure     </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotate and transfer mechanical torque from stator to driven load </t>
+          <t xml:space="preserve">Support shaft radial position; reduce friction                 </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRO - Failure to rotate         </t>
+          <t xml:space="preserve">VIB - Vibration          </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking                </t>
+          <t xml:space="preserve">2.6 Fatigue                 </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotor seizure preventing rotation                      </t>
+          <t xml:space="preserve">Fatigue induction of vibration                           </t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lubrication system inspection [Y/N]; Thermal and vibration monitoring [Y/N]; Rotor cleaning and maintenance [Y/N] </t>
+          <t xml:space="preserve">Vibration trend analysis [Y/N]; Fatigue monitoring [Y/N]; Scheduled maintenance [Y/N]                            </t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive             </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -1885,32 +1885,32 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotor Failure              </t>
+          <t xml:space="preserve">NDE Bearing Failure     </t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotate and transfer mechanical torque from stator to driven load </t>
+          <t xml:space="preserve">Support shaft radial position; reduce friction                 </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRO - Failure to rotate         </t>
+          <t xml:space="preserve">NOI - Noise              </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness              </t>
+          <t xml:space="preserve">2.4 Wear                    </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotor parts loose causing rotation failure             </t>
+          <t xml:space="preserve">Noise from bearing surface wear                           </t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visual inspection of rotor mounting [Y/N]; Tightening bolts and checks [Y/N]; Scheduled maintenance [Y/N]         </t>
+          <t xml:space="preserve">Acoustic emission analysis [Y/N]; Bearing noise monitoring [Y/N]; Scheduled bearing replacement [Y/N]            </t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive             </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -1937,32 +1937,32 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotor Failure              </t>
+          <t xml:space="preserve">NDE Bearing Failure     </t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotate and transfer mechanical torque from stator to driven load </t>
+          <t xml:space="preserve">Support shaft radial position; reduce friction                 </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRO - Failure to rotate         </t>
+          <t xml:space="preserve">NOI - Noise              </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                </t>
+          <t xml:space="preserve">1.5 Looseness              </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue cracks causing seizure                         </t>
+          <t xml:space="preserve">Noise caused by looseness                                </t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE testing [Y/N]; Replacement on failure detection [Y/N]; Vibration monitoring [Y/N]                           </t>
+          <t xml:space="preserve">Fastener tightness check [Y/N]; Visual inspection [Y/N]; Assembly quality control [Y/N]                           </t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive             </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -1989,32 +1989,32 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotor Failure              </t>
+          <t xml:space="preserve">NDE Bearing Failure     </t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotate and transfer mechanical torque from stator to driven load </t>
+          <t xml:space="preserve">Support shaft radial position; reduce friction                 </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
+          <t xml:space="preserve">NOI - Noise              </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation            </t>
+          <t xml:space="preserve">2.6 Fatigue                 </t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deformation causing imbalance and vibration            </t>
+          <t xml:space="preserve">Noise from fatigue cracks                                </t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimensional inspection [Y/N]; Rotor repair or replacement [Y/N]; Alignment check [Y/N]                           </t>
+          <t xml:space="preserve">Noise and vibration analysis [Y/N]; Fatigue crack detection [Y/N]; Bearing replacement planning [Y/N]            </t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive             </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -2041,32 +2041,32 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotor Failure              </t>
+          <t xml:space="preserve">NDE Bearing Failure     </t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotate and transfer mechanical torque from stator to driven load </t>
+          <t xml:space="preserve">Support shaft radial position; reduce friction                 </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
+          <t xml:space="preserve">FWR - Failure while running </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage               </t>
+          <t xml:space="preserve">2.4 Wear                   </t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Broken rotor components causing vibration               </t>
+          <t xml:space="preserve">Wear causing failure during operation                    </t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visual inspection [Y/N]; Rotor repair or replacement [Y/N]; Vibration trending [Y/N]                            </t>
+          <t xml:space="preserve">Lubrication inspection [Y/N]; Bearing condition monitoring [Y/N]; Wear debris analysis [Y/N]                     </t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding         </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -2093,32 +2093,32 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotor Failure              </t>
+          <t xml:space="preserve">NDE Bearing Failure     </t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotate and transfer mechanical torque from stator to driven load </t>
+          <t xml:space="preserve">Support shaft radial position; reduce friction                 </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                  </t>
+          <t xml:space="preserve">FWR - Failure while running </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage               </t>
+          <t xml:space="preserve">1.6 Sticking                </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise due to rotor breakage                             </t>
+          <t xml:space="preserve">Seizure due to lubrication failure                      </t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise monitoring [Y/N]; Rotor visual inspections [Y/N]; Repair or replacement [Y/N]                             </t>
+          <t xml:space="preserve">Lubrication quality check [Y/N]; Cleaning and relubrication [Y/N]; Contamination control [Y/N]                   </t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding         </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -2145,32 +2145,32 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotor Failure              </t>
+          <t xml:space="preserve">NDE Bearing Failure     </t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotate and transfer mechanical torque from stator to driven load </t>
+          <t xml:space="preserve">Support shaft radial position; reduce friction                 </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation    </t>
+          <t xml:space="preserve">FWR - Failure while running </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion              </t>
+          <t xml:space="preserve">2.6 Fatigue                 </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion degrading rotor performance                   </t>
+          <t xml:space="preserve">Fatigue failure during operation                       </t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion inspection and treatment [Y/N]; Replacement of corroded parts [Y/N]; Maintenance [Y/N]               </t>
+          <t xml:space="preserve">Fatigue load monitoring [Y/N]; Vibration analysis [Y/N]; Scheduled bearing replacement [Y/N]                     </t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive             </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -2197,32 +2197,32 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotor Failure              </t>
+          <t xml:space="preserve">NDE Bearing Failure     </t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotate and transfer mechanical torque from stator to driven load </t>
+          <t xml:space="preserve">Support shaft radial position; reduce friction                 </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running  </t>
+          <t xml:space="preserve">OHE - Elevated temperature </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                </t>
+          <t xml:space="preserve">2.2 Corrosion              </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue damage causing failure during operation          </t>
+          <t xml:space="preserve">Corrosion causes temperature rise                       </t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotor condition monitoring [Y/N]; NDE examination [Y/N]; Replacement upon fatigue detection [Y/N]               </t>
+          <t xml:space="preserve">Visual corrosion inspections [Y/N]; Cooling system performance monitoring [Y/N]; Seal integrity checks [Y/N]      </t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive             </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -2249,32 +2249,32 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stator Failure             </t>
+          <t xml:space="preserve">NDE Bearing Failure     </t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate magnetic field and transfer electromagnetic energy </t>
+          <t xml:space="preserve">Support shaft radial position; reduce friction                 </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRO - Failure to rotate         </t>
+          <t xml:space="preserve">OHE - Elevated temperature </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.1 Short circuiting       </t>
+          <t xml:space="preserve">1.4 Deformation           </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Short circuit causing rotor not to rotate               </t>
+          <t xml:space="preserve">Deformation increasing localized heating               </t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Testing insulation resistance [Y/N]; Megger tests [Y/N]; Repair or rewind windings [Y/N]                       </t>
+          <t xml:space="preserve">Dimensional inspection [Y/N]; Visual assessment [Y/N]; Cooling system maintenance [Y/N]                          </t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive             </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -2301,32 +2301,32 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stator Failure             </t>
+          <t xml:space="preserve">NDE Bearing Failure     </t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate magnetic field and transfer electromagnetic energy </t>
+          <t xml:space="preserve">Support shaft radial position; reduce friction                 </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRO - Failure to rotate         </t>
+          <t xml:space="preserve">OHE - Elevated temperature </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness             </t>
+          <t xml:space="preserve">2.6 Fatigue                 </t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose laminations or core causing rotation failure      </t>
+          <t xml:space="preserve">Overheating due to fatigue cracks                      </t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tightening bolts [Y/N]; Visual inspection of laminations [Y/N]; Structural repair [Y/N]                         </t>
+          <t xml:space="preserve">Thermal monitoring [Y/N]; Lubrication state inspection [Y/N]; Vibration analysis [Y/N]                            </t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive             </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -2353,32 +2353,32 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stator Failure             </t>
+          <t xml:space="preserve">Brushes Failure         </t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate magnetic field and transfer electromagnetic energy </t>
+          <t xml:space="preserve">Provide electrical contact to rotor                           </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRO - Failure to rotate         </t>
+          <t xml:space="preserve">FRO - Failure to rotate   </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">4.2 Open circuit            </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear in stator components causing malfunction          </t>
+          <t xml:space="preserve">Loss of current flow causes failure to rotate            </t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visual inspection [Y/N]; Replacement of worn parts [Y/N]; Condition-based maintenance [Y/N]                     </t>
+          <t xml:space="preserve">Brush wear inspection [Y/N]; Electrical continuity test [Y/N]; Brush replacement scheduling [Y/N]                </t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive             </t>
+          <t xml:space="preserve">Failure-Finding        </t>
         </is>
       </c>
     </row>
@@ -2405,32 +2405,32 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stator Failure             </t>
+          <t xml:space="preserve">Brushes Failure         </t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate magnetic field and transfer electromagnetic energy </t>
+          <t xml:space="preserve">Provide electrical contact to rotor                           </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                  </t>
+          <t xml:space="preserve">FRO - Failure to rotate   </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness             </t>
+          <t xml:space="preserve">4.5 Earth/isolation fault    </t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise from loose stator parts                            </t>
+          <t xml:space="preserve">Ground fault causing rotor failure                      </t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acoustic noise monitoring [Y/N]; Visual inspection and tightening [Y/N]; Repair and replacement [Y/N]            </t>
+          <t xml:space="preserve">Ground fault detection [Y/N]; Insulation testing [Y/N]; Brush circuit repair [Y/N]                              </t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding         </t>
+          <t xml:space="preserve">Failure-Finding        </t>
         </is>
       </c>
     </row>
@@ -2457,32 +2457,32 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stator Failure             </t>
+          <t xml:space="preserve">Brushes Failure         </t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate magnetic field and transfer electromagnetic energy </t>
+          <t xml:space="preserve">Provide electrical contact to rotor                           </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                  </t>
+          <t xml:space="preserve">FRO - Failure to rotate   </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">1.5 Looseness              </t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise from stator wear                                   </t>
+          <t xml:space="preserve">Loose brush assembly causes loss of current flow        </t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise trending [Y/N]; Visual inspection and replacement [Y/N]; Lubrication [Y/N]                               </t>
+          <t xml:space="preserve">Brush holder inspection [Y/N]; Fastener tightening [Y/N]; Brush spring tension verification [Y/N]              </t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding         </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -2509,32 +2509,32 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stator Failure             </t>
+          <t xml:space="preserve">Brushes Failure         </t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate magnetic field and transfer electromagnetic energy </t>
+          <t xml:space="preserve">Provide electrical contact to rotor                           </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOO - No output              </t>
+          <t xml:space="preserve">NOI - Noise              </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.1 Short circuiting       </t>
+          <t xml:space="preserve">4.4 Faulty power/voltage     </t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">No output from electrical fault                          </t>
+          <t xml:space="preserve">Noise due to sparking/arcing                            </t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electrical continuity checks [Y/N]; Repair or rewind windings [Y/N]; Insulation maintenance [Y/N]              </t>
+          <t xml:space="preserve">Power supply voltage inspection [Y/N]; Brush surface examination [Y/N]; Electrical connection checks [Y/N]      </t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive             </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -2561,32 +2561,32 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stator Failure             </t>
+          <t xml:space="preserve">Brushes Failure         </t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate magnetic field and transfer electromagnetic energy </t>
+          <t xml:space="preserve">Provide electrical contact to rotor                           </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOO - No output              </t>
+          <t xml:space="preserve">NOI - Noise              </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 Open circuit          </t>
+          <t xml:space="preserve">1.5 Looseness              </t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open circuit causing output loss                         </t>
+          <t xml:space="preserve">Noise due to loose components                           </t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Continuity testing [Y/N]; Repair or replacement of wiring [Y/N]; Functional test [Y/N]                          </t>
+          <t xml:space="preserve">Mechanical inspection [Y/N]; Brush holder tightening [Y/N]; Vibration analysis [Y/N]                            </t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding         </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -2613,32 +2613,32 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stator Failure             </t>
+          <t xml:space="preserve">Brushes Failure         </t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate magnetic field and transfer electromagnetic energy </t>
+          <t xml:space="preserve">Provide electrical contact to rotor                           </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating            </t>
+          <t xml:space="preserve">NOI - Noise              </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation            </t>
+          <t xml:space="preserve">2.4 Wear                   </t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overheating due to deformation                           </t>
+          <t xml:space="preserve">Noise from brush wear                                   </t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thermal imaging [Y/N]; Structural repairs [Y/N]; Cooling system checks [Y/N]                                  </t>
+          <t xml:space="preserve">Brush wear monitoring [Y/N]; Replacement scheduling [Y/N]; Surface cleaning [Y/N]                              </t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive             </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -2665,32 +2665,32 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stator Failure             </t>
+          <t xml:space="preserve">Brushes Failure         </t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate magnetic field and transfer electromagnetic energy </t>
+          <t xml:space="preserve">Provide electrical contact to rotor                           </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating            </t>
+          <t xml:space="preserve">FTS - Failure to start    </t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion              </t>
+          <t xml:space="preserve">4.2 Open circuit            </t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion causing insulation breakdown                  </t>
+          <t xml:space="preserve">Open brush circuit prevents motor start                </t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion prevention and inspection [Y/N]; Replacement of corroded parts [Y/N]; Scheduled maintenance [Y/N]     </t>
+          <t xml:space="preserve">Continuity tests [Y/N]; Brush assembly inspection [Y/N]; Electrical circuit checks [Y/N]                        </t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive             </t>
+          <t xml:space="preserve">Failure-Finding        </t>
         </is>
       </c>
     </row>
@@ -2717,32 +2717,32 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stator Failure             </t>
+          <t xml:space="preserve">Brushes Failure         </t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate magnetic field and transfer electromagnetic energy </t>
+          <t xml:space="preserve">Provide electrical contact to rotor                           </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation    </t>
+          <t xml:space="preserve">FTS - Failure to start    </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">4.5 Earth/isolation fault    </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parameter deviation from wear                            </t>
+          <t xml:space="preserve">Ground fault prevents motor start                       </t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trending operational parameters [Y/N]; Scheduled inspection [Y/N]; Corrective maintenance [Y/N]                 </t>
+          <t xml:space="preserve">Ground fault tests [Y/N]; Insulation resistance measurement [Y/N]; Repair or replacement [Y/N]                 </t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive             </t>
+          <t xml:space="preserve">Failure-Finding        </t>
         </is>
       </c>
     </row>
@@ -2769,32 +2769,32 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stator Failure             </t>
+          <t xml:space="preserve">Brushes Failure         </t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate magnetic field and transfer electromagnetic energy </t>
+          <t xml:space="preserve">Provide electrical contact to rotor                           </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation    </t>
+          <t xml:space="preserve">FTS - Failure to start    </t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness             </t>
+          <t xml:space="preserve">1.5 Looseness              </t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parameter deviation due to looseness                     </t>
+          <t xml:space="preserve">Loose brush connections cause failure to start         </t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspection and tightening [Y/N]; Corrective repairs [Y/N]; Condition-based maintenance [Y/N]                    </t>
+          <t xml:space="preserve">Tightness checks [Y/N]; Brush assembly inspection [Y/N]; Brush spring tension measurement [Y/N]               </t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive             </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -2821,32 +2821,32 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stator Failure             </t>
+          <t xml:space="preserve">Brushes Failure         </t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate magnetic field and transfer electromagnetic energy </t>
+          <t xml:space="preserve">Provide electrical contact to rotor                           </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation    </t>
+          <t xml:space="preserve">FTS - Failure to start    </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 Faulty power/voltage   </t>
+          <t xml:space="preserve">3.5 Software error         </t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power supply variation affecting function               </t>
+          <t xml:space="preserve">Control software fault inhibits start                   </t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electrical quality monitoring [Y/N]; Power supply maintenance [Y/N]; Repair and replacement [Y/N]              </t>
+          <t xml:space="preserve">Control system diagnostics [Y/N]; Software update [Y/N]; Communication verification [Y/N]                      </t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding         </t>
+          <t xml:space="preserve">Failure-Finding        </t>
         </is>
       </c>
     </row>
@@ -2873,32 +2873,32 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stator Failure             </t>
+          <t xml:space="preserve">Coupling Failure        </t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate magnetic field and transfer electromagnetic energy </t>
+          <t xml:space="preserve">Transmit torque between motor and driven equipment        </t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
+          <t xml:space="preserve">VIB - Vibration           </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
+          <t xml:space="preserve">1.3 Clearance / alignment failure </t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stator assembly misalignment causing vibration       </t>
+          <t xml:space="preserve">Misalignment leading to coupling vibration              </t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alignment verification [Y/N]; Mechanical adjustment [Y/N]; Vibration trending [Y/N]                            </t>
+          <t xml:space="preserve">Alignment verification [Y/N]; Coupling inspection [Y/N]; Drive shaft balance check [Y/N]                      </t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive             </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -2925,32 +2925,32 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stator Failure             </t>
+          <t xml:space="preserve">Coupling Failure        </t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate magnetic field and transfer electromagnetic energy </t>
+          <t xml:space="preserve">Transmit torque between motor and driven equipment        </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
+          <t xml:space="preserve">VIB - Vibration           </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue               </t>
+          <t xml:space="preserve">2.6 Fatigue                </t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue cracks in stator laminations                      </t>
+          <t xml:space="preserve">Fatigue damage causing vibration                         </t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visual/NDE inspection of stator [Y/N]; Repair/replacement planning [Y/N]; Vibration monitoring [Y/N]            </t>
+          <t xml:space="preserve">Vibration monitoring [Y/N]; Fatigue crack inspection [Y/N]; Coupling replacement [Y/N]                        </t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive             </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -2977,32 +2977,32 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stator Failure             </t>
+          <t xml:space="preserve">Coupling Failure        </t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate magnetic field and transfer electromagnetic energy </t>
+          <t xml:space="preserve">Transmit torque between motor and driven equipment        </t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running  </t>
+          <t xml:space="preserve">NOI - Noise               </t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness             </t>
+          <t xml:space="preserve">5.3 External influences    </t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Looseness causing system failure                          </t>
+          <t xml:space="preserve">Noise due to mechanical impact or damage                </t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspection and tightening [Y/N]; Maintenance scheduling [Y/N]; Vibration monitoring [Y/N]                     </t>
+          <t xml:space="preserve">Noise monitoring [Y/N]; Visual inspection [Y/N]; Lubrication check [Y/N]                                     </t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding         </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -3029,32 +3029,32 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stator Failure             </t>
+          <t xml:space="preserve">Coupling Failure        </t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generate magnetic field and transfer electromagnetic energy </t>
+          <t xml:space="preserve">Transmit torque between motor and driven equipment        </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running  </t>
+          <t xml:space="preserve">NOI - Noise               </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                  </t>
+          <t xml:space="preserve">1.5 Looseness              </t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear causing failure during operation                     </t>
+          <t xml:space="preserve">Noise due to loose components                            </t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maintenance planning [Y/N]; Lubrication inspections [Y/N]; Replacement on wear detection [Y/N]                 </t>
+          <t xml:space="preserve">Fastener torque inspection [Y/N]; Coupling mounting inspection [Y/N]; Repair scheduling [Y/N]                </t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive             </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -3081,32 +3081,32 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Windings Failure           </t>
+          <t xml:space="preserve">Coupling Failure        </t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conduct electrical current for motor operation             </t>
+          <t xml:space="preserve">Transmit torque between motor and driven equipment        </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOO - No output              </t>
+          <t xml:space="preserve">FWR - Failure while running </t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.1 Short circuiting       </t>
+          <t xml:space="preserve">2.5 Breakage               </t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Short-circuited windings causing no output               </t>
+          <t xml:space="preserve">Mechanical breakage causing failure                     </t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electrical insulation tests [Y/N]; Winding repairs or rewinding [Y/N]; Preventive insulation maintenance [Y/N]  </t>
+          <t xml:space="preserve">Visual inspection [Y/N]; Torque load tests [Y/N]; Component replacement [Y/N]                                </t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive             </t>
+          <t xml:space="preserve">Failure-Finding        </t>
         </is>
       </c>
     </row>
@@ -3133,32 +3133,32 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Windings Failure           </t>
+          <t xml:space="preserve">Coupling Failure        </t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conduct electrical current for motor operation             </t>
+          <t xml:space="preserve">Transmit torque between motor and driven equipment        </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOO - No output              </t>
+          <t xml:space="preserve">FWR - Failure while running </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 Open circuit          </t>
+          <t xml:space="preserve">1.6 Sticking               </t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open-circuited windings causing no output               </t>
+          <t xml:space="preserve">Jamming leading to failure                              </t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Continuity tests [Y/N]; Repair or replacement of wiring [Y/N]; Functional tests [Y/N]                          </t>
+          <t xml:space="preserve">Lubrication inspection [Y/N]; Mechanical function test [Y/N]; Corrective maintenance [Y/N]                   </t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding         </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -3185,32 +3185,32 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Windings Failure           </t>
+          <t xml:space="preserve">Coupling Failure        </t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conduct electrical current for motor operation             </t>
+          <t xml:space="preserve">Transmit torque between motor and driven equipment        </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                 </t>
+          <t xml:space="preserve">ELU - External leakage - utility medium </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage              </t>
+          <t xml:space="preserve">2.4 Wear                  </t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Broken winding strands causing noise                      </t>
+          <t xml:space="preserve">Wear causing leakage                                     </t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise monitoring [Y/N]; Visual inspection and repair [Y/N]; Scheduled maintenance [Y/N]                       </t>
+          <t xml:space="preserve">Visual inspection [Y/N]; Seal replacement [Y/N]; Leak testing [Y/N]                                          </t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding         </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -3237,32 +3237,32 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Windings Failure           </t>
+          <t xml:space="preserve">Coupling Failure        </t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conduct electrical current for motor operation             </t>
+          <t xml:space="preserve">Transmit torque between motor and driven equipment        </t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                 </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 Faulty power/voltage   </t>
+          <t xml:space="preserve">5.3 Fouling                </t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power fluctuation-induced noise                            </t>
+          <t xml:space="preserve">Fouling causes performance degradation                   </t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power supply quality monitoring [Y/N]; Electrical connection checks [Y/N]; Signal conditioning device maintenance [Y/N] </t>
+          <t xml:space="preserve">Cleaning schedule [Y/N]; Fouling removal [Y/N]; Performance monitoring [Y/N]                                 </t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding         </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -3289,32 +3289,32 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Windings Failure           </t>
+          <t xml:space="preserve">Junction Box Failure    </t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conduct electrical current for motor operation             </t>
+          <t xml:space="preserve">Provide electrical connection and protection for motor wiring  </t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation   </t>
+          <t xml:space="preserve">ELU - External leakage - utility medium </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.7 Overheating           </t>
+          <t xml:space="preserve">2.4 Wear                  </t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overheating causing winding damage                        </t>
+          <t xml:space="preserve">Worn sealing causing external leaks                      </t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Temperature sensors monitoring [Y/N]; Cooling system inspection [Y/N]; Winding maintenance [Y/N]               </t>
+          <t xml:space="preserve">Visual inspection [Y/N]; Seal replacement [Y/N]; Leak testing [Y/N]                                          </t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive             </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -3341,32 +3341,32 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Windings Failure           </t>
+          <t xml:space="preserve">Junction Box Failure    </t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conduct electrical current for motor operation             </t>
+          <t xml:space="preserve">Provide electrical connection and protection for motor wiring  </t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation   </t>
+          <t xml:space="preserve">OHE - Elevated temperature </t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                  </t>
+          <t xml:space="preserve">4.4 Faulty power/voltage     </t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear causing performance degradation                      </t>
+          <t xml:space="preserve">Wiring overheating causing damage                        </t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trending winding temperature and vibration [Y/N]; Inspection on mechanical wear [Y/N]; Winding maintenance [Y/N] </t>
+          <t xml:space="preserve">Temperature sensor inspection [Y/N]; Wiring insulation checks [Y/N]; Cooling ventilation checks [Y/N]        </t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive             </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -3393,32 +3393,32 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Windings Failure           </t>
+          <t xml:space="preserve">Junction Box Failure    </t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conduct electrical current for motor operation             </t>
+          <t xml:space="preserve">Provide electrical connection and protection for motor wiring  </t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation   </t>
+          <t xml:space="preserve">VIB - Vibration          </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation           </t>
+          <t xml:space="preserve">1.6 Sticking                </t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanical deformation affecting windings                 </t>
+          <t xml:space="preserve">Mechanical damage causing vibration                      </t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visual inspection [Y/N]; Repair or replacement planning [Y/N]; Vibration and thermal imaging checks [Y/N]       </t>
+          <t xml:space="preserve">Vibration monitoring [Y/N]; Internal junction box inspection [Y/N]; Repair of mechanical components [Y/N]     </t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive             </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -3445,32 +3445,32 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Windings Failure           </t>
+          <t xml:space="preserve">Junction Box Failure    </t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conduct electrical current for motor operation             </t>
+          <t xml:space="preserve">Provide electrical connection and protection for motor wiring  </t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating           </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion             </t>
+          <t xml:space="preserve">5.3 External influences     </t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion causing winding insulation breakdown            </t>
+          <t xml:space="preserve">Performance parameter deviation                           </t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion protection and inspection [Y/N]; Replacement of corroded components [Y/N]; Protective coating application [Y/N] </t>
+          <t xml:space="preserve">Electrical parameter monitoring [Y/N]; Visual inspection [Y/N]; Repair [Y/N]                                 </t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive             </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -3497,32 +3497,32 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Windings Failure           </t>
+          <t xml:space="preserve">Junction Box Failure    </t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conduct electrical current for motor operation             </t>
+          <t xml:space="preserve">Provide electrical connection and protection for motor wiring  </t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating           </t>
+          <t xml:space="preserve">HTF - Heating failure    </t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation           </t>
+          <t xml:space="preserve">6.1 No cause found          </t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overheating due to physical winding distortion             </t>
+          <t xml:space="preserve">Heater failure causing loss of heating                    </t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thermal monitoring [Y/N]; Visual inspection [Y/N]; Structural repair or replacement planning [Y/N]              </t>
+          <t xml:space="preserve">Heater operation test [Y/N]; Electrical circuit inspection [Y/N]; Heater replacement [Y/N]                    </t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive             </t>
+          <t xml:space="preserve">Failure-Finding        </t>
         </is>
       </c>
     </row>
@@ -3549,32 +3549,32 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fittings and Fasteners Failure (*) </t>
+          <t xml:space="preserve">Heaters Failure         </t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide structural integrity and hold components in place   </t>
+          <t xml:space="preserve">Provide heating to prevent condensation                     </t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration             </t>
+          <t xml:space="preserve">HTF - Heating failure    </t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness             </t>
+          <t xml:space="preserve">6.1 No cause found          </t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose fittings causing vibration and structural issues   </t>
+          <t xml:space="preserve">Heater failure causing loss of heating                    </t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torque checks of fasteners [Y/N]; Visual inspection [Y/N]; Replacement of damaged fasteners [Y/N]               </t>
+          <t xml:space="preserve">Heater operation test [Y/N]; Electrical circuit inspection [Y/N]; Heater replacement [Y/N]                    </t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive             </t>
+          <t xml:space="preserve">Failure-Finding        </t>
         </is>
       </c>
     </row>
@@ -3601,32 +3601,32 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fittings and Fasteners Failure (*) </t>
+          <t xml:space="preserve">Heaters Failure         </t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide structural integrity and hold components in place   </t>
+          <t xml:space="preserve">Provide heating to prevent condensation                     </t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation          </t>
+          <t xml:space="preserve">2.4 Wear                    </t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deformed fasteners compromising structural integrity    </t>
+          <t xml:space="preserve">Heater degradation causing heating inefficiency           </t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visual and dimensional inspections [Y/N]; Replacement of bent or broken fasteners [Y/N]; Structural repairs [Y/N]  </t>
+          <t xml:space="preserve">Heater visual inspection [Y/N]; Performance monitoring [Y/N]; Preventive replacement [Y/N]                    </t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive             </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -3653,32 +3653,32 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fittings and Fasteners Failure (*) </t>
+          <t xml:space="preserve">Heaters Failure         </t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide structural integrity and hold components in place   </t>
+          <t xml:space="preserve">Provide heating to prevent condensation                     </t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                 </t>
+          <t xml:space="preserve">ELU - External leakage - utility medium </t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness             </t>
+          <t xml:space="preserve">2.2 Corrosion              </t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise generated from loose parts                          </t>
+          <t xml:space="preserve">Corroded heating components causing leaks               </t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise level monitoring [Y/N]; Inspection and tightening [Y/N]; Replacement of faulty fasteners [Y/N]             </t>
+          <t xml:space="preserve">Visual corrosion checks [Y/N]; Heater sealing integrity test [Y/N]; Repair scheduling [Y/N]                   </t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding         </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -3705,32 +3705,32 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fittings and Fasteners Failure (*) </t>
+          <t xml:space="preserve">Heaters Failure         </t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide structural integrity and hold components in place   </t>
+          <t xml:space="preserve">Provide heating to prevent condensation                     </t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation   </t>
+          <t xml:space="preserve">FTS - Failure to start    </t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue               </t>
+          <t xml:space="preserve">4.2 Open circuit            </t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue cracks in structural fittings                    </t>
+          <t xml:space="preserve">Heater circuit open causing heating loss                 </t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE inspection [Y/N]; Replacement of fatigued fasteners [Y/N]; Structural maintenance [Y/N]                     </t>
+          <t xml:space="preserve">Continuity testing [Y/N]; Switch and wiring inspections [Y/N]; Electrical repairs [Y/N]                        </t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3740,7 +3740,111 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive             </t>
+          <t xml:space="preserve">Failure-Finding        </t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heaters Failure         </t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide heating to prevent condensation                     </t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HTF - Heating failure    </t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.6 Fatigue                 </t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heater fatigue failure causes heating loss                </t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thermal imaging [Y/N]; Visual fatigue inspection [Y/N]; Replacement scheduling [Y/N]                          </t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive            </t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heaters Failure         </t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide heating to prevent condensation                     </t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOO - Low output         </t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.1 Leakage                 </t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heating element leakage reduces system output            </t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visual inspection [Y/N]; Leak detection [Y/N]; Component replacement [Y/N]                                  </t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>

--- a/outputs/EMS upgrade output.xlsx
+++ b/outputs/EMS upgrade output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,17 +481,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing Failure         </t>
+          <t xml:space="preserve">NDE Bearing Failure       </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotating shaft, reduce friction and wear               </t>
+          <t xml:space="preserve">Support rotor shaft at non-drive end and facilitate rotation  </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration          </t>
+          <t xml:space="preserve">VIB - Vibration               </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -501,12 +501,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Increased vibration indicating bearing wear                  </t>
+          <t xml:space="preserve">Increased vibration due to bearing surface wear                    </t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing vibration monitoring [Y/N]; Regular lubricant checks [Y/N]; Scheduled bearing replacement [Y/N]              </t>
+          <t xml:space="preserve">NDE bearings inspected for wear signs? [Y/N]; Lubrication level checked and maintained? [Y/N]; Vibration analysis performed? [Y/N] </t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -533,17 +533,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing Failure         </t>
+          <t xml:space="preserve">NDE Bearing Failure       </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotating shaft, reduce friction and wear               </t>
+          <t xml:space="preserve">Support rotor shaft at non-drive end and facilitate rotation  </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration          </t>
+          <t xml:space="preserve">VIB - Vibration               </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -553,12 +553,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibration due to misalignment or clearance issues           </t>
+          <t xml:space="preserve">Abnormal vibration due to misaligned bearing                       </t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft alignment verification [Y/N]; Bearing clearance inspection [Y/N]; Bearing seating inspection [Y/N]             </t>
+          <t xml:space="preserve">Alignment measurements and corrections done? [Y/N]; Shaft alignment verified? [Y/N]; Corrective alignment actions performed? [Y/N] </t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -585,32 +585,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing Failure         </t>
+          <t xml:space="preserve">NDE Bearing Failure       </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotating shaft, reduce friction and wear               </t>
+          <t xml:space="preserve">Support rotor shaft at non-drive end and facilitate rotation  </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration          </t>
+          <t xml:space="preserve">VIB - Vibration               </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                  </t>
+          <t xml:space="preserve">2.6 Fatigue                   </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue causing vibration due to cyclic loading              </t>
+          <t xml:space="preserve">Fatigue damage in bearing material causing vibration               </t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue life monitoring [Y/N]; Vibration analysis [Y/N]; Bearing load monitoring [Y/N]                              </t>
+          <t xml:space="preserve">Bearing integrity inspection conducted? [Y/N]; Load and vibration history reviewed? [Y/N]; Bearings replaced as scheduled? [Y/N] </t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -637,32 +637,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing Failure         </t>
+          <t xml:space="preserve">NDE Bearing Failure       </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotating shaft, reduce friction and wear               </t>
+          <t xml:space="preserve">Support rotor shaft at non-drive end and facilitate rotation  </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise              </t>
+          <t xml:space="preserve">VIB - Vibration               </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                      </t>
+          <t xml:space="preserve">1.5 Looseness                </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise caused by bearing surface degradation                   </t>
+          <t xml:space="preserve">Bearing looseness causing abnormal vibration                       </t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acoustic emission monitoring [Y/N]; Bearing replacement planning [Y/N]; Lubrication check [Y/N]                      </t>
+          <t xml:space="preserve">Bolts and fittings checked for tightness? [Y/N]; Vibration monitored? [Y/N]; Maintenance of bearing housing tightness? [Y/N]       </t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -689,32 +689,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing Failure         </t>
+          <t xml:space="preserve">NDE Bearing Failure       </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotating shaft, reduce friction and wear               </t>
+          <t xml:space="preserve">Support rotor shaft at non-drive end and facilitate rotation  </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise              </t>
+          <t xml:space="preserve">NOI - Noise                   </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness                </t>
+          <t xml:space="preserve">2.4 Wear                      </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise due to loose bearing components                         </t>
+          <t xml:space="preserve">Noise caused by surface degradation or roughness                   </t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tightening inspection [Y/N]; Fastener torque check [Y/N]; Visual fatigue cracks inspection [Y/N]                    </t>
+          <t xml:space="preserve">Bearing noise monitoring performed? [Y/N]; Lubrication condition checked? [Y/N]; Noise source analysis conducted? [Y/N]            </t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive            </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -741,32 +741,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing Failure         </t>
+          <t xml:space="preserve">NDE Bearing Failure       </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotating shaft, reduce friction and wear               </t>
+          <t xml:space="preserve">Support rotor shaft at non-drive end and facilitate rotation  </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise              </t>
+          <t xml:space="preserve">NOI - Noise                   </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                  </t>
+          <t xml:space="preserve">1.5 Looseness                </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise due to fatigue cracks                                   </t>
+          <t xml:space="preserve">Looseness causing increased noise                                  </t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise and vibration analyses [Y/N]; Fatigue crack inspection [Y/N]; Vibration trend monitoring [Y/N]                </t>
+          <t xml:space="preserve">Bolts and fittings checked for tightness? [Y/N]; Noise monitored and analyzed? [Y/N]; Vibration checks performed? [Y/N]            </t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -793,32 +793,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing Failure         </t>
+          <t xml:space="preserve">NDE Bearing Failure       </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotating shaft, reduce friction and wear               </t>
+          <t xml:space="preserve">Support rotor shaft at non-drive end and facilitate rotation  </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">NOI - Noise                   </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">2.6 Fatigue                  </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear leading to bearing failure during operation             </t>
+          <t xml:space="preserve">Fatigue cracks causing noise                                       </t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Routine condition monitoring [Y/N]; Lubrication optimization [Y/N]; Bearing wear debris inspection [Y/N]            </t>
+          <t xml:space="preserve">Fatigue damage evaluation? [Y/N]; Acoustic emission monitoring? [Y/N]; Bearings replaced if fatigued? [Y/N]                      </t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing Failure         </t>
+          <t xml:space="preserve">NDE Bearing Failure       </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotating shaft, reduce friction and wear               </t>
+          <t xml:space="preserve">Support rotor shaft at non-drive end and facilitate rotation  </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">OHE - Overheating             </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking                </t>
+          <t xml:space="preserve">1.4 Deformation             </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seizure caused by lubrication failure or contamination     </t>
+          <t xml:space="preserve">Bearing deformation causing heat build-up                         </t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lubricant contamination check [Y/N]; Cleaning and relubrication [Y/N]; Contamination control [Y/N]                  </t>
+          <t xml:space="preserve">Bearing temperature monitored? [Y/N]; Physical inspection of bearing deformation? [Y/N]; Corrective actions on deformation? [Y/N] </t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive            </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -897,17 +897,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing Failure         </t>
+          <t xml:space="preserve">NDE Bearing Failure       </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotating shaft, reduce friction and wear               </t>
+          <t xml:space="preserve">Support rotor shaft at non-drive end and facilitate rotation  </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">OHE - Overheating             </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -917,12 +917,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue fracture during operation                             </t>
+          <t xml:space="preserve">Breakdown of material due to cyclic thermal stress                </t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue monitoring and analysis [Y/N]; Load condition evaluation [Y/N]; Scheduled bearing replacement [Y/N]        </t>
+          <t xml:space="preserve">Thermal cycling assessment performed? [Y/N]; Thermal imaging inspections? [Y/N]; Bearing replaced when fatigued? [Y/N]           </t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -949,32 +949,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing Failure         </t>
+          <t xml:space="preserve">NDE Bearing Failure       </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotating shaft, reduce friction and wear               </t>
+          <t xml:space="preserve">Support rotor shaft at non-drive end and facilitate rotation  </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Elevated temperature </t>
+          <t xml:space="preserve">OHE - Overheating             </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                    </t>
+          <t xml:space="preserve">2.4 Wear                   </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear causing friction and localized heating                </t>
+          <t xml:space="preserve">Excessive friction causing overheating                            </t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Temperature monitoring [Y/N]; Lubrication oil temperature check [Y/N]; Cooling system inspection [Y/N]               </t>
+          <t xml:space="preserve">Lubrication levels checked? [Y/N]; Friction condition monitored? [Y/N]; Bearing lubricated and replaced per maintenance? [Y/N]    </t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1001,32 +1001,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing Failure         </t>
+          <t xml:space="preserve">NDE Bearing Failure       </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotating shaft, reduce friction and wear               </t>
+          <t xml:space="preserve">Support rotor shaft at non-drive end and facilitate rotation  </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Elevated temperature </t>
+          <t xml:space="preserve">LOO - Low output (*)           </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation            </t>
+          <t xml:space="preserve">5.2 Contamination           </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deformation causing friction and heat                       </t>
+          <t xml:space="preserve">Contamination degrades bearing lubrication                        </t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visual inspection for deformation [Y/N]; Dimensional checks [Y/N]; Lubrication system verification [Y/N]            </t>
+          <t xml:space="preserve">Lubricant contamination analysis? [Y/N]; Particulate filters checked? [Y/N]; Lubricant changed as per schedule? [Y/N]             </t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive            </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -1053,32 +1053,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing Failure         </t>
+          <t xml:space="preserve">NDE Bearing Failure       </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotating shaft, reduce friction and wear               </t>
+          <t xml:space="preserve">Support rotor shaft at non-drive end and facilitate rotation  </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Elevated temperature </t>
+          <t xml:space="preserve">LOO - Low output (*)           </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                 </t>
+          <t xml:space="preserve">2.2 Corrosion              </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue cracks causing heat buildup                         </t>
+          <t xml:space="preserve">Corrosion causes bearing surface degradation                      </t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thermal monitoring [Y/N]; Vibration and temperature trend analysis [Y/N]; Bearing replacement scheduling [Y/N]     </t>
+          <t xml:space="preserve">Corrosion inspection performed? [Y/N]; Protective coatings maintained? [Y/N]; Bearing replaced if corroded? [Y/N]                 </t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -1105,32 +1105,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure      </t>
+          <t xml:space="preserve">NDE Bearing Failure       </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support axial and radial loads; reduce friction                </t>
+          <t xml:space="preserve">Support rotor shaft at non-drive end and facilitate rotation  </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration          </t>
+          <t xml:space="preserve">FWR - Failure while running    </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                    </t>
+          <t xml:space="preserve">1.6 Sticking               </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibration from bearing wear                                 </t>
+          <t xml:space="preserve">Bearing seizure during operation                                  </t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibration monitoring [Y/N]; Visual wear inspection [Y/N]; Bearing replacement scheduling [Y/N]                     </t>
+          <t xml:space="preserve">Load and vibration monitored? [Y/N]; Seizure inspection after shutdown? [Y/N]; Lubricant and bearing replaced on schedule? [Y/N] </t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1157,32 +1157,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure      </t>
+          <t xml:space="preserve">NDE Bearing Failure       </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support axial and radial loads; reduce friction                </t>
+          <t xml:space="preserve">Support rotor shaft at non-drive end and facilitate rotation  </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration          </t>
+          <t xml:space="preserve">FWR - Failure while running    </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.3 Clearance / alignment failure </t>
+          <t xml:space="preserve">2.7 Thermal degradation    </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Misalignment causing vibration                              </t>
+          <t xml:space="preserve">Heat buildup causing bearing failure                             </t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft and coupling alignment checks [Y/N]; Bearing clearance inspection [Y/N]; Vibration analysis [Y/N]            </t>
+          <t xml:space="preserve">Temperature monitoring during operation? [Y/N]; Thermal protection system checked? [Y/N]; Bearing temperature maintained within limits? [Y/N] </t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive            </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -1209,32 +1209,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure      </t>
+          <t xml:space="preserve">DE Bearing Failure        </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support axial and radial loads; reduce friction                </t>
+          <t xml:space="preserve">Support rotor shaft at drive end and facilitate rotation      </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration          </t>
+          <t xml:space="preserve">VIB - Vibration               </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                 </t>
+          <t xml:space="preserve">2.4 Wear                   </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue resulting in vibration                             </t>
+          <t xml:space="preserve">Wear creating imbalance and vibration                           </t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue monitoring [Y/N]; Load analysis [Y/N]; Scheduled bearing replacement [Y/N]                                </t>
+          <t xml:space="preserve">DE bearing wear inspections? [Y/N]; Lubricant contamination checked? [Y/N]; Vibration spectrum analyzed? [Y/N]                  </t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1261,32 +1261,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure      </t>
+          <t xml:space="preserve">DE Bearing Failure        </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support axial and radial loads; reduce friction                </t>
+          <t xml:space="preserve">Support rotor shaft at drive end and facilitate rotation      </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise              </t>
+          <t xml:space="preserve">VIB - Vibration               </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                    </t>
+          <t xml:space="preserve">1.3 Clearance / alignment failure </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise from bearing surface degradation                     </t>
+          <t xml:space="preserve">Misalignment causing vibration                                 </t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acoustic emission monitoring [Y/N]; Noise analysis [Y/N]; Bearing replacement planning [Y/N]                      </t>
+          <t xml:space="preserve">Regular alignment checks? [Y/N]; Coupling and shaft alignment assessed? [Y/N]; Corrective realignment performed? [Y/N]          </t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -1313,32 +1313,32 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure      </t>
+          <t xml:space="preserve">DE Bearing Failure        </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support axial and radial loads; reduce friction                </t>
+          <t xml:space="preserve">Support rotor shaft at drive end and facilitate rotation      </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise              </t>
+          <t xml:space="preserve">VIB - Vibration               </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness              </t>
+          <t xml:space="preserve">2.6 Fatigue                </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise due to loose bearing components                      </t>
+          <t xml:space="preserve">Material fatigue in bearing causing vibration                   </t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fastener torque inspection [Y/N]; Bearing housing inspection [Y/N]; Assembly quality control [Y/N]                </t>
+          <t xml:space="preserve">Fatigue damage analysis conducted? [Y/N]; Bearing life cycles monitored? [Y/N]; Replace bearings based on damage? [Y/N]          </t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive            </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -1365,32 +1365,32 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure      </t>
+          <t xml:space="preserve">DE Bearing Failure        </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support axial and radial loads; reduce friction                </t>
+          <t xml:space="preserve">Support rotor shaft at drive end and facilitate rotation      </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise              </t>
+          <t xml:space="preserve">NOI - Noise                   </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                 </t>
+          <t xml:space="preserve">2.4 Wear                   </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise from fatigue cracks                                  </t>
+          <t xml:space="preserve">Noise generated due to wear                                     </t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise analysis [Y/N]; Fatigue crack inspection [Y/N]; Bearing replacement planning [Y/N]                          </t>
+          <t xml:space="preserve">Noise monitoring and analysis? [Y/N]; Lubricant condition checked? [Y/N]; Bearing noise diagnostics done? [Y/N]                 </t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1417,32 +1417,32 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure      </t>
+          <t xml:space="preserve">DE Bearing Failure        </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support axial and radial loads; reduce friction                </t>
+          <t xml:space="preserve">Support rotor shaft at drive end and facilitate rotation      </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">NOI - Noise                   </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">1.5 Looseness             </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear leading to bearing failure during operation           </t>
+          <t xml:space="preserve">Loose bearing components cause noise                          </t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing condition monitoring [Y/N]; Lubrication oil analysis [Y/N]; Wear debris analysis [Y/N]                    </t>
+          <t xml:space="preserve">Bearings bolts and caps inspected? [Y/N]; Noise trend analysis performed? [Y/N]; Tightening and repair conducted? [Y/N]          </t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -1469,42 +1469,42 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure      </t>
+          <t xml:space="preserve">DE Bearing Failure        </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support axial and radial loads; reduce friction                </t>
+          <t xml:space="preserve">Support rotor shaft at drive end and facilitate rotation      </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">OHE - Overheating             </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking                </t>
+          <t xml:space="preserve">1.4 Deformation           </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing seizure due to lubrication failure                </t>
+          <t xml:space="preserve">Structural deformation produces excessive heat               </t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lubrication quality control [Y/N]; Bearing cleaning and relubrication [Y/N]; Contamination control [Y/N]          </t>
+          <t>Visual inspection of bearing deformation? [Y/N]; Thermal sensor check? [Y/N]; Corrective action applied to reduce deformation? [Y/N]</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive            </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -1521,32 +1521,32 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure      </t>
+          <t xml:space="preserve">DE Bearing Failure        </t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support axial and radial loads; reduce friction                </t>
+          <t xml:space="preserve">Support rotor shaft at drive end and facilitate rotation      </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">OHE - Overheating             </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                 </t>
+          <t xml:space="preserve">2.6 Fatigue               </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue fracture during operation                          </t>
+          <t xml:space="preserve">Fatigue cracks causing heat build-up                          </t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue load monitoring [Y/N]; Vibration analysis [Y/N]; Scheduled bearing replacement [Y/N]                      </t>
+          <t xml:space="preserve">Fatigue life monitored? [Y/N]; Thermal imaging inspection? [Y/N]; Bearing replaced on fatigue detection? [Y/N]                   </t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1573,32 +1573,32 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure      </t>
+          <t xml:space="preserve">DE Bearing Failure        </t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support axial and radial loads; reduce friction                </t>
+          <t xml:space="preserve">Support rotor shaft at drive end and facilitate rotation      </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Elevated temperature </t>
+          <t xml:space="preserve">OHE - Overheating             </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion              </t>
+          <t xml:space="preserve">2.4 Wear                  </t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion leading to metal loss and temperature rise      </t>
+          <t xml:space="preserve">Excess friction causing overheating                           </t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visual corrosion inspection [Y/N]; Cooling system monitoring [Y/N]; Seal integrity check [Y/N]                    </t>
+          <t xml:space="preserve">Lubricant levels and condition checked? [Y/N]; Friction and temperature monitored? [Y/N]; Preventive lubrication applied? [Y/N] </t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive            </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -1625,32 +1625,32 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure      </t>
+          <t xml:space="preserve">DE Bearing Failure        </t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support axial and radial loads; reduce friction                </t>
+          <t xml:space="preserve">Support rotor shaft at drive end and facilitate rotation      </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Elevated temperature </t>
+          <t xml:space="preserve">LOO - Low output (*)           </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation           </t>
+          <t xml:space="preserve">5.2 Contamination         </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deformation causing overheating                           </t>
+          <t xml:space="preserve">Lubricant contamination causing performance loss             </t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimensional checks [Y/N]; Visual inspection [Y/N]; Cooling system maintenance [Y/N]                              </t>
+          <t xml:space="preserve">Lubricant checked for contamination? [Y/N]; Filters inspected? [Y/N]; Lubrication system maintained? [Y/N]                      </t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive            </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -1677,32 +1677,32 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure      </t>
+          <t xml:space="preserve">DE Bearing Failure        </t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support axial and radial loads; reduce friction                </t>
+          <t xml:space="preserve">Support rotor shaft at drive end and facilitate rotation      </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Elevated temperature </t>
+          <t xml:space="preserve">LOO - Low output (*)           </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                 </t>
+          <t xml:space="preserve">2.2 Corrosion             </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat buildup due to fatigue cracks                        </t>
+          <t xml:space="preserve">Corrosion on bearing surfaces causing failure                </t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thermal monitoring [Y/N]; Lubrication inspection [Y/N]; Vibration analysis [Y/N]                                  </t>
+          <t xml:space="preserve">Corrosion inspected? [Y/N]; Protective measures implemented? [Y/N]; Bearing replaced on corrosion detection? [Y/N]              </t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -1729,32 +1729,32 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure     </t>
+          <t xml:space="preserve">DE Bearing Failure        </t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support shaft radial position; reduce friction                 </t>
+          <t xml:space="preserve">Support rotor shaft at drive end and facilitate rotation      </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration          </t>
+          <t xml:space="preserve">FWR - Failure while running    </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                    </t>
+          <t xml:space="preserve">1.6 Sticking              </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibration from bearing wear                               </t>
+          <t xml:space="preserve">Bearing seizure causing failure during operation             </t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibration monitoring [Y/N]; Lubrication inspection [Y/N]; Bearing replacement scheduling [Y/N]                   </t>
+          <t xml:space="preserve">Operating conditions monitored? [Y/N]; Bearing lubed and cleaned? [Y/N]; Bearings replaced timely? [Y/N]                         </t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure     </t>
+          <t xml:space="preserve">DE Bearing Failure        </t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support shaft radial position; reduce friction                 </t>
+          <t xml:space="preserve">Support rotor shaft at drive end and facilitate rotation      </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration          </t>
+          <t xml:space="preserve">FWR - Failure while running    </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness              </t>
+          <t xml:space="preserve">2.7 Thermal degradation    </t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Looseness generating vibration                           </t>
+          <t xml:space="preserve">Overheating causing bearing failure                          </t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assembly inspection [Y/N]; Fastener torque checks [Y/N]; Bearing seating inspection [Y/N]                         </t>
+          <t xml:space="preserve">Temperature monitoring during operation? [Y/N]; Cooling system verified? [Y/N]; Thermo protection functional? [Y/N]             </t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive            </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -1833,32 +1833,32 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure     </t>
+          <t xml:space="preserve">Rotor Failure             </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support shaft radial position; reduce friction                 </t>
+          <t xml:space="preserve">Transmit torque from motor to driven equipment                 </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration          </t>
+          <t xml:space="preserve">VIB - Vibration              </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                 </t>
+          <t xml:space="preserve">1.3 Clearance / alignment failure </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue induction of vibration                           </t>
+          <t xml:space="preserve">Rotor imbalance or misalignment causing vibration          </t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibration trend analysis [Y/N]; Fatigue monitoring [Y/N]; Scheduled maintenance [Y/N]                            </t>
+          <t xml:space="preserve">Rotor balance inspected? [Y/N]; Alignment checked? [Y/N]; Corrective balancing and alignment performed? [Y/N]                  </t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -1885,32 +1885,32 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure     </t>
+          <t xml:space="preserve">Rotor Failure             </t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support shaft radial position; reduce friction                 </t>
+          <t xml:space="preserve">Transmit torque from motor to driven equipment                 </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise              </t>
+          <t xml:space="preserve">VIB - Vibration              </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                    </t>
+          <t xml:space="preserve">2.6 Fatigue               </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise from bearing surface wear                           </t>
+          <t xml:space="preserve">Rotor material fatigue causing vibration                     </t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acoustic emission analysis [Y/N]; Bearing noise monitoring [Y/N]; Scheduled bearing replacement [Y/N]            </t>
+          <t xml:space="preserve">Fatigue analysis performed? [Y/N]; Cycle counts reviewed? [Y/N]; Rotor replaced when required? [Y/N]                           </t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure     </t>
+          <t xml:space="preserve">Rotor Failure             </t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support shaft radial position; reduce friction                 </t>
+          <t xml:space="preserve">Transmit torque from motor to driven equipment                 </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise              </t>
+          <t xml:space="preserve">NOI - Noise                 </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness              </t>
+          <t xml:space="preserve">2.5 Breakage              </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise caused by looseness                                </t>
+          <t xml:space="preserve">Noise due to cracks or rotor breakage                        </t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fastener tightness check [Y/N]; Visual inspection [Y/N]; Assembly quality control [Y/N]                           </t>
+          <t xml:space="preserve">Acoustic monitoring performed? [Y/N]; Rotor inspected for cracks? [Y/N]; Rotor replaced after breakage detected? [Y/N]          </t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive            </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -1989,32 +1989,32 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure     </t>
+          <t xml:space="preserve">Rotor Failure             </t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support shaft radial position; reduce friction                 </t>
+          <t xml:space="preserve">Transmit torque from motor to driven equipment                 </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise              </t>
+          <t xml:space="preserve">NOI - Noise                 </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                 </t>
+          <t xml:space="preserve">1.5 Looseness             </t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise from fatigue cracks                                </t>
+          <t xml:space="preserve">Loose rotor components producing noise                      </t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise and vibration analysis [Y/N]; Fatigue crack detection [Y/N]; Bearing replacement planning [Y/N]            </t>
+          <t xml:space="preserve">Rotor component tightness checked? [Y/N]; Noise trend monitored? [Y/N]; Repairs performed promptly? [Y/N]                      </t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -2041,32 +2041,32 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure     </t>
+          <t xml:space="preserve">Rotor Failure             </t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support shaft radial position; reduce friction                 </t>
+          <t xml:space="preserve">Transmit torque from motor to driven equipment                 </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">OHE - Overheating           </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">1.4 Deformation           </t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear causing failure during operation                    </t>
+          <t xml:space="preserve">Thermal deformation causing overheating                     </t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lubrication inspection [Y/N]; Bearing condition monitoring [Y/N]; Wear debris analysis [Y/N]                     </t>
+          <t xml:space="preserve">Thermal imaging inspections? [Y/N]; Mechanical deformation assessed? [Y/N]; Cooling system maintained? [Y/N]                    </t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure     </t>
+          <t xml:space="preserve">Rotor Failure             </t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support shaft radial position; reduce friction                 </t>
+          <t xml:space="preserve">Transmit torque from motor to driven equipment                 </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">OHE - Overheating           </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking                </t>
+          <t xml:space="preserve">2.6 Fatigue               </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seizure due to lubrication failure                      </t>
+          <t xml:space="preserve">Fatigue cracking leading to overheating                      </t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lubrication quality check [Y/N]; Cleaning and relubrication [Y/N]; Contamination control [Y/N]                   </t>
+          <t xml:space="preserve">Thermal cycling assessment? [Y/N]; Rotor crack inspections? [Y/N]; Preventive replacement? [Y/N]                               </t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive            </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -2145,32 +2145,32 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure     </t>
+          <t xml:space="preserve">Rotor Failure             </t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support shaft radial position; reduce friction                 </t>
+          <t xml:space="preserve">Transmit torque from motor to driven equipment                 </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">PDE - Parameter deviation   </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                 </t>
+          <t xml:space="preserve">2.2 Corrosion             </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue failure during operation                       </t>
+          <t xml:space="preserve">Corrosion causing rotor degradation                         </t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue load monitoring [Y/N]; Vibration analysis [Y/N]; Scheduled bearing replacement [Y/N]                     </t>
+          <t>Visual and NDT corrosion inspection? [Y/N]; Protective coatings checked and maintained? [Y/N]; Rotor replaced if corroded? [Y/N]</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
@@ -2197,32 +2197,32 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure     </t>
+          <t xml:space="preserve">Rotor Failure             </t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support shaft radial position; reduce friction                 </t>
+          <t xml:space="preserve">Transmit torque from motor to driven equipment                 </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Elevated temperature </t>
+          <t xml:space="preserve">FWR - Failure while running  </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion              </t>
+          <t xml:space="preserve">1.6 Sticking              </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion causes temperature rise                       </t>
+          <t xml:space="preserve">Rotor seizure causing operational failure                   </t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visual corrosion inspections [Y/N]; Cooling system performance monitoring [Y/N]; Seal integrity checks [Y/N]      </t>
+          <t xml:space="preserve">Rotor operation monitored and recorded? [Y/N]; Operational parameters checked? [Y/N]; Maintenance actions followed? [Y/N]       </t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive            </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -2249,32 +2249,32 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure     </t>
+          <t xml:space="preserve">Stator Failure            </t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support shaft radial position; reduce friction                 </t>
+          <t xml:space="preserve">House stator windings and core; provides stator magnetic field </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Elevated temperature </t>
+          <t xml:space="preserve">NOO - No output             </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation           </t>
+          <t xml:space="preserve">4.1 Short circuiting      </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deformation increasing localized heating               </t>
+          <t xml:space="preserve">Electrical short causing complete loss of output            </t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimensional inspection [Y/N]; Visual assessment [Y/N]; Cooling system maintenance [Y/N]                          </t>
+          <t xml:space="preserve">Insulation resistance measured? [Y/N]; Electrical winding continuity tested? [Y/N]; Stator replaced upon detected faults? [Y/N] </t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive            </t>
+          <t xml:space="preserve">Failure-Finding       </t>
         </is>
       </c>
     </row>
@@ -2301,32 +2301,32 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure     </t>
+          <t xml:space="preserve">Stator Failure            </t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support shaft radial position; reduce friction                 </t>
+          <t xml:space="preserve">House stator windings and core; provides stator magnetic field </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Elevated temperature </t>
+          <t xml:space="preserve">NOO - No output             </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                 </t>
+          <t xml:space="preserve">4.2 Open circuit          </t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overheating due to fatigue cracks                      </t>
+          <t xml:space="preserve">Open circuits breaking electrical path                      </t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thermal monitoring [Y/N]; Lubrication state inspection [Y/N]; Vibration analysis [Y/N]                            </t>
+          <t xml:space="preserve">Electrical circuit continuity verified? [Y/N]; Connections repaired? [Y/N]; Stator repaired/replaced as needed? [Y/N]           </t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Failure-Finding       </t>
         </is>
       </c>
     </row>
@@ -2353,32 +2353,32 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brushes Failure         </t>
+          <t xml:space="preserve">Stator Failure            </t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide electrical contact to rotor                           </t>
+          <t xml:space="preserve">House stator windings and core; provides stator magnetic field </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRO - Failure to rotate   </t>
+          <t xml:space="preserve">OHE - Overheating           </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 Open circuit            </t>
+          <t xml:space="preserve">1.4 Deformation           </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loss of current flow causes failure to rotate            </t>
+          <t xml:space="preserve">Structural deformation due to heat                           </t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brush wear inspection [Y/N]; Electrical continuity test [Y/N]; Brush replacement scheduling [Y/N]                </t>
+          <t xml:space="preserve">Visual inspection for deformation? [Y/N]; Cooling performance checked? [Y/N]; Structural repairs undertaken? [Y/N]              </t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding        </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -2405,32 +2405,32 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brushes Failure         </t>
+          <t xml:space="preserve">Stator Failure            </t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide electrical contact to rotor                           </t>
+          <t xml:space="preserve">House stator windings and core; provides stator magnetic field </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRO - Failure to rotate   </t>
+          <t xml:space="preserve">OHE - Overheating           </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.5 Earth/isolation fault    </t>
+          <t xml:space="preserve">2.6 Fatigue               </t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ground fault causing rotor failure                      </t>
+          <t xml:space="preserve">Fatigue damages stator insulation                            </t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ground fault detection [Y/N]; Insulation testing [Y/N]; Brush circuit repair [Y/N]                              </t>
+          <t xml:space="preserve">Thermal cycle analysis? [Y/N]; Insulation integrity tests? [Y/N]; Maintenance and replacement scheduled? [Y/N]                  </t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding        </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
@@ -2457,44 +2457,36 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brushes Failure         </t>
+          <t xml:space="preserve">Stator Failure            </t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide electrical contact to rotor                           </t>
+          <t xml:space="preserve">House stator windings and core; provides stator magnetic field </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">FRO - Failure to rotate   </t>
+          <t xml:space="preserve">PDE - Parameter deviation   </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness              </t>
+          <t xml:space="preserve">2.4 Wear                  </t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose brush assembly causes loss of current flow        </t>
+          <t xml:space="preserve">Wear of stator core and insulation                           </t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brush holder inspection [Y/N]; Fastener tightening [Y/N]; Brush spring tension verification [Y/N]              </t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive            </t>
-        </is>
-      </c>
+          <t xml:space="preserve">Wear inspections performed? [Y/N]; Protective coatings discussed? [Y/N]; Maintenance performed on schedule? [Y/N]              </t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2509,44 +2501,36 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brushes Failure         </t>
+          <t xml:space="preserve">Stator Failure            </t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide electrical contact to rotor                           </t>
+          <t xml:space="preserve">House stator windings and core; provides stator magnetic field </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise              </t>
+          <t xml:space="preserve">PDE - Parameter deviation   </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 Faulty power/voltage     </t>
+          <t xml:space="preserve">2.2 Corrosion             </t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise due to sparking/arcing                            </t>
+          <t xml:space="preserve">Corrosion degrading core and insulation                      </t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power supply voltage inspection [Y/N]; Brush surface examination [Y/N]; Electrical connection checks [Y/N]      </t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive            </t>
-        </is>
-      </c>
+          <t xml:space="preserve">Corrosion inspections and coatings maintained? [Y/N]; Replacement actions taken if needed? [Y/N]                               </t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2561,44 +2545,36 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brushes Failure         </t>
+          <t xml:space="preserve">Stator Failure            </t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide electrical contact to rotor                           </t>
+          <t xml:space="preserve">House stator windings and core; provides stator magnetic field </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise              </t>
+          <t xml:space="preserve">VIB - Vibration             </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness              </t>
+          <t xml:space="preserve">1.5 Looseness             </t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise due to loose components                           </t>
+          <t xml:space="preserve">Loose laminations cause vibration                            </t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanical inspection [Y/N]; Brush holder tightening [Y/N]; Vibration analysis [Y/N]                            </t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive            </t>
-        </is>
-      </c>
+          <t xml:space="preserve">Lamination tightening checked? [Y/N]; Vibration monitored? [Y/N]; Repairs done as needed? [Y/N]                                 </t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2613,44 +2589,36 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brushes Failure         </t>
+          <t xml:space="preserve">Stator Failure            </t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide electrical contact to rotor                           </t>
+          <t xml:space="preserve">House stator windings and core; provides stator magnetic field </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise              </t>
+          <t xml:space="preserve">NOI - Noise                 </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">1.5 Looseness             </t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise from brush wear                                   </t>
+          <t xml:space="preserve">Noise from loose stator components                           </t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brush wear monitoring [Y/N]; Replacement scheduling [Y/N]; Surface cleaning [Y/N]                              </t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive            </t>
-        </is>
-      </c>
+          <t xml:space="preserve">Noise level checked? [Y/N]; Structural fasteners inspected? [Y/N]; Repairs undertaken? [Y/N]                                    </t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2665,44 +2633,36 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brushes Failure         </t>
+          <t xml:space="preserve">Stator Failure            </t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide electrical contact to rotor                           </t>
+          <t xml:space="preserve">House stator windings and core; provides stator magnetic field </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTS - Failure to start    </t>
+          <t xml:space="preserve">FWR - Failure while running </t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 Open circuit            </t>
+          <t xml:space="preserve">1.6 Sticking              </t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open brush circuit prevents motor start                </t>
+          <t xml:space="preserve">Sticking in winding or core causing failure during running   </t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Continuity tests [Y/N]; Brush assembly inspection [Y/N]; Electrical circuit checks [Y/N]                        </t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Failure-Finding        </t>
-        </is>
-      </c>
+          <t xml:space="preserve">Monitoring ongoing operation? [Y/N]; Detect and repair sticking? [Y/N]; Scheduled maintenance? [Y/N]                            </t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2717,44 +2677,36 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brushes Failure         </t>
+          <t xml:space="preserve">Windings Failure          </t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide electrical contact to rotor                           </t>
+          <t xml:space="preserve">Convert electrical power into magnetic field for rotor motion </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTS - Failure to start    </t>
+          <t xml:space="preserve">NOO - No output            </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.5 Earth/isolation fault    </t>
+          <t xml:space="preserve">4.1 Short circuiting      </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ground fault prevents motor start                       </t>
+          <t xml:space="preserve">Short circuit leading to no motor output                      </t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ground fault tests [Y/N]; Insulation resistance measurement [Y/N]; Repair or replacement [Y/N]                 </t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Failure-Finding        </t>
-        </is>
-      </c>
+          <t xml:space="preserve">Electrical insulation tests conducted? [Y/N]; Winding continuity ensured? [Y/N]; Replacement as needed? [Y/N]                   </t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2769,44 +2721,36 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brushes Failure         </t>
+          <t xml:space="preserve">Windings Failure          </t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide electrical contact to rotor                           </t>
+          <t xml:space="preserve">Convert electrical power into magnetic field for rotor motion </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTS - Failure to start    </t>
+          <t xml:space="preserve">NOO - No output            </t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness              </t>
+          <t xml:space="preserve">4.2 Open circuit          </t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose brush connections cause failure to start         </t>
+          <t xml:space="preserve">Open circuit breaking motor phase circuit                     </t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tightness checks [Y/N]; Brush assembly inspection [Y/N]; Brush spring tension measurement [Y/N]               </t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive            </t>
-        </is>
-      </c>
+          <t xml:space="preserve">Circuit continuity measured? [Y/N]; Repairs executed? [Y/N]; Replacement performed if needed? [Y/N]                             </t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2821,44 +2765,36 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brushes Failure         </t>
+          <t xml:space="preserve">Windings Failure          </t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide electrical contact to rotor                           </t>
+          <t xml:space="preserve">Convert electrical power into magnetic field for rotor motion </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTS - Failure to start    </t>
+          <t xml:space="preserve">PDE - Parameter deviation  </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.5 Software error         </t>
+          <t xml:space="preserve">2.2 Corrosion             </t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control software fault inhibits start                   </t>
+          <t xml:space="preserve">Corrosion damaging winding insulation                        </t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control system diagnostics [Y/N]; Software update [Y/N]; Communication verification [Y/N]                      </t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Failure-Finding        </t>
-        </is>
-      </c>
+          <t xml:space="preserve">Corrosion inspections and prevention? [Y/N]; Winding replaced if damaged? [Y/N]                                             </t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2873,44 +2809,36 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coupling Failure        </t>
+          <t xml:space="preserve">Windings Failure          </t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque between motor and driven equipment        </t>
+          <t xml:space="preserve">Convert electrical power into magnetic field for rotor motion </t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration           </t>
+          <t xml:space="preserve">PDE - Parameter deviation  </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.3 Clearance / alignment failure </t>
+          <t xml:space="preserve">2.4 Wear                  </t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Misalignment leading to coupling vibration              </t>
+          <t xml:space="preserve">Wear or mechanical damage to winding insulation              </t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alignment verification [Y/N]; Coupling inspection [Y/N]; Drive shaft balance check [Y/N]                      </t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive            </t>
-        </is>
-      </c>
+          <t xml:space="preserve">Inspection and preventive maintenance? [Y/N]; Timely winding replacement? [Y/N]                                               </t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2925,44 +2853,36 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coupling Failure        </t>
+          <t xml:space="preserve">Windings Failure          </t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque between motor and driven equipment        </t>
+          <t xml:space="preserve">Convert electrical power into magnetic field for rotor motion </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration           </t>
+          <t xml:space="preserve">OHE - Overheating          </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                </t>
+          <t xml:space="preserve">1.4 Deformation           </t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue damage causing vibration                         </t>
+          <t xml:space="preserve">Thermal deformation causing insulation failure               </t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibration monitoring [Y/N]; Fatigue crack inspection [Y/N]; Coupling replacement [Y/N]                        </t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive            </t>
-        </is>
-      </c>
+          <t xml:space="preserve">Thermal imaging and inspection? [Y/N]; Repair or replacement scheduled? [Y/N]                                                 </t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2977,44 +2897,36 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coupling Failure        </t>
+          <t xml:space="preserve">Windings Failure          </t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque between motor and driven equipment        </t>
+          <t xml:space="preserve">Convert electrical power into magnetic field for rotor motion </t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise               </t>
+          <t xml:space="preserve">OHE - Overheating          </t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 External influences    </t>
+          <t xml:space="preserve">2.6 Fatigue               </t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise due to mechanical impact or damage                </t>
+          <t xml:space="preserve">Fatigue cracks or failures due to thermal cycling            </t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise monitoring [Y/N]; Visual inspection [Y/N]; Lubrication check [Y/N]                                     </t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive            </t>
-        </is>
-      </c>
+          <t xml:space="preserve">Fatigue analysis and thermal cycling monitoring? [Y/N]; Repairs scheduled based on diagnostics? [Y/N]                          </t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3029,44 +2941,36 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coupling Failure        </t>
+          <t xml:space="preserve">Windings Failure          </t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque between motor and driven equipment        </t>
+          <t xml:space="preserve">Convert electrical power into magnetic field for rotor motion </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise               </t>
+          <t xml:space="preserve">VIB - Vibration            </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness              </t>
+          <t xml:space="preserve">1.5 Looseness             </t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise due to loose components                            </t>
+          <t xml:space="preserve">Loose connections causing vibration and failure              </t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fastener torque inspection [Y/N]; Coupling mounting inspection [Y/N]; Repair scheduling [Y/N]                </t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive            </t>
-        </is>
-      </c>
+          <t xml:space="preserve">Mechanical and electrical tightness inspections? [Y/N]; Vibration analysis? [Y/N]; Repairs done? [Y/N]                          </t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3081,44 +2985,36 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coupling Failure        </t>
+          <t xml:space="preserve">Windings Failure          </t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque between motor and driven equipment        </t>
+          <t xml:space="preserve">Convert electrical power into magnetic field for rotor motion </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t>FWR - Failure while running</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage               </t>
+          <t xml:space="preserve">1.6 Sticking              </t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanical breakage causing failure                     </t>
+          <t xml:space="preserve">Winding sticking causing failure during operation            </t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visual inspection [Y/N]; Torque load tests [Y/N]; Component replacement [Y/N]                                </t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Failure-Finding        </t>
-        </is>
-      </c>
+          <t xml:space="preserve">Monitoring of operating condition? [Y/N]; Corrective maintenance scheduled? [Y/N]; Replacement or repair as needed? [Y/N]       </t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3133,44 +3029,36 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coupling Failure        </t>
+          <t xml:space="preserve">Brushes Failure           </t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque between motor and driven equipment        </t>
+          <t xml:space="preserve">Transfer electrical current to rotor via slip rings           </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">FTS - Failure to start on demand </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking               </t>
+          <t xml:space="preserve">1.5 Looseness           </t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jamming leading to failure                              </t>
+          <t xml:space="preserve">Brush looseness leading to failure to start                   </t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lubrication inspection [Y/N]; Mechanical function test [Y/N]; Corrective maintenance [Y/N]                   </t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive            </t>
-        </is>
-      </c>
+          <t xml:space="preserve">Brushes checked for looseness? [Y/N]; Electrical continuity verified? [Y/N]; Brushes replaced as per schedule? [Y/N]             </t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3185,44 +3073,36 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coupling Failure        </t>
+          <t xml:space="preserve">Brushes Failure           </t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque between motor and driven equipment        </t>
+          <t xml:space="preserve">Transfer electrical current to rotor via slip rings           </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELU - External leakage - utility medium </t>
+          <t xml:space="preserve">FTS - Failure to start on demand </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                  </t>
+          <t xml:space="preserve">4.2 Open circuit        </t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear causing leakage                                     </t>
+          <t xml:space="preserve">Open circuit in brush causing failure to start                </t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visual inspection [Y/N]; Seal replacement [Y/N]; Leak testing [Y/N]                                          </t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive            </t>
-        </is>
-      </c>
+          <t xml:space="preserve">Electrical path continuity checked? [Y/N]; Brush connection repaired? [Y/N]; Replacement when necessary? [Y/N]                  </t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3237,44 +3117,36 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coupling Failure        </t>
+          <t xml:space="preserve">Brushes Failure           </t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque between motor and driven equipment        </t>
+          <t xml:space="preserve">Transfer electrical current to rotor via slip rings           </t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">NOI - Noise                  </t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 Fouling                </t>
+          <t xml:space="preserve">2.4 Wear                  </t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fouling causes performance degradation                   </t>
+          <t xml:space="preserve">Noise due to brush wear or arcing                             </t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cleaning schedule [Y/N]; Fouling removal [Y/N]; Performance monitoring [Y/N]                                 </t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive            </t>
-        </is>
-      </c>
+          <t xml:space="preserve">Brush wear inspected and recorded? [Y/N]; Electrical contacts cleaned? [Y/N]; Brushes replaced on schedule? [Y/N]              </t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3289,44 +3161,36 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Junction Box Failure    </t>
+          <t xml:space="preserve">Brushes Failure           </t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide electrical connection and protection for motor wiring  </t>
+          <t xml:space="preserve">Transfer electrical current to rotor via slip rings           </t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELU - External leakage - utility medium </t>
+          <t xml:space="preserve">NOI - Noise                  </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                  </t>
+          <t xml:space="preserve">1.5 Looseness             </t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Worn sealing causing external leaks                      </t>
+          <t xml:space="preserve">Loose brush causing abnormal noise                            </t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visual inspection [Y/N]; Seal replacement [Y/N]; Leak testing [Y/N]                                          </t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive            </t>
-        </is>
-      </c>
+          <t xml:space="preserve">Brush connection tightness checked? [Y/N]; Noise monitoring conducted? [Y/N]; Maintenance performed? [Y/N]                      </t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3341,44 +3205,36 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Junction Box Failure    </t>
+          <t xml:space="preserve">Brushes Failure           </t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide electrical connection and protection for motor wiring  </t>
+          <t xml:space="preserve">Transfer electrical current to rotor via slip rings           </t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Elevated temperature </t>
+          <t xml:space="preserve">FWR - Failure while running   </t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.4 Faulty power/voltage     </t>
+          <t xml:space="preserve">1.5 Looseness             </t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wiring overheating causing damage                        </t>
+          <t xml:space="preserve">Brush sticking causing failure during operation               </t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Temperature sensor inspection [Y/N]; Wiring insulation checks [Y/N]; Cooling ventilation checks [Y/N]        </t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive            </t>
-        </is>
-      </c>
+          <t xml:space="preserve">Operation condition monitored? [Y/N]; Brush integrity checked? [Y/N]; Replace brushes if worn? [Y/N]                            </t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3393,44 +3249,36 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Junction Box Failure    </t>
+          <t xml:space="preserve">Brushes Failure           </t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide electrical connection and protection for motor wiring  </t>
+          <t xml:space="preserve">Transfer electrical current to rotor via slip rings           </t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration          </t>
+          <t xml:space="preserve">PDE - Parameter deviation    </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking                </t>
+          <t xml:space="preserve">2.4 Wear                  </t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanical damage causing vibration                      </t>
+          <t xml:space="preserve">Wear or damage causing operational deviations                 </t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibration monitoring [Y/N]; Internal junction box inspection [Y/N]; Repair of mechanical components [Y/N]     </t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive            </t>
-        </is>
-      </c>
+          <t xml:space="preserve">Brush wear inspections performed? [Y/N]; Parameter deviation monitoring? [Y/N]; Repairs or maintenance scheduled? [Y/N]         </t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3445,44 +3293,36 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Junction Box Failure    </t>
+          <t xml:space="preserve">Coupling Failure          </t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide electrical connection and protection for motor wiring  </t>
+          <t xml:space="preserve">Transmit torque between motor and driven equipment            </t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">VIB - Vibration              </t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 External influences     </t>
+          <t xml:space="preserve">1.3 Clearance / alignment failure </t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Performance parameter deviation                           </t>
+          <t xml:space="preserve">Misalignment causing vibration                             </t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electrical parameter monitoring [Y/N]; Visual inspection [Y/N]; Repair [Y/N]                                 </t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive            </t>
-        </is>
-      </c>
+          <t xml:space="preserve">Coupling alignment checked? [Y/N]; Vibration measurements performed? [Y/N]; Corrective actions implemented? [Y/N]              </t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3497,44 +3337,36 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Junction Box Failure    </t>
+          <t xml:space="preserve">Coupling Failure          </t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide electrical connection and protection for motor wiring  </t>
+          <t xml:space="preserve">Transmit torque between motor and driven equipment            </t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTF - Heating failure    </t>
+          <t xml:space="preserve">VIB - Vibration              </t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.1 No cause found          </t>
+          <t xml:space="preserve">2.4 Wear                  </t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heater failure causing loss of heating                    </t>
+          <t xml:space="preserve">Wear in coupling creating vibration                         </t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heater operation test [Y/N]; Electrical circuit inspection [Y/N]; Heater replacement [Y/N]                    </t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Failure-Finding        </t>
-        </is>
-      </c>
+          <t xml:space="preserve">Coupling surface inspected? [Y/N]; Wear replacement scheduled? [Y/N]; Vibration monitoring ongoing? [Y/N]                      </t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3549,44 +3381,36 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heaters Failure         </t>
+          <t xml:space="preserve">Coupling Failure          </t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide heating to prevent condensation                     </t>
+          <t xml:space="preserve">Transmit torque between motor and driven equipment            </t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTF - Heating failure    </t>
+          <t xml:space="preserve">VIB - Vibration              </t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">6.1 No cause found          </t>
+          <t xml:space="preserve">1.5 Looseness             </t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heater failure causing loss of heating                    </t>
+          <t xml:space="preserve">Looseness in coupling causing abnormal vibration           </t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heater operation test [Y/N]; Electrical circuit inspection [Y/N]; Heater replacement [Y/N]                    </t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Failure-Finding        </t>
-        </is>
-      </c>
+          <t xml:space="preserve">Tightness inspections? [Y/N]; Coupling fasteners checked? [Y/N]; Repair or tighten as needed? [Y/N]                            </t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3601,44 +3425,36 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heaters Failure         </t>
+          <t xml:space="preserve">Coupling Failure          </t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide heating to prevent condensation                     </t>
+          <t xml:space="preserve">Transmit torque between motor and driven equipment            </t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">FWR - Failure while running   </t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                    </t>
+          <t xml:space="preserve">2.5 Breakage              </t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heater degradation causing heating inefficiency           </t>
+          <t xml:space="preserve">Coupling breakage causing failure while running            </t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heater visual inspection [Y/N]; Performance monitoring [Y/N]; Preventive replacement [Y/N]                    </t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive            </t>
-        </is>
-      </c>
+          <t xml:space="preserve">Visual inspections? [Y/N]; Load monitoring done? [Y/N]; Coupling replaced if broken? [Y/N]                                    </t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3653,44 +3469,36 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heaters Failure         </t>
+          <t xml:space="preserve">Coupling Failure          </t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide heating to prevent condensation                     </t>
+          <t xml:space="preserve">Transmit torque between motor and driven equipment            </t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELU - External leakage - utility medium </t>
+          <t xml:space="preserve">FWR - Failure while running   </t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion              </t>
+          <t xml:space="preserve">1.6 Sticking              </t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corroded heating components causing leaks               </t>
+          <t xml:space="preserve">Coupling stuck causing operational failure                 </t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visual corrosion checks [Y/N]; Heater sealing integrity test [Y/N]; Repair scheduling [Y/N]                   </t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive            </t>
-        </is>
-      </c>
+          <t xml:space="preserve">Operation condition monitored? [Y/N]; Lubrication inspected? [Y/N]; Maintenance actions taken promptly? [Y/N]                 </t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3705,44 +3513,36 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heaters Failure         </t>
+          <t xml:space="preserve">Coupling Failure          </t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide heating to prevent condensation                     </t>
+          <t xml:space="preserve">Transmit torque between motor and driven equipment            </t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTS - Failure to start    </t>
+          <t xml:space="preserve">STU - Stuck                  </t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 Open circuit            </t>
+          <t xml:space="preserve">1.6 Sticking              </t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heater circuit open causing heating loss                 </t>
+          <t xml:space="preserve">Coupling seizure causing failure                            </t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Continuity testing [Y/N]; Switch and wiring inspections [Y/N]; Electrical repairs [Y/N]                        </t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Failure-Finding        </t>
-        </is>
-      </c>
+          <t xml:space="preserve">Operational tests? [Y/N]; Lubrication system monitored? [Y/N]; Repairs performed as necessary? [Y/N]                           </t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3757,44 +3557,36 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heaters Failure         </t>
+          <t xml:space="preserve">Coupling Failure          </t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide heating to prevent condensation                     </t>
+          <t xml:space="preserve">Transmit torque between motor and driven equipment            </t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTF - Heating failure    </t>
+          <t xml:space="preserve">NOI - Noise                  </t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                 </t>
+          <t xml:space="preserve">1.5 Looseness             </t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heater fatigue failure causes heating loss                </t>
+          <t xml:space="preserve">Noise caused by looseness or misalignment                  </t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thermal imaging [Y/N]; Visual fatigue inspection [Y/N]; Replacement scheduling [Y/N]                          </t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Predictive            </t>
-        </is>
-      </c>
+          <t xml:space="preserve">Noise analysis performed? [Y/N]; Coupling fastener tightness verified? [Y/N]; Repairs performed? [Y/N]                         </t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3809,44 +3601,1488 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heaters Failure         </t>
+          <t xml:space="preserve">Cooling System Failure    </t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provide heating to prevent condensation                     </t>
+          <t xml:space="preserve">Removes heat to maintain motor temperature                     </t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOO - Low output         </t>
+          <t xml:space="preserve">PDE - Parameter deviation    </t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.1 Leakage                 </t>
+          <t xml:space="preserve">5.2 Contamination          </t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heating element leakage reduces system output            </t>
+          <t xml:space="preserve">Fluid contamination reducing cooling efficiency            </t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visual inspection [Y/N]; Leak detection [Y/N]; Component replacement [Y/N]                                  </t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive            </t>
-        </is>
-      </c>
+          <t xml:space="preserve">Cooling system flush scheduled? [Y/N]; Fluid quality monitored regularly? [Y/N]; Preventive cleaning performed? [Y/N]          </t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cooling System Failure    </t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removes heat to maintain motor temperature                     </t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDE - Parameter deviation    </t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fouling or external blockage reducing cooling performance </t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exterior cleaning and inspection? [Y/N]; Flow restrictions removed? [Y/N]; Regular maintenance adhered to? [Y/N]               </t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cooling System Failure    </t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removes heat to maintain motor temperature                     </t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELU - External leakage utility medium </t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.4 Wear                </t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wear causing external leaks                                </t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leak checks performed? [Y/N]; Seal replacements timely? [Y/N]; Leak repairs completed? [Y/N]                                 </t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cooling System Failure    </t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removes heat to maintain motor temperature                     </t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELU - External leakage utility medium </t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.6 Fatigue             </t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fatigue cracks causing leaks                               </t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ultrasonic leak detection done? [Y/N]; Repairs on cracked pipes? [Y/N]; Prevention measures implemented? [Y/N]                 </t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cooling System Failure    </t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removes heat to maintain motor temperature                     </t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LCP - Leakage in closed position </t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4 Deformation          </t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seal or gasket deformation causing leaks                  </t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seal integrity tested? [Y/N]; Gasket replacements managed? [Y/N]; Leak tests completed? [Y/N]                                </t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cooling System Failure    </t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removes heat to maintain motor temperature                     </t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LCP - Leakage in closed position </t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.4 Wear                 </t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wear on sealing surfaces causing leakage                  </t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seal wear inspection? [Y/N]; Seal replaced on condition? [Y/N]; Leak monitoring ongoing? [Y/N]                               </t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cooling System Failure    </t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removes heat to maintain motor temperature                     </t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OHE - Overheating            </t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.2 Contamination          </t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contamination causing reduced cooling                      </t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fluid sampling and cleaning? [Y/N]; Flow rates verified? [Y/N]; Fouling prevention? [Y/N]                                    </t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cooling System Failure    </t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removes heat to maintain motor temperature                     </t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OHE - Overheating            </t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4 Deformation           </t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Structural deformation affecting flow or heat removal     </t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visual inspection of components? [Y/N]; Repairs or replacements completed? [Y/N]; Temperature monitored? [Y/N]                 </t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cooling System Failure    </t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removes heat to maintain motor temperature                     </t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDE - Parameter deviation    </t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion             </t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrosion reducing cooling performance                     </t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrosion detection and mitigation? [Y/N]; Protective coatings applied? [Y/N]                                              </t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cooling System Failure    </t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removes heat to maintain motor temperature                     </t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FWR - Failure while running  </t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.1 Leakage                </t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leaks causing cooling failure                              </t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Continuous leak monitoring? [Y/N]; Prompt leak repairs? [Y/N]; Seal and gasket replacements? [Y/N]                            </t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cooling System Failure    </t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removes heat to maintain motor temperature                     </t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FWR - Failure while running  </t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.2 Contamination          </t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fouling causing cooling failure                            </t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">System cleaning performed? [Y/N]; Fluid quality monitored? [Y/N]; Maintenance schedule followed? [Y/N]                        </t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enclosure Failure         </t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Houses motor components and protects from environment         </t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STD - Structural deficiency  </t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4 Deformation           </t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Buckling or damage causing enclosure failure              </t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regular inspections? [Y/N]; Structural repairs made? [Y/N]; Corrosion protection maintained? [Y/N]                            </t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enclosure Failure         </t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Houses motor components and protects from environment         </t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STD - Structural deficiency  </t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion             </t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrosion weakening enclosure                             </t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrosion inspections? [Y/N]; Protective coatings applied? [Y/N]; Replacements installed if needed? [Y/N]                     </t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enclosure Failure         </t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Houses motor components and protects from environment         </t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELU - External leakage utility medium </t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.4 Wear                </t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wear causing protective barrier leaks                      </t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seals inspected for wear? [Y/N]; Repairs and replacements done? [Y/N]; Leakage monitored regularly? [Y/N]                    </t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enclosure Failure         </t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Houses motor components and protects from environment         </t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELU - External leakage utility medium </t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.6 Fatigue             </t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fatigue induced cracks resulting in noise                </t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Structural fatigue inspections? [Y/N]; Crack repairs and reinforcements? [Y/N]; Noise monitoring? [Y/N]                       </t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enclosure Failure         </t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Houses motor components and protects from environment         </t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOI - Noise                  </t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5 Looseness             </t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loose enclosure parts causing noise                       </t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fastener tightness checks? [Y/N]; Noise level monitored? [Y/N]; Repairs performed? [Y/N]                                      </t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enclosure Failure         </t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Houses motor components and protects from environment         </t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOI - Noise                  </t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.6 Fatigue               </t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fatigue cracks causing noise                              </t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fatigue evaluation and repair? [Y/N]; Noise trend analysis? [Y/N]; Repairs scheduled? [Y/N]                                  </t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enclosure Failure         </t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Houses motor components and protects from environment         </t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIB - Vibration              </t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4 Deformation           </t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vibration due to structural deformation                  </t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Structural inspections? [Y/N]; Repairs implemented? [Y/N]; Vibration checked after repair? [Y/N]                             </t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enclosure Failure         </t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Houses motor components and protects from environment         </t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIB - Vibration              </t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.4 Wear                  </t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wear causing enclosure vibrations                        </t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wear inspections? [Y/N]; Maintenance actions scheduled? [Y/N]; Vibration measurements taken? [Y/N]                           </t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gearbox Failure (*)       </t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transmit torque via gears inside coupling                       </t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIB - Vibration              </t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.4 Wear                  </t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gear tooth wear causing vibration                         </t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gearbox oil sampled and analyzed? [Y/N]; Gear teeth inspected? [Y/N]; Replacement scheduled? [Y/N]                           </t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gearbox Failure (*)       </t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transmit torque via gears inside coupling                       </t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIB - Vibration              </t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.3 Clearance / alignment failure </t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Misalignment causing gearbox vibration                  </t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gear alignment verification? [Y/N]; Coupling adjustments made? [Y/N]; Wear monitored? [Y/N]                                </t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gearbox Failure (*)       </t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transmit torque via gears inside coupling                       </t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOI - Noise                  </t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.5 Breakage              </t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gear tooth breakage causing noise                         </t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inspection and replacement of broken gears? [Y/N]; Noise monitoring? [Y/N]; Preventive maintenance? [Y/N]                    </t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gearbox Failure (*)       </t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transmit torque via gears inside coupling                       </t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOO - Low output (*)          </t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.1 Blockage              </t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blockage causing reduced output                           </t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gearbox flow path cleaned? [Y/N]; Blockages removed? [Y/N]; Lubricant replaced? [Y/N]                                       </t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gearbox Failure (*)       </t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transmit torque via gears inside coupling                       </t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FWR - Failure while running   </t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.6 Sticking              </t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gearbox seizure causing failure while running            </t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lubrication condition monitored? [Y/N]; Seizure inspections? [Y/N]; Scheduled overhauls? [Y/N]                                </t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heaters Failure (*)       </t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide heat to prevent moisture and condensation in motor     </t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FTS - Failure to start on demand </t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.1 Control failure     </t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control failure causing heater not to start              </t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heater control system tested? [Y/N]; Electrical wiring checked? [Y/N]; Replacement or repair performed? [Y/N]                 </t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heaters Failure (*)       </t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide heat to prevent moisture and condensation in motor     </t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FTS - Failure to start on demand </t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.2 Open circuit         </t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open circuit preventing heater start                      </t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrical continuity verified? [Y/N]; Heater wiring continuity checked? [Y/N]; Repairs conducted as required? [Y/N]         </t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heaters Failure (*)       </t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide heat to prevent moisture and condensation in motor     </t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OHE - Overheating            </t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4 Deformation           </t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heater element deformation causing overheating            </t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visual inspections conducted? [Y/N]; Temperature regulation verified? [Y/N]; Preventive maintenance scheduled? [Y/N]         </t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heaters Failure (*)       </t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide heat to prevent moisture and condensation in motor     </t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OHE - Overheating            </t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.7 Electrical failure    </t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrical fault causing overheating                       </t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrical testing of heater? [Y/N]; Insulation resistance checked? [Y/N]; Replacement or repair performed? [Y/N]            </t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heaters Failure (*)       </t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide heat to prevent moisture and condensation in motor     </t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDE - Parameter deviation    </t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Environmental effects leading to failure                </t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Environmental condition monitored? [Y/N]; Protective measures applied? [Y/N]; Heater replacement scheduled? [Y/N]            </t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Junction Box Failure      </t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">House wiring connections and terminal blocks                   </t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELU - External leakage utility medium </t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.4 Wear               </t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Seal or gasket wear causing leakage                      </t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Junction box seals inspected? [Y/N]; Leak repairs done? [Y/N]; Seal replaced regularly? [Y/N]                                 </t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Junction Box Failure      </t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">House wiring connections and terminal blocks                   </t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELU - External leakage utility medium </t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.6 Fatigue            </t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fatigue cracking causing leaks                            </t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Structural inspections conducted? [Y/N]; Leak repair actions performed? [Y/N]; Preventive measures applied? [Y/N]             </t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Junction Box Failure      </t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">House wiring connections and terminal blocks                   </t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSF - Control / signal failure </t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.2 Open circuit        </t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrical break causing signal failure                  </t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wiring continuity checked? [Y/N]; Repairs or replacements done? [Y/N]; Electrical tests performed? [Y/N]                      </t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Junction Box Failure      </t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">House wiring connections and terminal blocks                   </t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOI - Noise                  </t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5 Looseness             </t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loose connection causing noise                            </t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Terminal tightness inspected? [Y/N]; Noise monitoring performed? [Y/N]; Repair conducted? [Y/N]                               </t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motor, Electric </t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Junction Box Failure      </t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">House wiring connections and terminal blocks                   </t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIB - Vibration              </t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4 Deformation           </t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Structural deformation causing vibration                  </t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Structural integrity inspections? [Y/N]; Corrective maintenance? [Y/N]; Vibration trend monitoring? [Y/N]                     </t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/EMS upgrade output.xlsx
+++ b/outputs/EMS upgrade output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J99"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,27 +486,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotor shaft at non-drive end and facilitate rotation  </t>
+          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on the non-drive end </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration               </t>
+          <t xml:space="preserve">VIB - Vibration              </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                      </t>
+          <t xml:space="preserve">2.4 Wear                         </t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Increased vibration due to bearing surface wear                    </t>
+          <t xml:space="preserve">Increased vibration and eventual bearing damage               </t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE bearings inspected for wear signs? [Y/N]; Lubrication level checked and maintained? [Y/N]; Vibration analysis performed? [Y/N] </t>
+          <t xml:space="preserve">1. Vibration analysis performed regularly? [Y/N]&lt;br&gt;2. Bearing condition monitored visually or via sensors? [Y/N]&lt;br&gt;3. Lubrication levels maintained as per schedule? [Y/N] </t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Predictive, Preventive             </t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -538,12 +538,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotor shaft at non-drive end and facilitate rotation  </t>
+          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on the non-drive end </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration               </t>
+          <t xml:space="preserve">VIB - Vibration              </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -553,12 +553,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abnormal vibration due to misaligned bearing                       </t>
+          <t xml:space="preserve">Excessive vibration causing premature bearing failure          </t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alignment measurements and corrections done? [Y/N]; Shaft alignment verified? [Y/N]; Corrective alignment actions performed? [Y/N] </t>
+          <t xml:space="preserve">1. Shaft alignment checked periodically? [Y/N]&lt;br&gt;2. Coupling alignment verified during maintenance? [Y/N]&lt;br&gt;3. Corrective alignment performed promptly? [Y/N]        </t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive            </t>
+          <t xml:space="preserve">Preventive                       </t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -590,27 +590,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotor shaft at non-drive end and facilitate rotation  </t>
+          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on the non-drive end </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration               </t>
+          <t xml:space="preserve">VIB - Vibration              </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                   </t>
+          <t xml:space="preserve">2.6 Fatigue                      </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue damage in bearing material causing vibration               </t>
+          <t xml:space="preserve">Fatigue cracks leading to bearing spalling or failure         </t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing integrity inspection conducted? [Y/N]; Load and vibration history reviewed? [Y/N]; Bearings replaced as scheduled? [Y/N] </t>
+          <t xml:space="preserve">1. Load and vibration monitoring conducted? [Y/N]&lt;br&gt;2. Operating within design load limits? [Y/N]&lt;br&gt;3. Bearings replaced at end of fatigue life? [Y/N]               </t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Predictive, Preventive             </t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -642,27 +642,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotor shaft at non-drive end and facilitate rotation  </t>
+          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on the non-drive end </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration               </t>
+          <t xml:space="preserve">NOI - Noise                  </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness                </t>
+          <t xml:space="preserve">2.4 Wear                         </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing looseness causing abnormal vibration                       </t>
+          <t xml:space="preserve">Abnormal noise indicating bearing wear                       </t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bolts and fittings checked for tightness? [Y/N]; Vibration monitored? [Y/N]; Maintenance of bearing housing tightness? [Y/N]       </t>
+          <t xml:space="preserve">1. Audible inspections carried out? [Y/N]&lt;br&gt;2. Noise level recorded and trended? [Y/N]&lt;br&gt;3. Corrective action on abnormal noise? [Y/N]                           </t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive            </t>
+          <t xml:space="preserve">Failure-Finding, Preventive       </t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -694,27 +694,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotor shaft at non-drive end and facilitate rotation  </t>
+          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on the non-drive end </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                   </t>
+          <t xml:space="preserve">NOI - Noise                  </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                      </t>
+          <t xml:space="preserve">1.5 Looseness                   </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise caused by surface degradation or roughness                   </t>
+          <t xml:space="preserve">Loose bearing causing noise and movement                      </t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing noise monitoring performed? [Y/N]; Lubrication condition checked? [Y/N]; Noise source analysis conducted? [Y/N]            </t>
+          <t xml:space="preserve">1. Bearing housing tightness verified during maintenance? [Y/N]&lt;br&gt;2. Bearing mounting inspected? [Y/N]&lt;br&gt;3. Torque of bolts checked and corrected? [Y/N]        </t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Failure-Finding                  </t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -746,27 +746,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotor shaft at non-drive end and facilitate rotation  </t>
+          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on the non-drive end </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                   </t>
+          <t xml:space="preserve">NOI - Noise                  </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness                </t>
+          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Looseness causing increased noise                                  </t>
+          <t xml:space="preserve">Noise caused by external impacts or contamination           </t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bolts and fittings checked for tightness? [Y/N]; Noise monitored and analyzed? [Y/N]; Vibration checks performed? [Y/N]            </t>
+          <t xml:space="preserve">1. Visual inspection for foreign objects? [Y/N]&lt;br&gt;2. Environmental sealing maintained? [Y/N]&lt;br&gt;3. Protection measures implemented? [Y/N]                      </t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive            </t>
+          <t xml:space="preserve">Failure-Finding, Preventive       </t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -798,27 +798,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotor shaft at non-drive end and facilitate rotation  </t>
+          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on the non-drive end </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                   </t>
+          <t xml:space="preserve">ELU - External leakage - utility medium </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                  </t>
+          <t xml:space="preserve">2.2 Corrosion               </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue cracks causing noise                                       </t>
+          <t xml:space="preserve">Corrosion leading to lubricant leak                           </t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue damage evaluation? [Y/N]; Acoustic emission monitoring? [Y/N]; Bearings replaced if fatigued? [Y/N]                      </t>
+          <t xml:space="preserve">1. Seal and housing inspected for corrosion? [Y/N]&lt;br&gt;2. Corrosion protective treatments applied? [Y/N]&lt;br&gt;3. Repairs done immediately on leak detection? [Y/N]    </t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Failure-Finding, Preventive       </t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotor shaft at non-drive end and facilitate rotation  </t>
+          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on the non-drive end </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating             </t>
+          <t xml:space="preserve">ELU - External leakage - utility medium </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation             </t>
+          <t xml:space="preserve">2.4 Wear                    </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing deformation causing heat build-up                         </t>
+          <t xml:space="preserve">Wear causing seal or housing leakage                         </t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing temperature monitored? [Y/N]; Physical inspection of bearing deformation? [Y/N]; Corrective actions on deformation? [Y/N] </t>
+          <t xml:space="preserve">1. Seal and housing condition monitored? [Y/N]&lt;br&gt;2. Replacement or repair of worn parts? [Y/N]&lt;br&gt;3. Routine lubrication system checks? [Y/N]                  </t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Failure-Finding, Preventive       </t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -902,27 +902,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotor shaft at non-drive end and facilitate rotation  </t>
+          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on the non-drive end </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating             </t>
+          <t xml:space="preserve">OHE - Overheating            </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                 </t>
+          <t xml:space="preserve">1.4 Deformation               </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Breakdown of material due to cyclic thermal stress                </t>
+          <t xml:space="preserve">Bearing housing deformation causing heat build-up           </t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thermal cycling assessment performed? [Y/N]; Thermal imaging inspections? [Y/N]; Bearing replaced when fatigued? [Y/N]           </t>
+          <t xml:space="preserve">1. Visual inspection of bearing housing? [Y/N]&lt;br&gt;2. Structural integrity checks performed? [Y/N]&lt;br&gt;3. Alignment corrections made if required? [Y/N]             </t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Preventive                       </t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -954,27 +954,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotor shaft at non-drive end and facilitate rotation  </t>
+          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on the non-drive end </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating             </t>
+          <t xml:space="preserve">OHE - Overheating            </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">2.6 Fatigue                  </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Excessive friction causing overheating                            </t>
+          <t xml:space="preserve">Overheating caused by fatigue in bearing components          </t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lubrication levels checked? [Y/N]; Friction condition monitored? [Y/N]; Bearing lubricated and replaced per maintenance? [Y/N]    </t>
+          <t xml:space="preserve">1. Temperature sensors regularly checked? [Y/N]&lt;br&gt;2. Vibration monitored for fatigue? [Y/N]&lt;br&gt;3. Bearings replaced on signs of overload? [Y/N]                  </t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Predictive, Preventive             </t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1006,27 +1006,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotor shaft at non-drive end and facilitate rotation  </t>
+          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on the non-drive end </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOO - Low output (*)           </t>
+          <t xml:space="preserve">FWR - Failure while running  </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination           </t>
+          <t xml:space="preserve">2.5 Breakage                 </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contamination degrades bearing lubrication                        </t>
+          <t xml:space="preserve">Bearing rolling element or cage failure                      </t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lubricant contamination analysis? [Y/N]; Particulate filters checked? [Y/N]; Lubricant changed as per schedule? [Y/N]             </t>
+          <t>1. Visual and vibration inspections regularly scheduled? [Y/N]&lt;br&gt;2. Early replacement of damaged bearings? [Y/N]&lt;br&gt;3. Lubrication monitored and maintained? [Y/N]</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Failure-Finding, Preventive       </t>
         </is>
       </c>
     </row>
@@ -1048,37 +1048,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure       </t>
+          <t xml:space="preserve">DE Bearing Failure       </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotor shaft at non-drive end and facilitate rotation  </t>
+          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on drive end         </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOO - Low output (*)           </t>
+          <t xml:space="preserve">VIB - Vibration              </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion              </t>
+          <t xml:space="preserve">2.4 Wear                       </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion causes bearing surface degradation                      </t>
+          <t xml:space="preserve">Increased vibration due to wear                              </t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion inspection performed? [Y/N]; Protective coatings maintained? [Y/N]; Bearing replaced if corroded? [Y/N]                 </t>
+          <t xml:space="preserve">1. Vibration monitoring and analysis scheduled? [Y/N]&lt;br&gt;2. Lubrication intervals adhered to? [Y/N]&lt;br&gt;3. Maintenance on bearing condition conducted? [Y/N]       </t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive            </t>
+          <t xml:space="preserve">Predictive, Preventive             </t>
         </is>
       </c>
     </row>
@@ -1100,37 +1100,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure       </t>
+          <t xml:space="preserve">DE Bearing Failure       </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotor shaft at non-drive end and facilitate rotation  </t>
+          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on drive end         </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running    </t>
+          <t xml:space="preserve">VIB - Vibration              </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking               </t>
+          <t xml:space="preserve">1.3 Clearance / alignment failure </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing seizure during operation                                  </t>
+          <t xml:space="preserve">Misalignment causing vibration and premature failure       </t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Load and vibration monitored? [Y/N]; Seizure inspection after shutdown? [Y/N]; Lubricant and bearing replaced on schedule? [Y/N] </t>
+          <t xml:space="preserve">1. Shaft and coupling alignment checked? [Y/N]&lt;br&gt;2. Realignment maintenance carried out timely? [Y/N]&lt;br&gt;3. Adjustment recorded and monitored? [Y/N]             </t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Preventive                       </t>
         </is>
       </c>
     </row>
@@ -1152,37 +1152,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure       </t>
+          <t xml:space="preserve">DE Bearing Failure       </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotor shaft at non-drive end and facilitate rotation  </t>
+          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on drive end         </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running    </t>
+          <t xml:space="preserve">VIB - Vibration              </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.7 Thermal degradation    </t>
+          <t xml:space="preserve">2.6 Fatigue                  </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat buildup causing bearing failure                             </t>
+          <t xml:space="preserve">Fatigue cracks causing bearing damage                      </t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Temperature monitoring during operation? [Y/N]; Thermal protection system checked? [Y/N]; Bearing temperature maintained within limits? [Y/N] </t>
+          <t xml:space="preserve">1. Fatigue condition monitoring? [Y/N]&lt;br&gt;2. Replacing bearings before failure? [Y/N]&lt;br&gt;3. Vibration data trended and analyzed? [Y/N]                           </t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Predictive, Preventive             </t>
         </is>
       </c>
     </row>
@@ -1204,37 +1204,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure        </t>
+          <t xml:space="preserve">DE Bearing Failure       </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotor shaft at drive end and facilitate rotation      </t>
+          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on drive end         </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration               </t>
+          <t xml:space="preserve">NOI - Noise                  </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">2.4 Wear                       </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear creating imbalance and vibration                           </t>
+          <t xml:space="preserve">Noise due to bearing wear                                   </t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE bearing wear inspections? [Y/N]; Lubricant contamination checked? [Y/N]; Vibration spectrum analyzed? [Y/N]                  </t>
+          <t xml:space="preserve">1. Noise inspections and acoustic monitoring? [Y/N]&lt;br&gt;2. Bearings replaced on abnormal noise? [Y/N]&lt;br&gt;3. Repair of loose fittings? [Y/N]                     </t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Failure-Finding, Preventive       </t>
         </is>
       </c>
     </row>
@@ -1256,37 +1256,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure        </t>
+          <t xml:space="preserve">DE Bearing Failure       </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotor shaft at drive end and facilitate rotation      </t>
+          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on drive end         </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration               </t>
+          <t xml:space="preserve">NOI - Noise                  </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.3 Clearance / alignment failure </t>
+          <t xml:space="preserve">1.5 Looseness                </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Misalignment causing vibration                                 </t>
+          <t xml:space="preserve">Looseness creating noise                                    </t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regular alignment checks? [Y/N]; Coupling and shaft alignment assessed? [Y/N]; Corrective realignment performed? [Y/N]          </t>
+          <t xml:space="preserve">1. Tightness and torque checks? [Y/N]&lt;br&gt;2. Repair after looseness detected? [Y/N]&lt;br&gt;3. Tightening procedure routinely performed? [Y/N]                         </t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive            </t>
+          <t xml:space="preserve">Failure-Finding                  </t>
         </is>
       </c>
     </row>
@@ -1308,37 +1308,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure        </t>
+          <t xml:space="preserve">DE Bearing Failure       </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotor shaft at drive end and facilitate rotation      </t>
+          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on drive end         </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration               </t>
+          <t xml:space="preserve">OHE - Overheating            </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                </t>
+          <t xml:space="preserve">2.4 Wear                      </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Material fatigue in bearing causing vibration                   </t>
+          <t xml:space="preserve">Lubricant deterioration causing heat increase                </t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue damage analysis conducted? [Y/N]; Bearing life cycles monitored? [Y/N]; Replace bearings based on damage? [Y/N]          </t>
+          <t xml:space="preserve">1. Lubricant condition regularly tested? [Y/N]&lt;br&gt;2. Cooling functionality checked? [Y/N]&lt;br&gt;3. Lubrication system maintained? [Y/N]                           </t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Predictive, Preventive             </t>
         </is>
       </c>
     </row>
@@ -1360,37 +1360,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure        </t>
+          <t xml:space="preserve">DE Bearing Failure       </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotor shaft at drive end and facilitate rotation      </t>
+          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on drive end         </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                   </t>
+          <t xml:space="preserve">OHE - Overheating            </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">1.4 Deformation             </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise generated due to wear                                     </t>
+          <t xml:space="preserve">Deformation causing heat build-up                          </t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise monitoring and analysis? [Y/N]; Lubricant condition checked? [Y/N]; Bearing noise diagnostics done? [Y/N]                 </t>
+          <t xml:space="preserve">1. Visual inspection for housing deformation? [Y/N]&lt;br&gt;2. Structural repair performed? [Y/N]&lt;br&gt;3. Monitoring of housing condition? [Y/N]                     </t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Preventive                       </t>
         </is>
       </c>
     </row>
@@ -1412,37 +1412,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure        </t>
+          <t xml:space="preserve">DE Bearing Failure       </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotor shaft at drive end and facilitate rotation      </t>
+          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on drive end         </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                   </t>
+          <t xml:space="preserve">FWR - Failure while running  </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness             </t>
+          <t xml:space="preserve">2.5 Breakage                  </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose bearing components cause noise                          </t>
+          <t xml:space="preserve">Breakage of bearing components                             </t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearings bolts and caps inspected? [Y/N]; Noise trend analysis performed? [Y/N]; Tightening and repair conducted? [Y/N]          </t>
+          <t xml:space="preserve">1. Visual and vibration inspections? [Y/N]&lt;br&gt;2. Replacement after breakage? [Y/N]&lt;br&gt;3. Continuous monitoring program? [Y/N]                                </t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive            </t>
+          <t xml:space="preserve">Failure-Finding, Preventive       </t>
         </is>
       </c>
     </row>
@@ -1464,47 +1464,47 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure        </t>
+          <t xml:space="preserve">DE Bearing Failure       </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotor shaft at drive end and facilitate rotation      </t>
+          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on drive end         </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating             </t>
+          <t xml:space="preserve">FWR - Failure while running  </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation           </t>
+          <t xml:space="preserve">2.6 Fatigue                  </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Structural deformation produces excessive heat               </t>
+          <t xml:space="preserve">Fatigue and material failure                                </t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Visual inspection of bearing deformation? [Y/N]; Thermal sensor check? [Y/N]; Corrective action applied to reduce deformation? [Y/N]</t>
+          <t xml:space="preserve">1. Fatigue analysis program? [Y/N]&lt;br&gt;2. Vibration trending? [Y/N]&lt;br&gt;3. Timely replacement before failure? [Y/N]                                         </t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                  </t>
+          <t xml:space="preserve">TBD                   </t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Predictive, Preventive             </t>
         </is>
       </c>
     </row>
@@ -1516,37 +1516,37 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure        </t>
+          <t xml:space="preserve">Brushes Failure          </t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotor shaft at drive end and facilitate rotation      </t>
+          <t xml:space="preserve">Conducts current to rotor for energy transfer                              </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating             </t>
+          <t xml:space="preserve">VIB - Vibration              </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue               </t>
+          <t xml:space="preserve">2.4 Wear                      </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue cracks causing heat build-up                          </t>
+          <t xml:space="preserve">Increased vibration due to brush wear                      </t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue life monitored? [Y/N]; Thermal imaging inspection? [Y/N]; Bearing replaced on fatigue detection? [Y/N]                   </t>
+          <t xml:space="preserve">1. Periodic brush wear measurement? [Y/N]&lt;br&gt;2. Timely brush replacement? [Y/N]&lt;br&gt;3. Inspection of brush holders? [Y/N]                                  </t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Predictive, Preventive             </t>
         </is>
       </c>
     </row>
@@ -1568,37 +1568,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure        </t>
+          <t xml:space="preserve">Brushes Failure          </t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotor shaft at drive end and facilitate rotation      </t>
+          <t xml:space="preserve">Conducts current to rotor for energy transfer                              </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating             </t>
+          <t xml:space="preserve">VIB - Vibration              </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                  </t>
+          <t xml:space="preserve">1.5 Looseness                </t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Excess friction causing overheating                           </t>
+          <t xml:space="preserve">Brush looseness causing noise and wear                    </t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lubricant levels and condition checked? [Y/N]; Friction and temperature monitored? [Y/N]; Preventive lubrication applied? [Y/N] </t>
+          <t xml:space="preserve">1. Brush mount tightness verified regularly? [Y/N]&lt;br&gt;2. Fasteners tightened as necessary? [Y/N]&lt;br&gt;3. Repair actions undertaken? [Y/N]                      </t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Failure-Finding                  </t>
         </is>
       </c>
     </row>
@@ -1620,37 +1620,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure        </t>
+          <t xml:space="preserve">Brushes Failure          </t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotor shaft at drive end and facilitate rotation      </t>
+          <t xml:space="preserve">Conducts current to rotor for energy transfer                              </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOO - Low output (*)           </t>
+          <t xml:space="preserve">NOI - Noise                  </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination         </t>
+          <t xml:space="preserve">2.4 Wear                      </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lubricant contamination causing performance loss             </t>
+          <t xml:space="preserve">Noise due to worn brushes                                 </t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lubricant checked for contamination? [Y/N]; Filters inspected? [Y/N]; Lubrication system maintained? [Y/N]                      </t>
+          <t xml:space="preserve">1. Auditory inspections? [Y/N]&lt;br&gt;2. Noise level monitoring and trending? [Y/N]&lt;br&gt;3. Brush replacement on abnormal noise? [Y/N]                            </t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Failure-Finding                  </t>
         </is>
       </c>
     </row>
@@ -1672,37 +1672,37 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure        </t>
+          <t xml:space="preserve">Brushes Failure          </t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotor shaft at drive end and facilitate rotation      </t>
+          <t xml:space="preserve">Conducts current to rotor for energy transfer                              </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOO - Low output (*)           </t>
+          <t xml:space="preserve">NOI - Noise                  </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion             </t>
+          <t xml:space="preserve">1.5 Looseness                </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion on bearing surfaces causing failure                </t>
+          <t xml:space="preserve">Noise generated by loose brushes                          </t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion inspected? [Y/N]; Protective measures implemented? [Y/N]; Bearing replaced on corrosion detection? [Y/N]              </t>
+          <t xml:space="preserve">1. Tightness of brush mounting checked? [Y/N]&lt;br&gt;2. Loose brush repairs? [Y/N]&lt;br&gt;3. Vibration noise surveys conducted? [Y/N]                              </t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive            </t>
+          <t xml:space="preserve">Failure-Finding                  </t>
         </is>
       </c>
     </row>
@@ -1724,37 +1724,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure        </t>
+          <t xml:space="preserve">Brushes Failure          </t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotor shaft at drive end and facilitate rotation      </t>
+          <t xml:space="preserve">Conducts current to rotor for energy transfer                              </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running    </t>
+          <t xml:space="preserve">FTS - Failure to start on demand </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking              </t>
+          <t xml:space="preserve">4.2 Open circuit            </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing seizure causing failure during operation             </t>
+          <t xml:space="preserve">Open circuit preventing motor start                      </t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operating conditions monitored? [Y/N]; Bearing lubed and cleaned? [Y/N]; Bearings replaced timely? [Y/N]                         </t>
+          <t xml:space="preserve">1. Electrical continuity tested? [Y/N]&lt;br&gt;2. Brush connection inspected? [Y/N]&lt;br&gt;3. Replacement scheduled? [Y/N]                                         </t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Failure-Finding                  </t>
         </is>
       </c>
     </row>
@@ -1776,37 +1776,37 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure        </t>
+          <t xml:space="preserve">Brushes Failure          </t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support rotor shaft at drive end and facilitate rotation      </t>
+          <t xml:space="preserve">Conducts current to rotor for energy transfer                              </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running    </t>
+          <t xml:space="preserve">STU - Stuck                  </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.7 Thermal degradation    </t>
+          <t xml:space="preserve">1.6 Sticking                 </t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overheating causing bearing failure                          </t>
+          <t xml:space="preserve">Brush or holder stuck causing failure                    </t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Temperature monitoring during operation? [Y/N]; Cooling system verified? [Y/N]; Thermo protection functional? [Y/N]             </t>
+          <t xml:space="preserve">1. Brush movement checked during inspection? [Y/N]&lt;br&gt;2. Immediately freed or replaced if stuck? [Y/N]&lt;br&gt;3. Lubrication of brush holders as needed? [Y/N]     </t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Failure-Finding                  </t>
         </is>
       </c>
     </row>
@@ -1828,37 +1828,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotor Failure             </t>
+          <t xml:space="preserve">Cooling System Failure   </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque from motor to driven equipment                 </t>
+          <t xml:space="preserve">Removes heat from motor components                                        </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
+          <t xml:space="preserve">ELU - External leakage - utility medium </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.3 Clearance / alignment failure </t>
+          <t xml:space="preserve">2.2 Corrosion              </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotor imbalance or misalignment causing vibration          </t>
+          <t xml:space="preserve">Leak causing cooling inefficiency                         </t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotor balance inspected? [Y/N]; Alignment checked? [Y/N]; Corrective balancing and alignment performed? [Y/N]                  </t>
+          <t xml:space="preserve">1. Visual inspections for leaks? [Y/N]&lt;br&gt;2. Corrosion treated or repaired? [Y/N]&lt;br&gt;3. Preventive corrosion control applied? [Y/N]                      </t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive            </t>
+          <t xml:space="preserve">Failure-Finding, Preventive       </t>
         </is>
       </c>
     </row>
@@ -1880,37 +1880,37 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotor Failure             </t>
+          <t xml:space="preserve">Cooling System Failure   </t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque from motor to driven equipment                 </t>
+          <t xml:space="preserve">Removes heat from motor components                                        </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
+          <t xml:space="preserve">ELU - External leakage - utility medium </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue               </t>
+          <t xml:space="preserve">1.4 Deformation           </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotor material fatigue causing vibration                     </t>
+          <t xml:space="preserve">Deformation or crack causing leaks                        </t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue analysis performed? [Y/N]; Cycle counts reviewed? [Y/N]; Rotor replaced when required? [Y/N]                           </t>
+          <t xml:space="preserve">1. Structural inspections performed? [Y/N]&lt;br&gt;2. Repairs or replacements carried out promptly? [Y/N]&lt;br&gt;3. Cooling efficiency monitored? [Y/N]            </t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Preventive                       </t>
         </is>
       </c>
     </row>
@@ -1932,37 +1932,37 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotor Failure             </t>
+          <t xml:space="preserve">Cooling System Failure   </t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque from motor to driven equipment                 </t>
+          <t xml:space="preserve">Removes heat from motor components                                        </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                 </t>
+          <t xml:space="preserve">PDE - Parameter deviation   </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage              </t>
+          <t xml:space="preserve">5.2 Contamination           </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise due to cracks or rotor breakage                        </t>
+          <t xml:space="preserve">Cooling fluid contaminated reducing performance          </t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acoustic monitoring performed? [Y/N]; Rotor inspected for cracks? [Y/N]; Rotor replaced after breakage detected? [Y/N]          </t>
+          <t xml:space="preserve">1. Cooling fluid quality tested? [Y/N]&lt;br&gt;2. Filters cleaned or replaced? [Y/N]&lt;br&gt;3. Contaminated fluid replaced? [Y/N]                            </t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Predictive, Preventive             </t>
         </is>
       </c>
     </row>
@@ -1984,37 +1984,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotor Failure             </t>
+          <t xml:space="preserve">Cooling System Failure   </t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque from motor to driven equipment                 </t>
+          <t xml:space="preserve">Removes heat from motor components                                        </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                 </t>
+          <t xml:space="preserve">PDE - Parameter deviation   </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness             </t>
+          <t xml:space="preserve">2.4 Wear                   </t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose rotor components producing noise                      </t>
+          <t xml:space="preserve">Wear causing restricted fluid flow                       </t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotor component tightness checked? [Y/N]; Noise trend monitored? [Y/N]; Repairs performed promptly? [Y/N]                      </t>
+          <t xml:space="preserve">1. Visual inspections and monitoring? [Y/N]&lt;br&gt;2. Regular filter changes? [Y/N]&lt;br&gt;3. Fluid flow measurements made regularly? [Y/N]                    </t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive            </t>
+          <t xml:space="preserve">Preventive                       </t>
         </is>
       </c>
     </row>
@@ -2036,37 +2036,37 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotor Failure             </t>
+          <t xml:space="preserve">Cooling System Failure   </t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque from motor to driven equipment                 </t>
+          <t xml:space="preserve">Removes heat from motor components                                        </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating           </t>
+          <t xml:space="preserve">FWR - Failure while running </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation           </t>
+          <t xml:space="preserve">2.5 Breakage               </t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thermal deformation causing overheating                     </t>
+          <t xml:space="preserve">Cracks or structural failure affecting cooling            </t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thermal imaging inspections? [Y/N]; Mechanical deformation assessed? [Y/N]; Cooling system maintained? [Y/N]                    </t>
+          <t xml:space="preserve">1. Visual crack detection inspections? [Y/N]&lt;br&gt;2. Repair or replace broken parts? [Y/N]&lt;br&gt;3. Preventive maintenance scheduled? [Y/N]                   </t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Failure-Finding, Preventive       </t>
         </is>
       </c>
     </row>
@@ -2088,37 +2088,37 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotor Failure             </t>
+          <t xml:space="preserve">Cooling System Failure   </t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque from motor to driven equipment                 </t>
+          <t xml:space="preserve">Removes heat from motor components                                        </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating           </t>
+          <t xml:space="preserve">FWR - Failure while running </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue               </t>
+          <t xml:space="preserve">2.6 Fatigue                </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue cracking leading to overheating                      </t>
+          <t xml:space="preserve">Fatigue cracks affecting structural/pipe components       </t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thermal cycling assessment? [Y/N]; Rotor crack inspections? [Y/N]; Preventive replacement? [Y/N]                               </t>
+          <t xml:space="preserve">1. Monitoring for signs of fatigue? [Y/N]&lt;br&gt;2. Reinforcement or replacement as necessary? [Y/N]&lt;br&gt;3. Periodic stress relief? [Y/N]                      </t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Failure-Finding, Preventive       </t>
         </is>
       </c>
     </row>
@@ -2140,37 +2140,37 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotor Failure             </t>
+          <t xml:space="preserve">Cooling System Failure   </t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque from motor to driven equipment                 </t>
+          <t xml:space="preserve">Removes heat from motor components                                        </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation   </t>
+          <t xml:space="preserve">OHE - Overheating          </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion             </t>
+          <t xml:space="preserve">1.4 Deformation           </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion causing rotor degradation                         </t>
+          <t xml:space="preserve">Structural deformation causing overheating                </t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Visual and NDT corrosion inspection? [Y/N]; Protective coatings checked and maintained? [Y/N]; Rotor replaced if corroded? [Y/N]</t>
+          <t xml:space="preserve">1. Visual inspections for deformation? [Y/N]&lt;br&gt;2. Repairs and monitoring? [Y/N]&lt;br&gt;3. Functional cooling checks? [Y/N]                                </t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive            </t>
+          <t xml:space="preserve">Preventive                       </t>
         </is>
       </c>
     </row>
@@ -2192,37 +2192,37 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotor Failure             </t>
+          <t xml:space="preserve">Cooling System Failure   </t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque from motor to driven equipment                 </t>
+          <t xml:space="preserve">Removes heat from motor components                                        </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running  </t>
+          <t xml:space="preserve">OHE - Overheating          </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking              </t>
+          <t xml:space="preserve">2.2 Corrosion             </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotor seizure causing operational failure                   </t>
+          <t xml:space="preserve">Corrosion decreasing cooling efficiency                   </t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rotor operation monitored and recorded? [Y/N]; Operational parameters checked? [Y/N]; Maintenance actions followed? [Y/N]       </t>
+          <t xml:space="preserve">1. Corrosion inspections and treatments? [Y/N]&lt;br&gt;2. Protective coatings maintained? [Y/N]&lt;br&gt;3. Repairs performed when corrosion found? [Y/N]           </t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Failure-Finding, Preventive       </t>
         </is>
       </c>
     </row>
@@ -2244,37 +2244,37 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stator Failure            </t>
+          <t xml:space="preserve">Coupling Failure         </t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">House stator windings and core; provides stator magnetic field </t>
+          <t xml:space="preserve">Transfers torque from motor to driven equipment                           </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOO - No output             </t>
+          <t xml:space="preserve">SLP - Slippage             </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.1 Short circuiting      </t>
+          <t xml:space="preserve">1.3 Clearance / alignment failure </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electrical short causing complete loss of output            </t>
+          <t xml:space="preserve">Slippage causing loss of torque transmission              </t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Insulation resistance measured? [Y/N]; Electrical winding continuity tested? [Y/N]; Stator replaced upon detected faults? [Y/N] </t>
+          <t xml:space="preserve">1. Coupling alignment checked? [Y/N]&lt;br&gt;2. Belt tension or gear mesh maintained? [Y/N]&lt;br&gt;3. Coupling replaced upon excessive slippage? [Y/N]              </t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding       </t>
+          <t xml:space="preserve">Failure-Finding, Preventive       </t>
         </is>
       </c>
     </row>
@@ -2296,37 +2296,37 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stator Failure            </t>
+          <t xml:space="preserve">Coupling Failure         </t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">House stator windings and core; provides stator magnetic field </t>
+          <t xml:space="preserve">Transfers torque from motor to driven equipment                           </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOO - No output             </t>
+          <t xml:space="preserve">VIB - Vibration            </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 Open circuit          </t>
+          <t xml:space="preserve">2.6 Fatigue               </t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open circuits breaking electrical path                      </t>
+          <t xml:space="preserve">Fatigue cracking causing vibration and failure             </t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electrical circuit continuity verified? [Y/N]; Connections repaired? [Y/N]; Stator repaired/replaced as needed? [Y/N]           </t>
+          <t xml:space="preserve">1. Vibration monitored continuously? [Y/N]&lt;br&gt;2. Coupling integrity inspection? [Y/N]&lt;br&gt;3. Repairs/replacements done promptly? [Y/N]                   </t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding       </t>
+          <t xml:space="preserve">Predictive, Preventive             </t>
         </is>
       </c>
     </row>
@@ -2348,37 +2348,37 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stator Failure            </t>
+          <t xml:space="preserve">Coupling Failure         </t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">House stator windings and core; provides stator magnetic field </t>
+          <t xml:space="preserve">Transfers torque from motor to driven equipment                           </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating           </t>
+          <t xml:space="preserve">NOI - Noise                </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation           </t>
+          <t xml:space="preserve">1.5 Looseness             </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Structural deformation due to heat                           </t>
+          <t xml:space="preserve">Loose coupling parts causing noise                        </t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visual inspection for deformation? [Y/N]; Cooling performance checked? [Y/N]; Structural repairs undertaken? [Y/N]              </t>
+          <t xml:space="preserve">1. Tightness inspections during maintenance? [Y/N]&lt;br&gt;2. Noise level recorded and trended? [Y/N]&lt;br&gt;3. Repair loose couplings as required? [Y/N]           </t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Failure-Finding                  </t>
         </is>
       </c>
     </row>
@@ -2400,37 +2400,37 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stator Failure            </t>
+          <t xml:space="preserve">Coupling Failure         </t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">House stator windings and core; provides stator magnetic field </t>
+          <t xml:space="preserve">Transfers torque from motor to driven equipment                           </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating           </t>
+          <t xml:space="preserve">BRD - Breakdown            </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue               </t>
+          <t xml:space="preserve">2.5 Breakage              </t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue damages stator insulation                            </t>
+          <t xml:space="preserve">Complete mechanical failure causing torque loss            </t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thermal cycle analysis? [Y/N]; Insulation integrity tests? [Y/N]; Maintenance and replacement scheduled? [Y/N]                  </t>
+          <t xml:space="preserve">1. Visual mechanical inspections? [Y/N]&lt;br&gt;2. Replacement of broken parts? [Y/N]&lt;br&gt;3. Monitoring for early warning signs? [Y/N]                         </t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive            </t>
+          <t xml:space="preserve">Failure-Finding, Preventive       </t>
         </is>
       </c>
     </row>
@@ -2452,41 +2452,49 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stator Failure            </t>
+          <t xml:space="preserve">Detector Failure         </t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">House stator windings and core; provides stator magnetic field </t>
+          <t xml:space="preserve">Detects operational parameters                                           </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation   </t>
+          <t xml:space="preserve">AIR - Abnormal instrument reading </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                  </t>
+          <t xml:space="preserve">3.4 Out of adjustment     </t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear of stator core and insulation                           </t>
+          <t xml:space="preserve">Faulty or drifted reading causing incorrect data            </t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear inspections performed? [Y/N]; Protective coatings discussed? [Y/N]; Maintenance performed on schedule? [Y/N]              </t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t xml:space="preserve">1. Regular calibration performed? [Y/N]&lt;br&gt;2. Faulty detectors replaced? [Y/N]&lt;br&gt;3. Diagnostic tests routinely conducted? [Y/N]                         </t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive, Failure-Finding       </t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2496,41 +2504,49 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stator Failure            </t>
+          <t xml:space="preserve">Detector Failure         </t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">House stator windings and core; provides stator magnetic field </t>
+          <t xml:space="preserve">Detects operational parameters                                           </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation   </t>
+          <t xml:space="preserve">SHH - Spurious high alarm level </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion             </t>
+          <t xml:space="preserve">3.3 Faulty signal/indication/alarm </t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion degrading core and insulation                      </t>
+          <t xml:space="preserve">False high alarms causing unnecessary shutdowns              </t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion inspections and coatings maintained? [Y/N]; Replacement actions taken if needed? [Y/N]                               </t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t xml:space="preserve">1. Alarm false activation incidents investigated? [Y/N]&lt;br&gt;2. Sensor health checked? [Y/N]&lt;br&gt;3. Corrective actions executed? [Y/N]                  </t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding                  </t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2540,41 +2556,49 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stator Failure            </t>
+          <t xml:space="preserve">Detector Failure         </t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">House stator windings and core; provides stator magnetic field </t>
+          <t xml:space="preserve">Detects operational parameters                                           </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration             </t>
+          <t xml:space="preserve">SLL - Spurious low alarm level </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness             </t>
+          <t xml:space="preserve">3.3 Faulty signal/indication/alarm </t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose laminations cause vibration                            </t>
+          <t xml:space="preserve">False low alarms causing inappropriate responses             </t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lamination tightening checked? [Y/N]; Vibration monitored? [Y/N]; Repairs done as needed? [Y/N]                                 </t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t xml:space="preserve">1. Sensor calibration periodically done? [Y/N]&lt;br&gt;2. Faulty detectors maintained and replaced? [Y/N]&lt;br&gt;3. Alarm thresholds verified? [Y/N]                </t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding                  </t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2584,41 +2608,49 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stator Failure            </t>
+          <t xml:space="preserve">Detector Failure         </t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">House stator windings and core; provides stator magnetic field </t>
+          <t xml:space="preserve">Detects operational parameters                                           </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                 </t>
+          <t xml:space="preserve">SPO - Spurious operation   </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness             </t>
+          <t xml:space="preserve">3.5 Software error          </t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise from loose stator components                           </t>
+          <t xml:space="preserve">Unintended operations due to software faults                </t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise level checked? [Y/N]; Structural fasteners inspected? [Y/N]; Repairs undertaken? [Y/N]                                    </t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t xml:space="preserve">1. Software updates applied regularly? [Y/N]&lt;br&gt;2. Monitoring of false operation reports? [Y/N]&lt;br&gt;3. Corrective maintenance performed promptly? [Y/N]       </t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding                  </t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2628,41 +2660,49 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stator Failure            </t>
+          <t xml:space="preserve">Enclosure Failure        </t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">House stator windings and core; provides stator magnetic field </t>
+          <t xml:space="preserve">Protects internal components from environment                            </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking              </t>
+          <t xml:space="preserve">1.4 Deformation             </t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sticking in winding or core causing failure during running   </t>
+          <t xml:space="preserve">Structural damage undermining protection                     </t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monitoring ongoing operation? [Y/N]; Detect and repair sticking? [Y/N]; Scheduled maintenance? [Y/N]                            </t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t xml:space="preserve">1. Visual inspection and structural tests? [Y/N]&lt;br&gt;2. Repairs performed on damage? [Y/N]&lt;br&gt;3. Protective coatings applied and maintained? [Y/N]             </t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive, Failure-Finding       </t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2672,41 +2712,49 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Windings Failure          </t>
+          <t xml:space="preserve">Enclosure Failure        </t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical power into magnetic field for rotor motion </t>
+          <t xml:space="preserve">Protects internal components from environment                            </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOO - No output            </t>
+          <t xml:space="preserve">BRD - Breakdown           </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.1 Short circuiting      </t>
+          <t xml:space="preserve">1.5 Looseness              </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Short circuit leading to no motor output                      </t>
+          <t xml:space="preserve">Structural failure causing enclosure malfunction             </t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electrical insulation tests conducted? [Y/N]; Winding continuity ensured? [Y/N]; Replacement as needed? [Y/N]                   </t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t xml:space="preserve">1. Structural fasteners checked? [Y/N]&lt;br&gt;2. Repairs on looseness executed? [Y/N]&lt;br&gt;3. Maintenance records updated? [Y/N]                                </t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2716,41 +2764,49 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Windings Failure          </t>
+          <t xml:space="preserve">Enclosure Failure        </t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical power into magnetic field for rotor motion </t>
+          <t xml:space="preserve">Protects internal components from environment                            </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOO - No output            </t>
+          <t xml:space="preserve">ELP - External leakage - process medium (*) </t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 Open circuit          </t>
+          <t xml:space="preserve">2.2 Corrosion           </t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open circuit breaking motor phase circuit                     </t>
+          <t xml:space="preserve">Corrosion causing external leakage                            </t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circuit continuity measured? [Y/N]; Repairs executed? [Y/N]; Replacement performed if needed? [Y/N]                             </t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t xml:space="preserve">1. Seal and gasket inspections? [Y/N]&lt;br&gt;2. Corrosion treated and monitored? [Y/N]&lt;br&gt;3. Seal replacement planned? [Y/N]                                  </t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2760,41 +2816,49 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Windings Failure          </t>
+          <t xml:space="preserve">Enclosure Failure        </t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical power into magnetic field for rotor motion </t>
+          <t xml:space="preserve">Protects internal components from environment                            </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation  </t>
+          <t xml:space="preserve">NOI - Noise               </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion             </t>
+          <t xml:space="preserve">2.6 Fatigue                </t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion damaging winding insulation                        </t>
+          <t xml:space="preserve">Noise caused by fatigue cracks in enclosure material          </t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion inspections and prevention? [Y/N]; Winding replaced if damaged? [Y/N]                                             </t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t xml:space="preserve">1. Auditory inspections? [Y/N]&lt;br&gt;2. Fatigue monitoring applied? [Y/N]&lt;br&gt;3. Repairs or replacements done timely? [Y/N]                                </t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding                  </t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2804,41 +2868,49 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Windings Failure          </t>
+          <t xml:space="preserve">Gearbox Failure          </t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical power into magnetic field for rotor motion </t>
+          <t xml:space="preserve">Transmits and modifies rotational power                                 </t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation  </t>
+          <t xml:space="preserve">VIB - Vibration            </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                  </t>
+          <t xml:space="preserve">2.4 Wear                   </t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear or mechanical damage to winding insulation              </t>
+          <t xml:space="preserve">Increased vibration from worn gear teeth                      </t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspection and preventive maintenance? [Y/N]; Timely winding replacement? [Y/N]                                               </t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t xml:space="preserve">1. Vibration analysis conducted regularly? [Y/N]&lt;br&gt;2. Gear lubrication status verified? [Y/N]&lt;br&gt;3. Worn gears replaced as needed? [Y/N]                 </t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive, Preventive             </t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2848,41 +2920,49 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Windings Failure          </t>
+          <t xml:space="preserve">Gearbox Failure          </t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical power into magnetic field for rotor motion </t>
+          <t xml:space="preserve">Transmits and modifies rotational power                                 </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating          </t>
+          <t xml:space="preserve">NOI - Noise                </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation           </t>
+          <t xml:space="preserve">1.5 Looseness              </t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thermal deformation causing insulation failure               </t>
+          <t xml:space="preserve">Noise generated by loose mounting or gears                  </t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thermal imaging and inspection? [Y/N]; Repair or replacement scheduled? [Y/N]                                                 </t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t xml:space="preserve">1. Visual and noise inspections? [Y/N]&lt;br&gt;2. Tightening of mounting bolts? [Y/N]&lt;br&gt;3. Maintenance on loose parts? [Y/N]                                   </t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding                  </t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2892,41 +2972,49 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Windings Failure          </t>
+          <t xml:space="preserve">Gearbox Failure          </t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical power into magnetic field for rotor motion </t>
+          <t xml:space="preserve">Transmits and modifies rotational power                                 </t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating          </t>
+          <t xml:space="preserve">PDE - Parameter deviation  </t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue               </t>
+          <t xml:space="preserve">2.4 Wear                   </t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue cracks or failures due to thermal cycling            </t>
+          <t xml:space="preserve">Parameter deviations due to gear wear                       </t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue analysis and thermal cycling monitoring? [Y/N]; Repairs scheduled based on diagnostics? [Y/N]                          </t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t xml:space="preserve">1. Control parameter monitoring? [Y/N]&lt;br&gt;2. Lubricant condition checked? [Y/N]&lt;br&gt;3. Timely maintenance performed? [Y/N]                               </t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive, Preventive             </t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2936,41 +3024,49 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Windings Failure          </t>
+          <t xml:space="preserve">Gearbox Failure          </t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical power into magnetic field for rotor motion </t>
+          <t xml:space="preserve">Transmits and modifies rotational power                                 </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration            </t>
+          <t xml:space="preserve">FWR - Failure while running </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness             </t>
+          <t xml:space="preserve">2.5 Breakage              </t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose connections causing vibration and failure              </t>
+          <t xml:space="preserve">Broken gears causing operational failure                     </t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanical and electrical tightness inspections? [Y/N]; Vibration analysis? [Y/N]; Repairs done? [Y/N]                          </t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t xml:space="preserve">1. Visual gear inspections scheduled? [Y/N]&lt;br&gt;2. Replacement of failed gears? [Y/N]&lt;br&gt;3. Condition monitoring used? [Y/N]                             </t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2980,41 +3076,49 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Windings Failure          </t>
+          <t xml:space="preserve">Heaters Failure          </t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical power into magnetic field for rotor motion </t>
+          <t xml:space="preserve">Provides anti-condensation or temperature control                       </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FWR - Failure while running</t>
+          <t xml:space="preserve">FTS - Failure to start on demand </t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking              </t>
+          <t xml:space="preserve">1.6 Sticking           </t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Winding sticking causing failure during operation            </t>
+          <t xml:space="preserve">Heater fails to energize                                     </t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monitoring of operating condition? [Y/N]; Corrective maintenance scheduled? [Y/N]; Replacement or repair as needed? [Y/N]       </t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t xml:space="preserve">1. Check heater power supply continuity? [Y/N]&lt;br&gt;2. Test heater circuit? [Y/N]&lt;br&gt;3. Schedule replacement of failed heaters? [Y/N]                      </t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding                  </t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3024,41 +3128,49 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brushes Failure           </t>
+          <t xml:space="preserve">Heaters Failure          </t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer electrical current to rotor via slip rings           </t>
+          <t xml:space="preserve">Provides anti-condensation or temperature control                       </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTS - Failure to start on demand </t>
+          <t xml:space="preserve">HTF - Heating failure      </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness           </t>
+          <t xml:space="preserve">1.5 Looseness              </t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brush looseness leading to failure to start                   </t>
+          <t xml:space="preserve">Loose connections causing heating failure                    </t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brushes checked for looseness? [Y/N]; Electrical continuity verified? [Y/N]; Brushes replaced as per schedule? [Y/N]             </t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+          <t xml:space="preserve">1. Inspect wiring and connection tightness? [Y/N]&lt;br&gt;2. Repair loose wiring? [Y/N]&lt;br&gt;3. Check insulation of heater wiring? [Y/N]                      </t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding                  </t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3068,41 +3180,49 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brushes Failure           </t>
+          <t xml:space="preserve">Heaters Failure          </t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer electrical current to rotor via slip rings           </t>
+          <t xml:space="preserve">Provides anti-condensation or temperature control                       </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTS - Failure to start on demand </t>
+          <t xml:space="preserve">PDE - Parameter deviation  </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 Open circuit        </t>
+          <t xml:space="preserve">3.4 Out of adjustment       </t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open circuit in brush causing failure to start                </t>
+          <t xml:space="preserve">Control failure causing abnormal heating                    </t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electrical path continuity checked? [Y/N]; Brush connection repaired? [Y/N]; Replacement when necessary? [Y/N]                  </t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t xml:space="preserve">1. Verify heater control settings? [Y/N]&lt;br&gt;2. Perform calibration checks? [Y/N]&lt;br&gt;3. Correct control parameters when needed? [Y/N]                      </t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3112,41 +3232,49 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brushes Failure           </t>
+          <t xml:space="preserve">Heaters Failure          </t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer electrical current to rotor via slip rings           </t>
+          <t xml:space="preserve">Provides anti-condensation or temperature control                       </t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                  </t>
+          <t xml:space="preserve">NOI - Noise                </t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                  </t>
+          <t xml:space="preserve">2.4 Wear                   </t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise due to brush wear or arcing                             </t>
+          <t xml:space="preserve">Noise caused by worn heater components                      </t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brush wear inspected and recorded? [Y/N]; Electrical contacts cleaned? [Y/N]; Brushes replaced on schedule? [Y/N]              </t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+          <t xml:space="preserve">1. Monitor noise levels? [Y/N]&lt;br&gt;2. Inspect heater components? [Y/N]&lt;br&gt;3. Perform repairs or replacements? [Y/N]                                        </t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding                  </t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3156,41 +3284,49 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brushes Failure           </t>
+          <t xml:space="preserve">Heaters Failure          </t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer electrical current to rotor via slip rings           </t>
+          <t xml:space="preserve">Provides anti-condensation or temperature control                       </t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                  </t>
+          <t xml:space="preserve">BRD - Breakdown            </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness             </t>
+          <t xml:space="preserve">2.5 Breakage              </t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose brush causing abnormal noise                            </t>
+          <t xml:space="preserve">Heater component failure causing loss of heating            </t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brush connection tightness checked? [Y/N]; Noise monitoring conducted? [Y/N]; Maintenance performed? [Y/N]                      </t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t xml:space="preserve">1. Visual inspection scheduled? [Y/N]&lt;br&gt;2. Repair or replace heaters as needed? [Y/N]&lt;br&gt;3. Monitor heater performance post maintenance? [Y/N]            </t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3200,41 +3336,49 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brushes Failure           </t>
+          <t xml:space="preserve">Junction Box Failure     </t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer electrical current to rotor via slip rings           </t>
+          <t xml:space="preserve">Houses electrical connections and protection                           </t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running   </t>
+          <t xml:space="preserve">FTS - Failure to start on demand </t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness             </t>
+          <t xml:space="preserve">4.3 No power/voltage     </t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brush sticking causing failure during operation               </t>
+          <t xml:space="preserve">Power loss preventing start                                 </t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operation condition monitored? [Y/N]; Brush integrity checked? [Y/N]; Replace brushes if worn? [Y/N]                            </t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t xml:space="preserve">1. Power supply continuity verified? [Y/N]&lt;br&gt;2. Check wiring and fuses? [Y/N]&lt;br&gt;3. Repairs done immediately? [Y/N]                                     </t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding                  </t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3244,41 +3388,49 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brushes Failure           </t>
+          <t xml:space="preserve">Junction Box Failure     </t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfer electrical current to rotor via slip rings           </t>
+          <t xml:space="preserve">Houses electrical connections and protection                           </t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation    </t>
+          <t xml:space="preserve">PTF - Power/signal transmission failure </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                  </t>
+          <t xml:space="preserve">4.2 Open circuit     </t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear or damage causing operational deviations                 </t>
+          <t xml:space="preserve">Open circuit causing loss of signal                         </t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brush wear inspections performed? [Y/N]; Parameter deviation monitoring? [Y/N]; Repairs or maintenance scheduled? [Y/N]         </t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+          <t xml:space="preserve">1. Inspect wiring and connectors? [Y/N]&lt;br&gt;2. Perform continuity tests? [Y/N]&lt;br&gt;3. Replace damaged wiring/connectors? [Y/N]                               </t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding                  </t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3288,41 +3440,49 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coupling Failure          </t>
+          <t xml:space="preserve">Junction Box Failure     </t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque between motor and driven equipment            </t>
+          <t xml:space="preserve">Houses electrical connections and protection                           </t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.3 Clearance / alignment failure </t>
+          <t xml:space="preserve">1.4 Deformation          </t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Misalignment causing vibration                             </t>
+          <t xml:space="preserve">Physical damage causing failure of junction box             </t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coupling alignment checked? [Y/N]; Vibration measurements performed? [Y/N]; Corrective actions implemented? [Y/N]              </t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+          <t xml:space="preserve">1. Visual inspection of box integrity? [Y/N]&lt;br&gt;2. Structural repairs performed? [Y/N]&lt;br&gt;3. Protective sealing maintained? [Y/N]                          </t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive, Failure-Finding       </t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3332,41 +3492,49 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coupling Failure          </t>
+          <t xml:space="preserve">Junction Box Failure     </t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque between motor and driven equipment            </t>
+          <t xml:space="preserve">Houses electrical connections and protection                           </t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
+          <t xml:space="preserve">NOI - Noise                </t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                  </t>
+          <t xml:space="preserve">1.5 Looseness             </t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear in coupling creating vibration                         </t>
+          <t xml:space="preserve">Loose connections causing noise                             </t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coupling surface inspected? [Y/N]; Wear replacement scheduled? [Y/N]; Vibration monitoring ongoing? [Y/N]                      </t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
+          <t xml:space="preserve">1. Connection tightness checked? [Y/N]&lt;br&gt;2. Tighten loose parts? [Y/N]&lt;br&gt;3. Noise level recorded and trended? [Y/N]                                    </t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding                  </t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3376,41 +3544,49 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coupling Failure          </t>
+          <t xml:space="preserve">Lubrication System Failure (*) </t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque between motor and driven equipment            </t>
+          <t xml:space="preserve">Supplies lubricant to bearings and moving parts                       </t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
+          <t xml:space="preserve">LOO - Low oil pressure      </t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness             </t>
+          <t xml:space="preserve">1.1 Leakage               </t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Looseness in coupling causing abnormal vibration           </t>
+          <t xml:space="preserve">Lubricant pressure loss causing equipment degradation       </t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tightness inspections? [Y/N]; Coupling fasteners checked? [Y/N]; Repair or tighten as needed? [Y/N]                            </t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
+          <t xml:space="preserve">1. Oil pressure monitored continuously? [Y/N]&lt;br&gt;2. Leak detection conducted regularly? [Y/N]&lt;br&gt;3. Lubricant levels maintained? [Y/N]                    </t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive, Failure-Finding        </t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3420,41 +3596,49 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coupling Failure          </t>
+          <t xml:space="preserve">Lubrication System Failure (*) </t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque between motor and driven equipment            </t>
+          <t xml:space="preserve">Supplies lubricant to bearings and moving parts                       </t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running   </t>
+          <t xml:space="preserve">ELU - External leakage - utility medium </t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage              </t>
+          <t xml:space="preserve">2.4 Wear               </t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coupling breakage causing failure while running            </t>
+          <t xml:space="preserve">Wear of lubrication parts causing leaks                     </t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visual inspections? [Y/N]; Load monitoring done? [Y/N]; Coupling replaced if broken? [Y/N]                                    </t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
+          <t xml:space="preserve">1. Visual inspection for leaks? [Y/N]&lt;br&gt;2. Seal conditions monitored? [Y/N]&lt;br&gt;3. Repair or replace leaking components? [Y/N]                         </t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3464,41 +3648,49 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coupling Failure          </t>
+          <t xml:space="preserve">Lubrication System Failure (*) </t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque between motor and driven equipment            </t>
+          <t xml:space="preserve">Supplies lubricant to bearings and moving parts                       </t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running   </t>
+          <t xml:space="preserve">PDE - Parameter deviation   </t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking              </t>
+          <t xml:space="preserve">5.3 Contamination        </t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coupling stuck causing operational failure                 </t>
+          <t xml:space="preserve">Contamination reducing lubricant effectiveness              </t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operation condition monitored? [Y/N]; Lubrication inspected? [Y/N]; Maintenance actions taken promptly? [Y/N]                 </t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
+          <t xml:space="preserve">1. Oil analysis performed regularly? [Y/N]&lt;br&gt;2. Filters cleaned/replaced? [Y/N]&lt;br&gt;3. Contaminated oil replaced? [Y/N]                              </t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive, Preventive             </t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3508,41 +3700,49 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coupling Failure          </t>
+          <t xml:space="preserve">Lubrication System Failure (*) </t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque between motor and driven equipment            </t>
+          <t xml:space="preserve">Supplies lubricant to bearings and moving parts                       </t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">STU - Stuck                  </t>
+          <t xml:space="preserve">FWR - Failure while running </t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking              </t>
+          <t xml:space="preserve">2.6 Fatigue              </t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coupling seizure causing failure                            </t>
+          <t xml:space="preserve">Fatigue damage arising from loss of lubrication              </t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operational tests? [Y/N]; Lubrication system monitored? [Y/N]; Repairs performed as necessary? [Y/N]                           </t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+          <t xml:space="preserve">1. Condition monitoring conducted? [Y/N]&lt;br&gt;2. Lubrication schedule strictly followed? [Y/N]&lt;br&gt;3. Repairs conducted promptly? [Y/N]                   </t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive                       </t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3552,41 +3752,49 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coupling Failure          </t>
+          <t xml:space="preserve">Shaft Failure (*)          </t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque between motor and driven equipment            </t>
+          <t xml:space="preserve">Transmits torque from rotor to driven equipment                        </t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                  </t>
+          <t xml:space="preserve">VIB - Vibration            </t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness             </t>
+          <t xml:space="preserve">2.6 Fatigue              </t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise caused by looseness or misalignment                  </t>
+          <t xml:space="preserve">Fatigue cracks causing increased vibration                  </t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise analysis performed? [Y/N]; Coupling fastener tightness verified? [Y/N]; Repairs performed? [Y/N]                         </t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
+          <t xml:space="preserve">1. Vibration analysis in operation? [Y/N]&lt;br&gt;2. Shaft inspections during maintenance? [Y/N]&lt;br&gt;3. Replacement before failure? [Y/N]                   </t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive, Preventive             </t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3596,41 +3804,49 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooling System Failure    </t>
+          <t xml:space="preserve">Shaft Failure (*)          </t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removes heat to maintain motor temperature                     </t>
+          <t xml:space="preserve">Transmits torque from rotor to driven equipment                        </t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation    </t>
+          <t xml:space="preserve">VIB - Vibration            </t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination          </t>
+          <t xml:space="preserve">1.3 Clearance / alignment failure </t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fluid contamination reducing cooling efficiency            </t>
+          <t xml:space="preserve">Shaft misalignment causing vibration                      </t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooling system flush scheduled? [Y/N]; Fluid quality monitored regularly? [Y/N]; Preventive cleaning performed? [Y/N]          </t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
+          <t xml:space="preserve">1. Shaft alignment measured? [Y/N]&lt;br&gt;2. Coupling alignment verified? [Y/N]&lt;br&gt;3. Maintenance actions on misalignment? [Y/N]                          </t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive                       </t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3640,41 +3856,49 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooling System Failure    </t>
+          <t xml:space="preserve">Shaft Failure (*)          </t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removes heat to maintain motor temperature                     </t>
+          <t xml:space="preserve">Transmits torque from rotor to driven equipment                        </t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation    </t>
+          <t xml:space="preserve">FWR - Failure while running </t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
+          <t xml:space="preserve">2.5 Breakage             </t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fouling or external blockage reducing cooling performance </t>
+          <t xml:space="preserve">Shaft breakage or fracture causing failure                  </t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exterior cleaning and inspection? [Y/N]; Flow restrictions removed? [Y/N]; Regular maintenance adhered to? [Y/N]               </t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+          <t xml:space="preserve">1. Visual inspection pre-operation? [Y/N]&lt;br&gt;2. Vibration monitoring? [Y/N]&lt;br&gt;3. Immediate repair or replacement? [Y/N]                               </t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3684,41 +3908,49 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooling System Failure    </t>
+          <t xml:space="preserve">Seal Failure (*)           </t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removes heat to maintain motor temperature                     </t>
+          <t xml:space="preserve">Prevents lubricant and cooling fluid leakage                           </t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELU - External leakage utility medium </t>
+          <t xml:space="preserve">ELU - External leakage - utility medium </t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                </t>
+          <t xml:space="preserve">2.4 Wear               </t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear causing external leaks                                </t>
+          <t xml:space="preserve">Seal wear causing fluid leaks                               </t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leak checks performed? [Y/N]; Seal replacements timely? [Y/N]; Leak repairs completed? [Y/N]                                 </t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+          <t xml:space="preserve">1. Seal integrity checked? [Y/N]&lt;br&gt;2. Leak monitoring established? [Y/N]&lt;br&gt;3. Replacement of worn seals? [Y/N]                                       </t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3728,41 +3960,49 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooling System Failure    </t>
+          <t xml:space="preserve">Seal Failure (*)           </t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removes heat to maintain motor temperature                     </t>
+          <t xml:space="preserve">Prevents lubricant and cooling fluid leakage                           </t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELU - External leakage utility medium </t>
+          <t xml:space="preserve">PDE - Parameter deviation  </t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue             </t>
+          <t xml:space="preserve">1.4 Deformation          </t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue cracks causing leaks                               </t>
+          <t xml:space="preserve">Seal deformation leading to packing or leakage              </t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ultrasonic leak detection done? [Y/N]; Repairs on cracked pipes? [Y/N]; Prevention measures implemented? [Y/N]                 </t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+          <t xml:space="preserve">1. Visual inspection for deformations? [Y/N]&lt;br&gt;2. Structural repairs performed? [Y/N]&lt;br&gt;3. Preventive maintenance scheduled? [Y/N]                  </t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive                       </t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3772,41 +4012,49 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooling System Failure    </t>
+          <t xml:space="preserve">Seal Failure (*)           </t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removes heat to maintain motor temperature                     </t>
+          <t xml:space="preserve">Prevents lubricant and cooling fluid leakage                           </t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCP - Leakage in closed position </t>
+          <t xml:space="preserve">SPO - Spurious operation   </t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation          </t>
+          <t xml:space="preserve">2.2 Corrosion            </t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal or gasket deformation causing leaks                  </t>
+          <t xml:space="preserve">Corrosion damaging seal surfaces                            </t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal integrity tested? [Y/N]; Gasket replacements managed? [Y/N]; Leak tests completed? [Y/N]                                </t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
+          <t xml:space="preserve">1. Corrosion monitoring? [Y/N]&lt;br&gt;2. Seal replacement if corroded? [Y/N]&lt;br&gt;3. Protective coatings applied? [Y/N]                                   </t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3816,41 +4064,49 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooling System Failure    </t>
+          <t xml:space="preserve">Power Supply Failure (*)    </t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removes heat to maintain motor temperature                     </t>
+          <t xml:space="preserve">Supplies electrical power to motor control and protection systems    </t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCP - Leakage in closed position </t>
+          <t xml:space="preserve">FTS - Failure to start on demand </t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                 </t>
+          <t xml:space="preserve">4.3 No power/voltage    </t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear on sealing surfaces causing leakage                  </t>
+          <t xml:space="preserve">Power failure preventing motor startup                    </t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal wear inspection? [Y/N]; Seal replaced on condition? [Y/N]; Leak monitoring ongoing? [Y/N]                               </t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+          <t xml:space="preserve">1. Power supply tested regularly? [Y/N]&lt;br&gt;2. Wiring and connections inspected? [Y/N]&lt;br&gt;3. Repairs completed as needed? [Y/N]                       </t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3860,41 +4116,49 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooling System Failure    </t>
+          <t xml:space="preserve">Power Supply Failure (*)    </t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removes heat to maintain motor temperature                     </t>
+          <t xml:space="preserve">Supplies electrical power to motor control and protection systems    </t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating            </t>
+          <t xml:space="preserve">PTF - Power/signal transmission failure </t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination          </t>
+          <t xml:space="preserve">4.2 Open circuit     </t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contamination causing reduced cooling                      </t>
+          <t xml:space="preserve">Open circuit leading to signal loss                        </t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fluid sampling and cleaning? [Y/N]; Flow rates verified? [Y/N]; Fouling prevention? [Y/N]                                    </t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+          <t xml:space="preserve">1. Electrical continuity checked? [Y/N]&lt;br&gt;2. Power supply components replaced when faulty? [Y/N]&lt;br&gt;3. Monitoring for power anomalies? [Y/N]          </t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding                  </t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3904,41 +4168,49 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooling System Failure    </t>
+          <t xml:space="preserve">Insulation System Failure (*) </t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removes heat to maintain motor temperature                     </t>
+          <t xml:space="preserve">Provides electrical insulation to prevent shorts and leakage         </t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating            </t>
+          <t xml:space="preserve">NOO - No output            </t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation           </t>
+          <t xml:space="preserve">4.1 Short circuiting       </t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Structural deformation affecting flow or heat removal     </t>
+          <t xml:space="preserve">Short circuit causing motor failure                        </t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visual inspection of components? [Y/N]; Repairs or replacements completed? [Y/N]; Temperature monitored? [Y/N]                 </t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+          <t xml:space="preserve">1. Insulation resistance tested? [Y/N]&lt;br&gt;2. Visual inspections for damage? [Y/N]&lt;br&gt;3. Repairs or rewinding performed promptly? [Y/N]                 </t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding, Redesign         </t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3948,41 +4220,49 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooling System Failure    </t>
+          <t xml:space="preserve">Insulation System Failure (*) </t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removes heat to maintain motor temperature                     </t>
+          <t xml:space="preserve">Provides electrical insulation to prevent shorts and leakage         </t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation    </t>
+          <t xml:space="preserve">OHE - Overheating          </t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion             </t>
+          <t xml:space="preserve">2.7 Overheating           </t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion reducing cooling performance                     </t>
+          <t xml:space="preserve">Overheating causing insulation breakdown                   </t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion detection and mitigation? [Y/N]; Protective coatings applied? [Y/N]                                              </t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+          <t xml:space="preserve">1. Temperature sensors monitored? [Y/N]&lt;br&gt;2. Cooling system functioning? [Y/N]&lt;br&gt;3. Thermal protection maintained? [Y/N]                            </t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive, Preventive             </t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3992,41 +4272,49 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooling System Failure    </t>
+          <t xml:space="preserve">Insulation System Failure (*) </t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removes heat to maintain motor temperature                     </t>
+          <t xml:space="preserve">Provides electrical insulation to prevent shorts and leakage         </t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running  </t>
+          <t xml:space="preserve">PDE - Parameter deviation  </t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.1 Leakage                </t>
+          <t xml:space="preserve">3.4 Out of adjustment      </t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leaks causing cooling failure                              </t>
+          <t xml:space="preserve">Parameter deviation due to insulation degradation          </t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Continuous leak monitoring? [Y/N]; Prompt leak repairs? [Y/N]; Seal and gasket replacements? [Y/N]                            </t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+          <t xml:space="preserve">1. Electrical parameters monitored? [Y/N]&lt;br&gt;2. Preventive maintenance scheduled? [Y/N]&lt;br&gt;3. Corrective actions performed? [Y/N]                     </t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4036,41 +4324,49 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooling System Failure    </t>
+          <t xml:space="preserve">Terminal Connections Failure (*) </t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removes heat to maintain motor temperature                     </t>
+          <t xml:space="preserve">Electrical connection points ensuring integrity of power delivery    </t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running  </t>
+          <t xml:space="preserve">FTS - Failure to start on demand </t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination          </t>
+          <t xml:space="preserve">4.2 Open circuit        </t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fouling causing cooling failure                            </t>
+          <t xml:space="preserve">Open circuit causing system start failure                 </t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">System cleaning performed? [Y/N]; Fluid quality monitored? [Y/N]; Maintenance schedule followed? [Y/N]                        </t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
+          <t xml:space="preserve">1. Terminal connections checked? [Y/N]&lt;br&gt;2. Tightening of connectors? [Y/N]&lt;br&gt;3. Repair or replacement of faulty terminals? [Y/N]                   </t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding                  </t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4080,41 +4376,49 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enclosure Failure         </t>
+          <t xml:space="preserve">Terminal Connections Failure (*) </t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houses motor components and protects from environment         </t>
+          <t xml:space="preserve">Electrical connection points ensuring integrity of power delivery    </t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency  </t>
+          <t xml:space="preserve">PTF - Power/signal transmission failure </t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation           </t>
+          <t xml:space="preserve">4.5 Earth/isolation fault </t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Buckling or damage causing enclosure failure              </t>
+          <t xml:space="preserve">Earth fault causing operational failure                   </t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regular inspections? [Y/N]; Structural repairs made? [Y/N]; Corrosion protection maintained? [Y/N]                            </t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+          <t xml:space="preserve">1. Insulation tests performed? [Y/N]&lt;br&gt;2. Connection integrity monitored? [Y/N]&lt;br&gt;3. Corrective maintenance done? [Y/N]                              </t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding                  </t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4124,965 +4428,49 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
+          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enclosure Failure         </t>
+          <t xml:space="preserve">Terminal Connections Failure (*) </t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houses motor components and protects from environment         </t>
+          <t xml:space="preserve">Electrical connection points ensuring integrity of power delivery    </t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency  </t>
+          <t xml:space="preserve">NOI - Noise                </t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion             </t>
+          <t xml:space="preserve">1.5 Looseness             </t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion weakening enclosure                             </t>
+          <t xml:space="preserve">Loose terminals causing noise                             </t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion inspections? [Y/N]; Protective coatings applied? [Y/N]; Replacements installed if needed? [Y/N]                     </t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Motor, Electric </t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enclosure Failure         </t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Houses motor components and protects from environment         </t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ELU - External leakage utility medium </t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.4 Wear                </t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wear causing protective barrier leaks                      </t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Seals inspected for wear? [Y/N]; Repairs and replacements done? [Y/N]; Leakage monitored regularly? [Y/N]                    </t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Motor, Electric </t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enclosure Failure         </t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Houses motor components and protects from environment         </t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ELU - External leakage utility medium </t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.6 Fatigue             </t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fatigue induced cracks resulting in noise                </t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Structural fatigue inspections? [Y/N]; Crack repairs and reinforcements? [Y/N]; Noise monitoring? [Y/N]                       </t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Motor, Electric </t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enclosure Failure         </t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Houses motor components and protects from environment         </t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NOI - Noise                  </t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.5 Looseness             </t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Loose enclosure parts causing noise                       </t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fastener tightness checks? [Y/N]; Noise level monitored? [Y/N]; Repairs performed? [Y/N]                                      </t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Motor, Electric </t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enclosure Failure         </t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Houses motor components and protects from environment         </t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NOI - Noise                  </t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.6 Fatigue               </t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fatigue cracks causing noise                              </t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fatigue evaluation and repair? [Y/N]; Noise trend analysis? [Y/N]; Repairs scheduled? [Y/N]                                  </t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Motor, Electric </t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enclosure Failure         </t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Houses motor components and protects from environment         </t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.4 Deformation           </t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vibration due to structural deformation                  </t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Structural inspections? [Y/N]; Repairs implemented? [Y/N]; Vibration checked after repair? [Y/N]                             </t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Motor, Electric </t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enclosure Failure         </t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Houses motor components and protects from environment         </t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.4 Wear                  </t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wear causing enclosure vibrations                        </t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wear inspections? [Y/N]; Maintenance actions scheduled? [Y/N]; Vibration measurements taken? [Y/N]                           </t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Motor, Electric </t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gearbox Failure (*)       </t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transmit torque via gears inside coupling                       </t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.4 Wear                  </t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gear tooth wear causing vibration                         </t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gearbox oil sampled and analyzed? [Y/N]; Gear teeth inspected? [Y/N]; Replacement scheduled? [Y/N]                           </t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Motor, Electric </t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gearbox Failure (*)       </t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transmit torque via gears inside coupling                       </t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.3 Clearance / alignment failure </t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Misalignment causing gearbox vibration                  </t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gear alignment verification? [Y/N]; Coupling adjustments made? [Y/N]; Wear monitored? [Y/N]                                </t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Motor, Electric </t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gearbox Failure (*)       </t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transmit torque via gears inside coupling                       </t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NOI - Noise                  </t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.5 Breakage              </t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gear tooth breakage causing noise                         </t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Inspection and replacement of broken gears? [Y/N]; Noise monitoring? [Y/N]; Preventive maintenance? [Y/N]                    </t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Motor, Electric </t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gearbox Failure (*)       </t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transmit torque via gears inside coupling                       </t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LOO - Low output (*)          </t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5.1 Blockage              </t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Blockage causing reduced output                           </t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gearbox flow path cleaned? [Y/N]; Blockages removed? [Y/N]; Lubricant replaced? [Y/N]                                       </t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Motor, Electric </t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gearbox Failure (*)       </t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transmit torque via gears inside coupling                       </t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FWR - Failure while running   </t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.6 Sticking              </t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gearbox seizure causing failure while running            </t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lubrication condition monitored? [Y/N]; Seizure inspections? [Y/N]; Scheduled overhauls? [Y/N]                                </t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Motor, Electric </t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heaters Failure (*)       </t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide heat to prevent moisture and condensation in motor     </t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FTS - Failure to start on demand </t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.1 Control failure     </t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Control failure causing heater not to start              </t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heater control system tested? [Y/N]; Electrical wiring checked? [Y/N]; Replacement or repair performed? [Y/N]                 </t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Motor, Electric </t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heaters Failure (*)       </t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide heat to prevent moisture and condensation in motor     </t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FTS - Failure to start on demand </t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 Open circuit         </t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Open circuit preventing heater start                      </t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Electrical continuity verified? [Y/N]; Heater wiring continuity checked? [Y/N]; Repairs conducted as required? [Y/N]         </t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Motor, Electric </t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heaters Failure (*)       </t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide heat to prevent moisture and condensation in motor     </t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OHE - Overheating            </t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.4 Deformation           </t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heater element deformation causing overheating            </t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Visual inspections conducted? [Y/N]; Temperature regulation verified? [Y/N]; Preventive maintenance scheduled? [Y/N]         </t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Motor, Electric </t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heaters Failure (*)       </t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide heat to prevent moisture and condensation in motor     </t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OHE - Overheating            </t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.7 Electrical failure    </t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Electrical fault causing overheating                       </t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Electrical testing of heater? [Y/N]; Insulation resistance checked? [Y/N]; Replacement or repair performed? [Y/N]            </t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Motor, Electric </t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heaters Failure (*)       </t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provide heat to prevent moisture and condensation in motor     </t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PDE - Parameter deviation    </t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Environmental effects leading to failure                </t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Environmental condition monitored? [Y/N]; Protective measures applied? [Y/N]; Heater replacement scheduled? [Y/N]            </t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Motor, Electric </t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Junction Box Failure      </t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">House wiring connections and terminal blocks                   </t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ELU - External leakage utility medium </t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.4 Wear               </t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Seal or gasket wear causing leakage                      </t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Junction box seals inspected? [Y/N]; Leak repairs done? [Y/N]; Seal replaced regularly? [Y/N]                                 </t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Motor, Electric </t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Junction Box Failure      </t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">House wiring connections and terminal blocks                   </t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ELU - External leakage utility medium </t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.6 Fatigue            </t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fatigue cracking causing leaks                            </t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Structural inspections conducted? [Y/N]; Leak repair actions performed? [Y/N]; Preventive measures applied? [Y/N]             </t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Motor, Electric </t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Junction Box Failure      </t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">House wiring connections and terminal blocks                   </t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CSF - Control / signal failure </t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.2 Open circuit        </t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Electrical break causing signal failure                  </t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wiring continuity checked? [Y/N]; Repairs or replacements done? [Y/N]; Electrical tests performed? [Y/N]                      </t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Motor, Electric </t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Junction Box Failure      </t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">House wiring connections and terminal blocks                   </t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NOI - Noise                  </t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.5 Looseness             </t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Loose connection causing noise                            </t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Terminal tightness inspected? [Y/N]; Noise monitoring performed? [Y/N]; Repair conducted? [Y/N]                               </t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Motor, Electric </t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy </t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Junction Box Failure      </t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">House wiring connections and terminal blocks                   </t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.4 Deformation           </t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Structural deformation causing vibration                  </t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Structural integrity inspections? [Y/N]; Corrective maintenance? [Y/N]; Vibration trend monitoring? [Y/N]                     </t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
+          <t xml:space="preserve">1. Noise level monitored? [Y/N]&lt;br&gt;2. Connectors checked and tightened? [Y/N]&lt;br&gt;3. Immediate repair on noise detection? [Y/N]                          </t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding                  </t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/outputs/EMS upgrade output.xlsx
+++ b/outputs/EMS upgrade output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,1535 +471,1535 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure       </t>
+          <t xml:space="preserve">Impeller Failure           </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on the non-drive end </t>
+          <t xml:space="preserve">Converts mechanical energy into fluid kinetic energy             </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
+          <t xml:space="preserve">VIB - Vibration                  </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                         </t>
+          <t xml:space="preserve">2.4 Wear                       </t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Increased vibration and eventual bearing damage               </t>
+          <t xml:space="preserve">Excessive vibration causing noise and potential damage        </t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Vibration analysis performed regularly? [Y/N]&lt;br&gt;2. Bearing condition monitored visually or via sensors? [Y/N]&lt;br&gt;3. Lubrication levels maintained as per schedule? [Y/N] </t>
+          <t xml:space="preserve">Perform impeller surface inspection? [Y/N]; Monitor vibration levels? [Y/N]; Dynamic balance correction? [Y/N]                                                                   </t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive, Preventive             </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure       </t>
+          <t xml:space="preserve">Impeller Failure           </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on the non-drive end </t>
+          <t xml:space="preserve">Converts mechanical energy into fluid kinetic energy             </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
+          <t xml:space="preserve">VIB - Vibration                  </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.3 Clearance / alignment failure </t>
+          <t xml:space="preserve">2.3 Erosion                    </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Excessive vibration causing premature bearing failure          </t>
+          <t xml:space="preserve">Material loss due to erosion impacting impeller efficiency    </t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Shaft alignment checked periodically? [Y/N]&lt;br&gt;2. Coupling alignment verified during maintenance? [Y/N]&lt;br&gt;3. Corrective alignment performed promptly? [Y/N]        </t>
+          <t xml:space="preserve">Monitor fluid contaminants? [Y/N]; Inspect impeller surfaces? [Y/N]; Schedule wear ring replacement? [Y/N]                                                                       </t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive                       </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure       </t>
+          <t xml:space="preserve">Impeller Failure           </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on the non-drive end </t>
+          <t xml:space="preserve">Converts mechanical energy into fluid kinetic energy             </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
+          <t xml:space="preserve">VIB - Vibration                  </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                      </t>
+          <t xml:space="preserve">2.6 Fatigue                    </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue cracks leading to bearing spalling or failure         </t>
+          <t xml:space="preserve">Cracks from cyclic stresses leading to failure                </t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Load and vibration monitoring conducted? [Y/N]&lt;br&gt;2. Operating within design load limits? [Y/N]&lt;br&gt;3. Bearings replaced at end of fatigue life? [Y/N]               </t>
+          <t xml:space="preserve">Perform fatigue analysis? [Y/N]; Carry out NDT inspections? [Y/N]; Limit operational overloads? [Y/N]                                                                             </t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive, Preventive             </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure       </t>
+          <t xml:space="preserve">Impeller Failure           </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on the non-drive end </t>
+          <t xml:space="preserve">Converts mechanical energy into fluid kinetic energy             </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                  </t>
+          <t xml:space="preserve">PDE - Parameter deviation        </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                         </t>
+          <t xml:space="preserve">2.2 Corrosion                  </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abnormal noise indicating bearing wear                       </t>
+          <t xml:space="preserve">Chemical degradation of impeller material                      </t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Audible inspections carried out? [Y/N]&lt;br&gt;2. Noise level recorded and trended? [Y/N]&lt;br&gt;3. Corrective action on abnormal noise? [Y/N]                           </t>
+          <t xml:space="preserve">Conduct corrosion monitoring? [Y/N]; Apply protective surface coatings? [Y/N]; Analyze process fluid chemistry? [Y/N]                                                           </t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure       </t>
+          <t xml:space="preserve">Impeller Failure           </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on the non-drive end </t>
+          <t xml:space="preserve">Converts mechanical energy into fluid kinetic energy             </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                  </t>
+          <t xml:space="preserve">PDE - Parameter deviation        </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness                   </t>
+          <t xml:space="preserve">1.4 Deformation               </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose bearing causing noise and movement                      </t>
+          <t xml:space="preserve">Impeller distortion affecting hydraulic performance           </t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Bearing housing tightness verified during maintenance? [Y/N]&lt;br&gt;2. Bearing mounting inspected? [Y/N]&lt;br&gt;3. Torque of bolts checked and corrected? [Y/N]        </t>
+          <t xml:space="preserve">Inspect for mechanical distortion? [Y/N]; Carry out stress analysis? [Y/N]; Control operational parameters? [Y/N]                                                               </t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding                  </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure       </t>
+          <t xml:space="preserve">Impeller Failure           </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on the non-drive end </t>
+          <t xml:space="preserve">Converts mechanical energy into fluid kinetic energy             </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                  </t>
+          <t xml:space="preserve">PDE - Parameter deviation        </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
+          <t xml:space="preserve">5.2 Contamination             </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise caused by external impacts or contamination           </t>
+          <t xml:space="preserve">Contaminants reducing hydraulic efficiency                     </t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Visual inspection for foreign objects? [Y/N]&lt;br&gt;2. Environmental sealing maintained? [Y/N]&lt;br&gt;3. Protection measures implemented? [Y/N]                      </t>
+          <t xml:space="preserve">Conduct fluid contamination analysis? [Y/N]; Maintain filtration system? [Y/N]; Flush system regularly? [Y/N]                                                                    </t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+          <t xml:space="preserve">Failure-Finding       </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure       </t>
+          <t xml:space="preserve">Impeller Failure           </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on the non-drive end </t>
+          <t xml:space="preserve">Converts mechanical energy into fluid kinetic energy             </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELU - External leakage - utility medium </t>
+          <t xml:space="preserve">NOI - Noise                     </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion               </t>
+          <t xml:space="preserve">2.5 Breakage                  </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion leading to lubricant leak                           </t>
+          <t xml:space="preserve">Noise generated by cracks or fragments                         </t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Seal and housing inspected for corrosion? [Y/N]&lt;br&gt;2. Corrosion protective treatments applied? [Y/N]&lt;br&gt;3. Repairs done immediately on leak detection? [Y/N]    </t>
+          <t xml:space="preserve">Visual and NDT inspections? [Y/N]; Replace damaged components? [Y/N]; Monitor noise levels? [Y/N]                                                                                </t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+          <t xml:space="preserve">Corrective            </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure       </t>
+          <t xml:space="preserve">Impeller Failure           </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on the non-drive end </t>
+          <t xml:space="preserve">Converts mechanical energy into fluid kinetic energy             </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELU - External leakage - utility medium </t>
+          <t xml:space="preserve">NOI - Noise                     </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                    </t>
+          <t xml:space="preserve">2.1 Cavitation                </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear causing seal or housing leakage                         </t>
+          <t xml:space="preserve">Noise from vapor bubble collapse                               </t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Seal and housing condition monitored? [Y/N]&lt;br&gt;2. Replacement or repair of worn parts? [Y/N]&lt;br&gt;3. Routine lubrication system checks? [Y/N]                  </t>
+          <t xml:space="preserve">Monitor NPSH and eliminate cavitation causes? [Y/N]; Inspect impeller for cavitation damage? [Y/N]; Adjust suction conditions? [Y/N]                                          </t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+          <t xml:space="preserve">Failure-Finding       </t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure       </t>
+          <t xml:space="preserve">Impeller Failure           </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on the non-drive end </t>
+          <t xml:space="preserve">Converts mechanical energy into fluid kinetic energy             </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating            </t>
+          <t xml:space="preserve">LOO - Leak of oil               </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation               </t>
+          <t xml:space="preserve">1.4 Deformation              </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing housing deformation causing heat build-up           </t>
+          <t xml:space="preserve">Leakage from seal or component deformation                    </t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Visual inspection of bearing housing? [Y/N]&lt;br&gt;2. Structural integrity checks performed? [Y/N]&lt;br&gt;3. Alignment corrections made if required? [Y/N]             </t>
+          <t xml:space="preserve">Inspect seal surfaces? [Y/N]; Repair or replace seals? [Y/N]; Monitor leakage points? [Y/N]                                                                                      </t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive                       </t>
+          <t xml:space="preserve">Corrective            </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure       </t>
+          <t xml:space="preserve">Impeller Failure           </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on the non-drive end </t>
+          <t xml:space="preserve">Converts mechanical energy into fluid kinetic energy             </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating            </t>
+          <t xml:space="preserve">LOO - Leak of oil               </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                  </t>
+          <t xml:space="preserve">2.4 Wear                    </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overheating caused by fatigue in bearing components          </t>
+          <t xml:space="preserve">Wear causing leakage through sealing surfaces                </t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Temperature sensors regularly checked? [Y/N]&lt;br&gt;2. Vibration monitored for fatigue? [Y/N]&lt;br&gt;3. Bearings replaced on signs of overload? [Y/N]                  </t>
+          <t xml:space="preserve">Scheduled wear inspections? [Y/N]; Seal replacements as needed? [Y/N]; Leakage monitoring? [Y/N]                                                                               </t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive, Preventive             </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDE Bearing Failure       </t>
+          <t xml:space="preserve">Impeller Failure           </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on the non-drive end </t>
+          <t xml:space="preserve">Converts mechanical energy into fluid kinetic energy             </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running  </t>
+          <t xml:space="preserve">OHE - Overheating               </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage                 </t>
+          <t xml:space="preserve">2.4 Wear                    </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing rolling element or cage failure                      </t>
+          <t xml:space="preserve">Overheating due to friction and wear                          </t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1. Visual and vibration inspections regularly scheduled? [Y/N]&lt;br&gt;2. Early replacement of damaged bearings? [Y/N]&lt;br&gt;3. Lubrication monitored and maintained? [Y/N]</t>
+          <t xml:space="preserve">Temperature monitoring? [Y/N]; Lubrication system inspections? [Y/N]; Cooling system maintenance? [Y/N]                                                                         </t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure       </t>
+          <t xml:space="preserve">Impeller Failure           </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on drive end         </t>
+          <t xml:space="preserve">Converts mechanical energy into fluid kinetic energy             </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
+          <t xml:space="preserve">OHE - Overheating               </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                       </t>
+          <t xml:space="preserve">1.6 Sticking                </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Increased vibration due to wear                              </t>
+          <t xml:space="preserve">Overheating due to component seizure                         </t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Vibration monitoring and analysis scheduled? [Y/N]&lt;br&gt;2. Lubrication intervals adhered to? [Y/N]&lt;br&gt;3. Maintenance on bearing condition conducted? [Y/N]       </t>
+          <t xml:space="preserve">Monitor component temperature? [Y/N]; Lubrication inspection? [Y/N]; Remove stuck conditions? [Y/N]                                                                             </t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive, Preventive             </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure       </t>
+          <t xml:space="preserve">Impeller Failure           </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on drive end         </t>
+          <t xml:space="preserve">Converts mechanical energy into fluid kinetic energy             </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
+          <t xml:space="preserve">FWR - Failure while running      </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.3 Clearance / alignment failure </t>
+          <t xml:space="preserve">2.3 Erosion                 </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Misalignment causing vibration and premature failure       </t>
+          <t xml:space="preserve">Material loss leading to failure                              </t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Shaft and coupling alignment checked? [Y/N]&lt;br&gt;2. Realignment maintenance carried out timely? [Y/N]&lt;br&gt;3. Adjustment recorded and monitored? [Y/N]             </t>
+          <t xml:space="preserve">Monitor erosion rates? [Y/N]; Inspect impeller regularly? [Y/N]; Flush system to remove particles? [Y/N]                                                                        </t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive                       </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure       </t>
+          <t xml:space="preserve">Impeller Failure           </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on drive end         </t>
+          <t xml:space="preserve">Converts mechanical energy into fluid kinetic energy             </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
+          <t xml:space="preserve">FWR - Failure while running      </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                  </t>
+          <t xml:space="preserve">2.4 Wear                    </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue cracks causing bearing damage                      </t>
+          <t xml:space="preserve">Progressive wear causing failure                              </t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Fatigue condition monitoring? [Y/N]&lt;br&gt;2. Replacing bearings before failure? [Y/N]&lt;br&gt;3. Vibration data trended and analyzed? [Y/N]                           </t>
+          <t xml:space="preserve">Schedule preventive maintenance? [Y/N]; Vibration monitoring? [Y/N]; Replace worn parts? [Y/N]                                                                                </t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive, Preventive             </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure       </t>
+          <t xml:space="preserve">Shaft Failure              </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on drive end         </t>
+          <t xml:space="preserve">Transfers torque between driver and impeller                      </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                  </t>
+          <t xml:space="preserve">VIB - Vibration                  </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                       </t>
+          <t xml:space="preserve">1.2 Misalignment            </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise due to bearing wear                                   </t>
+          <t xml:space="preserve">Shaft vibration caused by misalignment                      </t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Noise inspections and acoustic monitoring? [Y/N]&lt;br&gt;2. Bearings replaced on abnormal noise? [Y/N]&lt;br&gt;3. Repair of loose fittings? [Y/N]                     </t>
+          <t xml:space="preserve">Perform alignment checks? [Y/N]; Correct misalignments? [Y/N]; Inspect couplings? [Y/N]                                                                                        </t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+          <t xml:space="preserve">Failure-Finding       </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure       </t>
+          <t xml:space="preserve">Shaft Failure              </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on drive end         </t>
+          <t xml:space="preserve">Transfers torque between driver and impeller                      </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                  </t>
+          <t xml:space="preserve">VIB - Vibration                  </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness                </t>
+          <t xml:space="preserve">2.6 Fatigue                 </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Looseness creating noise                                    </t>
+          <t xml:space="preserve">Fatigue cracking from cyclic stress                         </t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Tightness and torque checks? [Y/N]&lt;br&gt;2. Repair after looseness detected? [Y/N]&lt;br&gt;3. Tightening procedure routinely performed? [Y/N]                         </t>
+          <t xml:space="preserve">Use NDT to inspect fatigue damage? [Y/N]; Limit overload cycles? [Y/N]; Schedule shaft assessments? [Y/N]                                                                    </t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding                  </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure       </t>
+          <t xml:space="preserve">Shaft Failure              </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on drive end         </t>
+          <t xml:space="preserve">Transfers torque between driver and impeller                      </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating            </t>
+          <t xml:space="preserve">PDE - Parameter deviation        </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                      </t>
+          <t xml:space="preserve">1.4 Deformation            </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lubricant deterioration causing heat increase                </t>
+          <t xml:space="preserve">Shaft deformation or bending affecting performance          </t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Lubricant condition regularly tested? [Y/N]&lt;br&gt;2. Cooling functionality checked? [Y/N]&lt;br&gt;3. Lubrication system maintained? [Y/N]                           </t>
+          <t xml:space="preserve">Monitor shaft geometry? [Y/N]; Inspect periodically? [Y/N]; Control operating loads? [Y/N]                                                                                     </t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive, Preventive             </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure       </t>
+          <t xml:space="preserve">Shaft Failure              </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on drive end         </t>
+          <t xml:space="preserve">Transfers torque between driver and impeller                      </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating            </t>
+          <t xml:space="preserve">NOI - Noise                     </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation             </t>
+          <t xml:space="preserve">2.5 Breakage               </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deformation causing heat build-up                          </t>
+          <t xml:space="preserve">Noise from shaft impact or fracture                         </t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Visual inspection for housing deformation? [Y/N]&lt;br&gt;2. Structural repair performed? [Y/N]&lt;br&gt;3. Monitoring of housing condition? [Y/N]                     </t>
+          <t xml:space="preserve">Visual inspections? [Y/N]; NDT inspections? [Y/N]; Replace broken shafts? [Y/N]                                                                                              </t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive                       </t>
+          <t xml:space="preserve">Corrective            </t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure       </t>
+          <t xml:space="preserve">Shaft Failure              </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on drive end         </t>
+          <t xml:space="preserve">Transfers torque between driver and impeller                      </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running  </t>
+          <t xml:space="preserve">OHE - Overheating               </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage                  </t>
+          <t xml:space="preserve">2.4 Wear                   </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Breakage of bearing components                             </t>
+          <t xml:space="preserve">Overheating due to friction or lubrication failure          </t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Visual and vibration inspections? [Y/N]&lt;br&gt;2. Replacement after breakage? [Y/N]&lt;br&gt;3. Continuous monitoring program? [Y/N]                                </t>
+          <t xml:space="preserve">Temperature monitoring? [Y/N]; Lubrication inspection? [Y/N]; Cooling system checks? [Y/N]                                                                                   </t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure       </t>
+          <t xml:space="preserve">Shaft Failure              </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supports rotor and shaft, reducing friction and wear on drive end         </t>
+          <t xml:space="preserve">Transfers torque between driver and impeller                      </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running  </t>
+          <t xml:space="preserve">FWR - Failure while running      </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                  </t>
+          <t xml:space="preserve">2.4 Wear                   </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue and material failure                                </t>
+          <t xml:space="preserve">Wear causing loss of shaft integrity                        </t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Fatigue analysis program? [Y/N]&lt;br&gt;2. Vibration trending? [Y/N]&lt;br&gt;3. Timely replacement before failure? [Y/N]                                         </t>
+          <t xml:space="preserve">Implement condition monitoring? [Y/N]; Scheduled shaft replacements? [Y/N]; Vibration monitoring? [Y/N]                                                                      </t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive, Preventive             </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brushes Failure          </t>
+          <t xml:space="preserve">NDE Bearing Failure        </t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conducts current to rotor for energy transfer                              </t>
+          <t xml:space="preserve">Supports radial loads on non-drive end                            </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
+          <t xml:space="preserve">VIB - Vibration                  </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                      </t>
+          <t xml:space="preserve">2.4 Wear                   </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Increased vibration due to brush wear                      </t>
+          <t xml:space="preserve">Vibration caused by bearing wear                            </t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Periodic brush wear measurement? [Y/N]&lt;br&gt;2. Timely brush replacement? [Y/N]&lt;br&gt;3. Inspection of brush holders? [Y/N]                                  </t>
+          <t xml:space="preserve">Vibration monitoring? [Y/N]; Bearing inspections? [Y/N]; Replace damaged bearings? [Y/N]                                                                                     </t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive, Preventive             </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brushes Failure          </t>
+          <t xml:space="preserve">NDE Bearing Failure        </t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conducts current to rotor for energy transfer                              </t>
+          <t xml:space="preserve">Supports radial loads on non-drive end                            </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
+          <t xml:space="preserve">VIB - Vibration                  </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness                </t>
+          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brush looseness causing noise and wear                    </t>
+          <t xml:space="preserve">Vibration from clearance or misalignment                  </t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Brush mount tightness verified regularly? [Y/N]&lt;br&gt;2. Fasteners tightened as necessary? [Y/N]&lt;br&gt;3. Repair actions undertaken? [Y/N]                      </t>
+          <t xml:space="preserve">Monitor bearing clearance? [Y/N]; Align improperly placed bearings? [Y/N]; Analyze vibration data? [Y/N]                                                                     </t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding                  </t>
+          <t xml:space="preserve">Failure-Finding       </t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brushes Failure          </t>
+          <t xml:space="preserve">NDE Bearing Failure        </t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conducts current to rotor for energy transfer                              </t>
+          <t xml:space="preserve">Supports radial loads on non-drive end                            </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                  </t>
+          <t xml:space="preserve">PDE - Parameter deviation        </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                      </t>
+          <t xml:space="preserve">2.6 Fatigue                </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise due to worn brushes                                 </t>
+          <t xml:space="preserve">Fatigue and cracking from cyclic loading                  </t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Auditory inspections? [Y/N]&lt;br&gt;2. Noise level monitoring and trending? [Y/N]&lt;br&gt;3. Brush replacement on abnormal noise? [Y/N]                            </t>
+          <t xml:space="preserve">Fatigue monitoring? [Y/N]; Visual inspections? [Y/N]; Scheduled bearing replacements? [Y/N]                                                                                </t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding                  </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brushes Failure          </t>
+          <t xml:space="preserve">NDE Bearing Failure        </t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conducts current to rotor for energy transfer                              </t>
+          <t xml:space="preserve">Supports radial loads on non-drive end                            </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                  </t>
+          <t xml:space="preserve">LOO - Leak of oil               </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness                </t>
+          <t xml:space="preserve">1.4 Deformation            </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise generated by loose brushes                          </t>
+          <t xml:space="preserve">Leakage affecting bearing lubrication                      </t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Tightness of brush mounting checked? [Y/N]&lt;br&gt;2. Loose brush repairs? [Y/N]&lt;br&gt;3. Vibration noise surveys conducted? [Y/N]                              </t>
+          <t xml:space="preserve">Seal inspection? [Y/N]; Oil leakage monitoring? [Y/N]; Repair or replace leaking seals? [Y/N]                                                                            </t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding                  </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brushes Failure          </t>
+          <t xml:space="preserve">NDE Bearing Failure        </t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conducts current to rotor for energy transfer                              </t>
+          <t xml:space="preserve">Supports radial loads on non-drive end                            </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTS - Failure to start on demand </t>
+          <t xml:space="preserve">OHE - Overheating               </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 Open circuit            </t>
+          <t xml:space="preserve">2.6 Fatigue                </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open circuit preventing motor start                      </t>
+          <t xml:space="preserve">Overheating from lubrication failure                      </t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Electrical continuity tested? [Y/N]&lt;br&gt;2. Brush connection inspected? [Y/N]&lt;br&gt;3. Replacement scheduled? [Y/N]                                         </t>
+          <t xml:space="preserve">Temperature monitoring? [Y/N]; Lubrication system inspection? [Y/N]; Cooling system maintenance? [Y/N]                                                                    </t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding                  </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brushes Failure          </t>
+          <t xml:space="preserve">NDE Bearing Failure        </t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conducts current to rotor for energy transfer                              </t>
+          <t xml:space="preserve">Supports radial loads on non-drive end                            </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">STU - Stuck                  </t>
+          <t xml:space="preserve">FWR - Failure while running      </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking                 </t>
+          <t xml:space="preserve">2.4 Wear                   </t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brush or holder stuck causing failure                    </t>
+          <t xml:space="preserve">Wear leading to bearing failure                          </t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Brush movement checked during inspection? [Y/N]&lt;br&gt;2. Immediately freed or replaced if stuck? [Y/N]&lt;br&gt;3. Lubrication of brush holders as needed? [Y/N]     </t>
+          <t xml:space="preserve">Scheduled condition monitoring? [Y/N]; Vibration analysis? [Y/N]; Timely replacement? [Y/N]                                                                             </t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding                  </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooling System Failure   </t>
+          <t xml:space="preserve">DE Bearing Failure         </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removes heat from motor components                                        </t>
+          <t xml:space="preserve">Supports radial loads on drive end                              </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELU - External leakage - utility medium </t>
+          <t xml:space="preserve">VIB - Vibration                  </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion              </t>
+          <t xml:space="preserve">2.4 Wear                   </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leak causing cooling inefficiency                         </t>
+          <t xml:space="preserve">Vibration caused by bearing wear                            </t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Visual inspections for leaks? [Y/N]&lt;br&gt;2. Corrosion treated or repaired? [Y/N]&lt;br&gt;3. Preventive corrosion control applied? [Y/N]                      </t>
+          <t xml:space="preserve">Vibration monitoring? [Y/N]; Bearing inspections? [Y/N]; Replace damaged bearings? [Y/N]                                                                                     </t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooling System Failure   </t>
+          <t xml:space="preserve">DE Bearing Failure         </t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removes heat from motor components                                        </t>
+          <t xml:space="preserve">Supports radial loads on drive end                              </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELU - External leakage - utility medium </t>
+          <t xml:space="preserve">VIB - Vibration                  </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation           </t>
+          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deformation or crack causing leaks                        </t>
+          <t xml:space="preserve">Vibration from clearance or misalignment                  </t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Structural inspections performed? [Y/N]&lt;br&gt;2. Repairs or replacements carried out promptly? [Y/N]&lt;br&gt;3. Cooling efficiency monitored? [Y/N]            </t>
+          <t xml:space="preserve">Monitor bearing clearance? [Y/N]; Align bearings? [Y/N]; Analyze vibration signals? [Y/N]                                                                                   </t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive                       </t>
+          <t xml:space="preserve">Failure-Finding       </t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooling System Failure   </t>
+          <t xml:space="preserve">DE Bearing Failure         </t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removes heat from motor components                                        </t>
+          <t xml:space="preserve">Supports radial loads on drive end                              </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation   </t>
+          <t xml:space="preserve">PDE - Parameter deviation        </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination           </t>
+          <t xml:space="preserve">2.6 Fatigue                </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooling fluid contaminated reducing performance          </t>
+          <t xml:space="preserve">Fatigue damage causing cracking                         </t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Cooling fluid quality tested? [Y/N]&lt;br&gt;2. Filters cleaned or replaced? [Y/N]&lt;br&gt;3. Contaminated fluid replaced? [Y/N]                            </t>
+          <t xml:space="preserve">Fatigue testing? [Y/N]; Visual inspections? [Y/N]; Scheduled replacement? [Y/N]                                                                                          </t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive, Preventive             </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooling System Failure   </t>
+          <t xml:space="preserve">DE Bearing Failure         </t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removes heat from motor components                                        </t>
+          <t xml:space="preserve">Supports radial loads on drive end                              </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation   </t>
+          <t xml:space="preserve">LOO - Leak of oil               </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2009,1973 +2009,1973 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear causing restricted fluid flow                       </t>
+          <t xml:space="preserve">Oil leakage leading to lubrication failure              </t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Visual inspections and monitoring? [Y/N]&lt;br&gt;2. Regular filter changes? [Y/N]&lt;br&gt;3. Fluid flow measurements made regularly? [Y/N]                    </t>
+          <t xml:space="preserve">Seal condition monitoring? [Y/N]; Leak detection? [Y/N]; Seal replacements? [Y/N]                                                                                        </t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive                       </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooling System Failure   </t>
+          <t xml:space="preserve">DE Bearing Failure         </t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removes heat from motor components                                        </t>
+          <t xml:space="preserve">Supports radial loads on drive end                              </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">OHE - Overheating               </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage               </t>
+          <t xml:space="preserve">2.4 Wear                   </t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cracks or structural failure affecting cooling            </t>
+          <t xml:space="preserve">Overheating from wear and lubrication failure          </t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Visual crack detection inspections? [Y/N]&lt;br&gt;2. Repair or replace broken parts? [Y/N]&lt;br&gt;3. Preventive maintenance scheduled? [Y/N]                   </t>
+          <t xml:space="preserve">Temperature monitoring? [Y/N]; Lubrication system checks? [Y/N]; Cooling inspections? [Y/N]                                                                           </t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooling System Failure   </t>
+          <t xml:space="preserve">DE Bearing Failure         </t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removes heat from motor components                                        </t>
+          <t xml:space="preserve">Supports radial loads on drive end                              </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">FWR - Failure while running      </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                </t>
+          <t xml:space="preserve">2.4 Wear                   </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue cracks affecting structural/pipe components       </t>
+          <t xml:space="preserve">Wear causing bearing failure                           </t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Monitoring for signs of fatigue? [Y/N]&lt;br&gt;2. Reinforcement or replacement as necessary? [Y/N]&lt;br&gt;3. Periodic stress relief? [Y/N]                      </t>
+          <t xml:space="preserve">Condition monitoring? [Y/N]; Scheduled replacement? [Y/N]; Vibration analysis? [Y/N]                                                                                   </t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooling System Failure   </t>
+          <t xml:space="preserve">Thrust Bearing Failure     </t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removes heat from motor components                                        </t>
+          <t xml:space="preserve">Supports axial thrust loads                                    </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating          </t>
+          <t xml:space="preserve">VIB - Vibration                  </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation           </t>
+          <t xml:space="preserve">2.4 Wear                   </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Structural deformation causing overheating                </t>
+          <t xml:space="preserve">Vibration from worn thrust bearings                     </t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Visual inspections for deformation? [Y/N]&lt;br&gt;2. Repairs and monitoring? [Y/N]&lt;br&gt;3. Functional cooling checks? [Y/N]                                </t>
+          <t xml:space="preserve">Vibration monitoring? [Y/N]; Bearing inspections? [Y/N]; Replace worn thrust bearings? [Y/N]                                                                        </t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive                       </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooling System Failure   </t>
+          <t xml:space="preserve">Thrust Bearing Failure     </t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removes heat from motor components                                        </t>
+          <t xml:space="preserve">Supports axial thrust loads                                    </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating          </t>
+          <t xml:space="preserve">PDE - Parameter deviation        </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion             </t>
+          <t xml:space="preserve">2.6 Fatigue                </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion decreasing cooling efficiency                   </t>
+          <t xml:space="preserve">Fatigue cracking from cyclic axial loads              </t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Corrosion inspections and treatments? [Y/N]&lt;br&gt;2. Protective coatings maintained? [Y/N]&lt;br&gt;3. Repairs performed when corrosion found? [Y/N]           </t>
+          <t xml:space="preserve">Fatigue testing? [Y/N]; Visual inspections? [Y/N]; Axial load management? [Y/N]                                                                                     </t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coupling Failure         </t>
+          <t xml:space="preserve">Thrust Bearing Failure     </t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfers torque from motor to driven equipment                           </t>
+          <t xml:space="preserve">Supports axial thrust loads                                    </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">SLP - Slippage             </t>
+          <t xml:space="preserve">LOO - Leak of oil               </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.3 Clearance / alignment failure </t>
+          <t xml:space="preserve">1.4 Deformation            </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slippage causing loss of torque transmission              </t>
+          <t xml:space="preserve">Oil leak affecting lubrication                           </t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Coupling alignment checked? [Y/N]&lt;br&gt;2. Belt tension or gear mesh maintained? [Y/N]&lt;br&gt;3. Coupling replaced upon excessive slippage? [Y/N]              </t>
+          <t xml:space="preserve">Seal housing inspections? [Y/N]; Leak detection? [Y/N]; Seal replacements? [Y/N]                                                                                      </t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coupling Failure         </t>
+          <t xml:space="preserve">Thrust Bearing Failure     </t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfers torque from motor to driven equipment                           </t>
+          <t xml:space="preserve">Supports axial thrust loads                                    </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration            </t>
+          <t xml:space="preserve">OHE - Overheating               </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue               </t>
+          <t xml:space="preserve">2.4 Wear                   </t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue cracking causing vibration and failure             </t>
+          <t xml:space="preserve">Overheating from lubrication failure                  </t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Vibration monitored continuously? [Y/N]&lt;br&gt;2. Coupling integrity inspection? [Y/N]&lt;br&gt;3. Repairs/replacements done promptly? [Y/N]                   </t>
+          <t xml:space="preserve">Temperature monitoring? [Y/N]; Lubrication system maintenance? [Y/N]; Cooling system inspections? [Y/N]                                                                </t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive, Preventive             </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coupling Failure         </t>
+          <t xml:space="preserve">Thrust Bearing Failure     </t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfers torque from motor to driven equipment                           </t>
+          <t xml:space="preserve">Supports axial thrust loads                                    </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                </t>
+          <t xml:space="preserve">FWR - Failure while running      </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness             </t>
+          <t xml:space="preserve">2.4 Wear                   </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose coupling parts causing noise                        </t>
+          <t xml:space="preserve">Wear leading to loss of thrust bearing capacity       </t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Tightness inspections during maintenance? [Y/N]&lt;br&gt;2. Noise level recorded and trended? [Y/N]&lt;br&gt;3. Repair loose couplings as required? [Y/N]           </t>
+          <t xml:space="preserve">Scheduled inspections? [Y/N]; Vibration monitoring? [Y/N]; Bearings replacement? [Y/N]                                                                             </t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding                  </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coupling Failure         </t>
+          <t xml:space="preserve">Mechanical Seal Failure    </t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transfers torque from motor to driven equipment                           </t>
+          <t xml:space="preserve">Prevents process fluid leakage along the shaft                 </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRD - Breakdown            </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage              </t>
+          <t xml:space="preserve">2.4 Wear                   </t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Complete mechanical failure causing torque loss            </t>
+          <t xml:space="preserve">Leakage from worn mechanical seals                    </t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Visual mechanical inspections? [Y/N]&lt;br&gt;2. Replacement of broken parts? [Y/N]&lt;br&gt;3. Monitoring for early warning signs? [Y/N]                         </t>
+          <t xml:space="preserve">Seal face inspections? [Y/N]; Scheduled replacements? [Y/N]; Leakage monitoring? [Y/N]                                                                             </t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detector Failure         </t>
+          <t xml:space="preserve">Mechanical Seal Failure    </t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detects operational parameters                                           </t>
+          <t xml:space="preserve">Prevents process fluid leakage along the shaft                 </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">AIR - Abnormal instrument reading </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.4 Out of adjustment     </t>
+          <t xml:space="preserve">2.2 Corrosion              </t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Faulty or drifted reading causing incorrect data            </t>
+          <t xml:space="preserve">Corrosion degrading seal components                   </t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Regular calibration performed? [Y/N]&lt;br&gt;2. Faulty detectors replaced? [Y/N]&lt;br&gt;3. Diagnostic tests routinely conducted? [Y/N]                         </t>
+          <t xml:space="preserve">Corrosion inspections? [Y/N]; Protective coatings? [Y/N]; Fluid chemistry monitoring? [Y/N]                                                                       </t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive, Failure-Finding       </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detector Failure         </t>
+          <t xml:space="preserve">Mechanical Seal Failure    </t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detects operational parameters                                           </t>
+          <t xml:space="preserve">Prevents process fluid leakage along the shaft                 </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">SHH - Spurious high alarm level </t>
+          <t xml:space="preserve">PDE - Parameter deviation        </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.3 Faulty signal/indication/alarm </t>
+          <t xml:space="preserve">2.7 Overheating            </t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">False high alarms causing unnecessary shutdowns              </t>
+          <t xml:space="preserve">Overheating causing seal damage                       </t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Alarm false activation incidents investigated? [Y/N]&lt;br&gt;2. Sensor health checked? [Y/N]&lt;br&gt;3. Corrective actions executed? [Y/N]                  </t>
+          <t xml:space="preserve">Temperature monitoring? [Y/N]; Cooling system inspection? [Y/N]; Seal surface condition monitoring? [Y/N]                                                            </t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding                  </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detector Failure         </t>
+          <t xml:space="preserve">Mechanical Seal Failure    </t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detects operational parameters                                           </t>
+          <t xml:space="preserve">Prevents process fluid leakage along the shaft                 </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">SLL - Spurious low alarm level </t>
+          <t xml:space="preserve">PDE - Parameter deviation        </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.3 Faulty signal/indication/alarm </t>
+          <t xml:space="preserve">2.6 Fatigue                </t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">False low alarms causing inappropriate responses             </t>
+          <t xml:space="preserve">Fatigue cracks on seal surfaces                       </t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Sensor calibration periodically done? [Y/N]&lt;br&gt;2. Faulty detectors maintained and replaced? [Y/N]&lt;br&gt;3. Alarm thresholds verified? [Y/N]                </t>
+          <t xml:space="preserve">Regular inspections? [Y/N]; Wear rate monitoring? [Y/N]; Maintain within operating limits? [Y/N]                                                                     </t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding                  </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detector Failure         </t>
+          <t xml:space="preserve">Mechanical Seal Failure    </t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Detects operational parameters                                           </t>
+          <t xml:space="preserve">Prevents process fluid leakage along the shaft                 </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPO - Spurious operation   </t>
+          <t xml:space="preserve">LOO - Leak of oil               </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.5 Software error          </t>
+          <t xml:space="preserve">1.4 Deformation            </t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unintended operations due to software faults                </t>
+          <t xml:space="preserve">Deformation causing seal leakage                       </t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Software updates applied regularly? [Y/N]&lt;br&gt;2. Monitoring of false operation reports? [Y/N]&lt;br&gt;3. Corrective maintenance performed promptly? [Y/N]       </t>
+          <t xml:space="preserve">Visual inspections? [Y/N]; Housing repair? [Y/N]; Leak detection? [Y/N]                                                                                            </t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding                  </t>
+          <t xml:space="preserve">Corrective            </t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enclosure Failure        </t>
+          <t xml:space="preserve">Mechanical Seal Failure    </t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Protects internal components from environment                            </t>
+          <t xml:space="preserve">Prevents process fluid leakage along the shaft                 </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">NOI - Noise                    </t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation             </t>
+          <t xml:space="preserve">2.4 Wear                   </t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Structural damage undermining protection                     </t>
+          <t xml:space="preserve">Noise from worn mechanical seals                       </t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Visual inspection and structural tests? [Y/N]&lt;br&gt;2. Repairs performed on damage? [Y/N]&lt;br&gt;3. Protective coatings applied and maintained? [Y/N]             </t>
+          <t xml:space="preserve">Acoustic monitoring? [Y/N]; Inspect seal surfaces? [Y/N]; Scheduled maintenance? [Y/N]                                                                           </t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive, Failure-Finding       </t>
+          <t xml:space="preserve">Failure-Finding       </t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enclosure Failure        </t>
+          <t xml:space="preserve">Mechanical Seal Failure    </t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Protects internal components from environment                            </t>
+          <t xml:space="preserve">Prevents process fluid leakage along the shaft                 </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRD - Breakdown           </t>
+          <t xml:space="preserve">FWR - Failure while running      </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness              </t>
+          <t xml:space="preserve">2.4 Wear                   </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Structural failure causing enclosure malfunction             </t>
+          <t xml:space="preserve">Wear causing functional loss                          </t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Structural fasteners checked? [Y/N]&lt;br&gt;2. Repairs on looseness executed? [Y/N]&lt;br&gt;3. Maintenance records updated? [Y/N]                                </t>
+          <t xml:space="preserve">Condition monitoring? [Y/N]; Wear rate analysis? [Y/N]; Timely replacement? [Y/N]                                                                               </t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enclosure Failure        </t>
+          <t xml:space="preserve">Coupling Failure           </t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Protects internal components from environment                            </t>
+          <t xml:space="preserve">Transmit torque between driver and pump shafts                </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium (*) </t>
+          <t xml:space="preserve">VIB - Vibration                  </t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion           </t>
+          <t xml:space="preserve">1.5 Looseness             </t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion causing external leakage                            </t>
+          <t xml:space="preserve">Vibration from loose coupling                         </t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Seal and gasket inspections? [Y/N]&lt;br&gt;2. Corrosion treated and monitored? [Y/N]&lt;br&gt;3. Seal replacement planned? [Y/N]                                  </t>
+          <t xml:space="preserve">Check fastener torque? [Y/N]; Secure or replace loose parts? [Y/N]; Vibration monitoring? [Y/N]                                                                     </t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+          <t xml:space="preserve">Failure-Finding       </t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enclosure Failure        </t>
+          <t xml:space="preserve">Coupling Failure           </t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Protects internal components from environment                            </t>
+          <t xml:space="preserve">Transmit torque between driver and pump shafts                </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise               </t>
+          <t xml:space="preserve">VIB - Vibration                  </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                </t>
+          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise caused by fatigue cracks in enclosure material          </t>
+          <t xml:space="preserve">Vibration caused by misalignment                    </t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Auditory inspections? [Y/N]&lt;br&gt;2. Fatigue monitoring applied? [Y/N]&lt;br&gt;3. Repairs or replacements done timely? [Y/N]                                </t>
+          <t xml:space="preserve">Alignment checks? [Y/N]; Correction of misalignment? [Y/N]; Use precision alignment tools? [Y/N]                                                                   </t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding                  </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gearbox Failure          </t>
+          <t xml:space="preserve">Coupling Failure           </t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmits and modifies rotational power                                 </t>
+          <t xml:space="preserve">Transmit torque between driver and pump shafts                </t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration            </t>
+          <t xml:space="preserve">FWR - Failure while running      </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">2.5 Breakage              </t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Increased vibration from worn gear teeth                      </t>
+          <t xml:space="preserve">Structural breakage causing torque loss               </t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Vibration analysis conducted regularly? [Y/N]&lt;br&gt;2. Gear lubrication status verified? [Y/N]&lt;br&gt;3. Worn gears replaced as needed? [Y/N]                 </t>
+          <t xml:space="preserve">Visual inspection? [Y/N]; NDT testing? [Y/N]; Component replacement? [Y/N]                                                                                        </t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive, Preventive             </t>
+          <t xml:space="preserve">Corrective            </t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gearbox Failure          </t>
+          <t xml:space="preserve">Coupling Failure           </t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmits and modifies rotational power                                 </t>
+          <t xml:space="preserve">Transmit torque between driver and pump shafts                </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                </t>
+          <t xml:space="preserve">STU - Stuck                   </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness              </t>
+          <t xml:space="preserve">1.6 Sticking              </t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise generated by loose mounting or gears                  </t>
+          <t xml:space="preserve">Sticking or seizure prevents rotation                </t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Visual and noise inspections? [Y/N]&lt;br&gt;2. Tightening of mounting bolts? [Y/N]&lt;br&gt;3. Maintenance on loose parts? [Y/N]                                   </t>
+          <t xml:space="preserve">Lubrication checks? [Y/N]; Movement monitoring? [Y/N]; Repair or replace stuck components? [Y/N]                                                                  </t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding                  </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gearbox Failure          </t>
+          <t xml:space="preserve">Coupling Failure           </t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmits and modifies rotational power                                 </t>
+          <t xml:space="preserve">Transmit torque between driver and pump shafts                </t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation  </t>
+          <t xml:space="preserve">PDE - Parameter deviation        </t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">1.4 Deformation           </t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parameter deviations due to gear wear                       </t>
+          <t xml:space="preserve">Mechanical deformation causing disalignment           </t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Control parameter monitoring? [Y/N]&lt;br&gt;2. Lubricant condition checked? [Y/N]&lt;br&gt;3. Timely maintenance performed? [Y/N]                               </t>
+          <t xml:space="preserve">Structural inspection? [Y/N]; Repair and realignment? [Y/N]; Condition monitoring? [Y/N]                                                                         </t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive, Preventive             </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gearbox Failure          </t>
+          <t xml:space="preserve">Baseplate Failure          </t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmits and modifies rotational power                                 </t>
+          <t xml:space="preserve">Structural support for pump and driver                         </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">STD - Structural deficiency      </t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage              </t>
+          <t xml:space="preserve">1.4 Deformation           </t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Broken gears causing operational failure                     </t>
+          <t xml:space="preserve">Cracks or bending causing loss of structural integrity </t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Visual gear inspections scheduled? [Y/N]&lt;br&gt;2. Replacement of failed gears? [Y/N]&lt;br&gt;3. Condition monitoring used? [Y/N]                             </t>
+          <t xml:space="preserve">Structural inspections? [Y/N]; Repair or replace damaged baseplate? [Y/N]; Vibration monitoring? [Y/N]                                                                </t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heaters Failure          </t>
+          <t xml:space="preserve">Baseplate Failure          </t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides anti-condensation or temperature control                       </t>
+          <t xml:space="preserve">Structural support for pump and driver                         </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTS - Failure to start on demand </t>
+          <t xml:space="preserve">STD - Structural deficiency      </t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking           </t>
+          <t xml:space="preserve">5.3 External impact       </t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heater fails to energize                                     </t>
+          <t xml:space="preserve">Damage caused by external impacts                      </t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Check heater power supply continuity? [Y/N]&lt;br&gt;2. Test heater circuit? [Y/N]&lt;br&gt;3. Schedule replacement of failed heaters? [Y/N]                      </t>
+          <t xml:space="preserve">Visual inspection for impact damage? [Y/N]; Repair and reinforcement? [Y/N]; Implement impact mitigation measures? [Y/N]                                             </t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding                  </t>
+          <t xml:space="preserve">Corrective            </t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heaters Failure          </t>
+          <t xml:space="preserve">Baseplate Failure          </t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides anti-condensation or temperature control                       </t>
+          <t xml:space="preserve">Structural support for pump and driver                         </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">HTF - Heating failure      </t>
+          <t xml:space="preserve">VIB - Vibration                  </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness              </t>
+          <t xml:space="preserve">1.5 Looseness             </t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose connections causing heating failure                    </t>
+          <t xml:space="preserve">Vibration caused by loose mounting                      </t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Inspect wiring and connection tightness? [Y/N]&lt;br&gt;2. Repair loose wiring? [Y/N]&lt;br&gt;3. Check insulation of heater wiring? [Y/N]                      </t>
+          <t xml:space="preserve">Check anchor bolt tightness? [Y/N]; Tighten or replace loose bolts? [Y/N]; Vibration level monitoring? [Y/N]                                                             </t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding                  </t>
+          <t xml:space="preserve">Failure-Finding       </t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heaters Failure          </t>
+          <t xml:space="preserve">Baseplate Failure          </t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides anti-condensation or temperature control                       </t>
+          <t xml:space="preserve">Structural support for pump and driver                         </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation  </t>
+          <t xml:space="preserve">ILP - Internal leakage – process medium </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.4 Out of adjustment       </t>
+          <t xml:space="preserve">2.2 Corrosion             </t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control failure causing abnormal heating                    </t>
+          <t xml:space="preserve">Internal corrosion weakening baseplate                 </t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Verify heater control settings? [Y/N]&lt;br&gt;2. Perform calibration checks? [Y/N]&lt;br&gt;3. Correct control parameters when needed? [Y/N]                      </t>
+          <t xml:space="preserve">Inspect for corrosion? [Y/N]; Apply corrosion protection? [Y/N]; Repair or replace corroded areas? [Y/N]                                                                   </t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heaters Failure          </t>
+          <t xml:space="preserve">Baseplate Failure          </t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides anti-condensation or temperature control                       </t>
+          <t xml:space="preserve">Structural support for pump and driver                         </t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                </t>
+          <t xml:space="preserve">STP - Failure to stop on demand  </t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">6.2 Combined causes       </t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise caused by worn heater components                      </t>
+          <t xml:space="preserve">Failure to stop due to mechanical or control issues   </t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Monitor noise levels? [Y/N]&lt;br&gt;2. Inspect heater components? [Y/N]&lt;br&gt;3. Perform repairs or replacements? [Y/N]                                        </t>
+          <t xml:space="preserve">Inspect mechanical stop devices? [Y/N]; Repair or remove obstructions? [Y/N]; Control system checks? [Y/N]                                                                </t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding                  </t>
+          <t xml:space="preserve">Failure-Finding       </t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heaters Failure          </t>
+          <t xml:space="preserve">Baseplate Failure          </t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides anti-condensation or temperature control                       </t>
+          <t xml:space="preserve">Structural support for pump and driver                         </t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRD - Breakdown            </t>
+          <t xml:space="preserve">FWR - Failure while running      </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage              </t>
+          <t xml:space="preserve">2.4 Wear                  </t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heater component failure causing loss of heating            </t>
+          <t xml:space="preserve">Wear and fatigue causing baseplate degradation         </t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Visual inspection scheduled? [Y/N]&lt;br&gt;2. Repair or replace heaters as needed? [Y/N]&lt;br&gt;3. Monitor heater performance post maintenance? [Y/N]            </t>
+          <t xml:space="preserve">Condition monitoring? [Y/N]; Scheduled baseplate inspection? [Y/N]; Repair or replace as needed? [Y/N]                                                                    </t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Junction Box Failure     </t>
+          <t xml:space="preserve">Lube Oil System Failure (*) </t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houses electrical connections and protection                           </t>
+          <t xml:space="preserve">Supplies lubrication oil to bearings and components           </t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTS - Failure to start on demand </t>
+          <t xml:space="preserve">LBP - Low oil supply pressure    </t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 No power/voltage     </t>
+          <t xml:space="preserve">5.1 Blockage              </t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power loss preventing start                                 </t>
+          <t xml:space="preserve">Reduced oil flow leading to bearing damage             </t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Power supply continuity verified? [Y/N]&lt;br&gt;2. Check wiring and fuses? [Y/N]&lt;br&gt;3. Repairs done immediately? [Y/N]                                     </t>
+          <t xml:space="preserve">Inspect and clean filters? [Y/N]; Monitor oil pump operation? [Y/N]; Measure oil pressure frequently? [Y/N]                                                                </t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding                  </t>
+          <t xml:space="preserve">Failure-Finding       </t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Junction Box Failure     </t>
+          <t xml:space="preserve">Lube Oil System Failure (*) </t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houses electrical connections and protection                           </t>
+          <t xml:space="preserve">Supplies lubrication oil to bearings and components           </t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">PTF - Power/signal transmission failure </t>
+          <t xml:space="preserve">ELU - External leakage - utility medium </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 Open circuit     </t>
+          <t xml:space="preserve">2.4 Wear                  </t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open circuit causing loss of signal                         </t>
+          <t xml:space="preserve">Oil leakage leading to poor lubrication                 </t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Inspect wiring and connectors? [Y/N]&lt;br&gt;2. Perform continuity tests? [Y/N]&lt;br&gt;3. Replace damaged wiring/connectors? [Y/N]                               </t>
+          <t xml:space="preserve">Inspect oil lines and seals? [Y/N]; Repair leaks? [Y/N]; Monitor for leaks continuously? [Y/N]                                                                            </t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding                  </t>
+          <t xml:space="preserve">Corrective            </t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Junction Box Failure     </t>
+          <t xml:space="preserve">Lube Oil System Failure (*) </t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houses electrical connections and protection                           </t>
+          <t xml:space="preserve">Supplies lubrication oil to bearings and components           </t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD - Structural deficiency </t>
+          <t xml:space="preserve">PDE - Parameter deviation        </t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation          </t>
+          <t xml:space="preserve">5.2 Contamination         </t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Physical damage causing failure of junction box             </t>
+          <t xml:space="preserve">Contaminated oil degrading system                       </t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Visual inspection of box integrity? [Y/N]&lt;br&gt;2. Structural repairs performed? [Y/N]&lt;br&gt;3. Protective sealing maintained? [Y/N]                          </t>
+          <t xml:space="preserve">Conduct oil analyses? [Y/N]; Maintain filtration system? [Y/N]; Eliminate contamination sources? [Y/N]                                                                     </t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive, Failure-Finding       </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Junction Box Failure     </t>
+          <t xml:space="preserve">Lube Oil System Failure (*) </t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Houses electrical connections and protection                           </t>
+          <t xml:space="preserve">Supplies lubrication oil to bearings and components           </t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                </t>
+          <t xml:space="preserve">LOO - Low output                 </t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness             </t>
+          <t xml:space="preserve">1.1 Leakage              </t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose connections causing noise                             </t>
+          <t xml:space="preserve">Loss of oil flow due to leaks or blockages              </t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Connection tightness checked? [Y/N]&lt;br&gt;2. Tighten loose parts? [Y/N]&lt;br&gt;3. Noise level recorded and trended? [Y/N]                                    </t>
+          <t xml:space="preserve">Inspect for leaks? [Y/N]; Check oil pumps and lines? [Y/N]; Repair defective parts? [Y/N]                                                                                </t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding                  </t>
+          <t xml:space="preserve">Corrective            </t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lubrication System Failure (*) </t>
+          <t xml:space="preserve">Lube Oil System Failure (*) </t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplies lubricant to bearings and moving parts                       </t>
+          <t xml:space="preserve">Supplies lubrication oil to bearings and components           </t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOO - Low oil pressure      </t>
+          <t xml:space="preserve">PLU - Plugged/choked             </t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.1 Leakage               </t>
+          <t xml:space="preserve">5.1 Blockage              </t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lubricant pressure loss causing equipment degradation       </t>
+          <t xml:space="preserve">Blockages causing oil flow disruption                   </t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Oil pressure monitored continuously? [Y/N]&lt;br&gt;2. Leak detection conducted regularly? [Y/N]&lt;br&gt;3. Lubricant levels maintained? [Y/N]                    </t>
+          <t xml:space="preserve">Clean filters and pipelines? [Y/N]; Monitor system pressure? [Y/N]; Remove blockages? [Y/N]                                                                               </t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive, Failure-Finding        </t>
+          <t xml:space="preserve">Failure-Finding       </t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lubrication System Failure (*) </t>
+          <t xml:space="preserve">Cooling System Failure (*)  </t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplies lubricant to bearings and moving parts                       </t>
+          <t xml:space="preserve">Removes heat from pump components                             </t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELU - External leakage - utility medium </t>
+          <t xml:space="preserve">PDE - Parameter deviation        </t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear               </t>
+          <t xml:space="preserve">5.1 Blockage              </t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear of lubrication parts causing leaks                     </t>
+          <t xml:space="preserve">Cooling water blockage leading to overheating          </t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Visual inspection for leaks? [Y/N]&lt;br&gt;2. Seal conditions monitored? [Y/N]&lt;br&gt;3. Repair or replace leaking components? [Y/N]                         </t>
+          <t xml:space="preserve">Inspect cooling filters? [Y/N]; Monitor flow and temperature? [Y/N]; Clean heat exchangers? [Y/N]                                                                       </t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lubrication System Failure (*) </t>
+          <t xml:space="preserve">Cooling System Failure (*)  </t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplies lubricant to bearings and moving parts                       </t>
+          <t xml:space="preserve">Removes heat from pump components                             </t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation   </t>
+          <t xml:space="preserve">ELU - External leakage - utility medium </t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 Contamination        </t>
+          <t xml:space="preserve">2.4 Wear                  </t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contamination reducing lubricant effectiveness              </t>
+          <t xml:space="preserve">Leak of cooling fluid causing overheating               </t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Oil analysis performed regularly? [Y/N]&lt;br&gt;2. Filters cleaned/replaced? [Y/N]&lt;br&gt;3. Contaminated oil replaced? [Y/N]                              </t>
+          <t xml:space="preserve">Leak detection? [Y/N]; Repair leaks? [Y/N]; Monitor coolant levels? [Y/N]                                                                                               </t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive, Preventive             </t>
+          <t xml:space="preserve">Corrective            </t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lubrication System Failure (*) </t>
+          <t xml:space="preserve">Cooling System Failure (*)  </t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplies lubricant to bearings and moving parts                       </t>
+          <t xml:space="preserve">Removes heat from pump components                             </t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">LOO - Low output                 </t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue              </t>
+          <t xml:space="preserve">2.2 Corrosion             </t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue damage arising from loss of lubrication              </t>
+          <t xml:space="preserve">Corrosion impairing cooling circuits                    </t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Condition monitoring conducted? [Y/N]&lt;br&gt;2. Lubrication schedule strictly followed? [Y/N]&lt;br&gt;3. Repairs conducted promptly? [Y/N]                   </t>
+          <t xml:space="preserve">Corrosion inspection? [Y/N]; Apply coatings? [Y/N]; Repair damage? [Y/N]                                                                                                </t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive                       </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft Failure (*)          </t>
+          <t xml:space="preserve">Cooling System Failure (*)  </t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmits torque from rotor to driven equipment                        </t>
+          <t xml:space="preserve">Removes heat from pump components                             </t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration            </t>
+          <t xml:space="preserve">STD - Structural deficiency      </t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue              </t>
+          <t xml:space="preserve">5.3 External influences   </t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue cracks causing increased vibration                  </t>
+          <t xml:space="preserve">External damage impacting cooling system                </t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Vibration analysis in operation? [Y/N]&lt;br&gt;2. Shaft inspections during maintenance? [Y/N]&lt;br&gt;3. Replacement before failure? [Y/N]                   </t>
+          <t xml:space="preserve">Visual inspection? [Y/N]; Repair external damage? [Y/N]; Environmental protection? [Y/N]                                                                                </t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive, Preventive             </t>
+          <t xml:space="preserve">Failure-Finding       </t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft Failure (*)          </t>
+          <t xml:space="preserve">Seal Piping Failure (*)     </t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmits torque from rotor to driven equipment                        </t>
+          <t xml:space="preserve">Provides flush fluid to seal                                  </t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration            </t>
+          <t xml:space="preserve">ELU - External leakage - utility medium </t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.3 Clearance / alignment failure </t>
+          <t xml:space="preserve">1.4 Deformation          </t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft misalignment causing vibration                      </t>
+          <t xml:space="preserve">Deformation causing fluid leaks                      </t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Shaft alignment measured? [Y/N]&lt;br&gt;2. Coupling alignment verified? [Y/N]&lt;br&gt;3. Maintenance actions on misalignment? [Y/N]                          </t>
+          <t xml:space="preserve">Inspect pipe integrity? [Y/N]; Repair or replace damaged pipes? [Y/N]; Leak detection? [Y/N]                                                                           </t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive                       </t>
+          <t xml:space="preserve">Corrective            </t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft Failure (*)          </t>
+          <t xml:space="preserve">Seal Piping Failure (*)     </t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmits torque from rotor to driven equipment                        </t>
+          <t xml:space="preserve">Provides flush fluid to seal                                  </t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">PLU - Plugged/choked             </t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage             </t>
+          <t xml:space="preserve">5.1 Blockage              </t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft breakage or fracture causing failure                  </t>
+          <t xml:space="preserve">Blockage obstructing flush fluid flow                    </t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Visual inspection pre-operation? [Y/N]&lt;br&gt;2. Vibration monitoring? [Y/N]&lt;br&gt;3. Immediate repair or replacement? [Y/N]                               </t>
+          <t xml:space="preserve">Flush and clean seal piping? [Y/N]; Inspect for blockages? [Y/N]; Pipe replacement? [Y/N]                                                                              </t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+          <t xml:space="preserve">Failure-Finding       </t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal Failure (*)           </t>
+          <t xml:space="preserve">Seal Piping Failure (*)     </t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevents lubricant and cooling fluid leakage                           </t>
+          <t xml:space="preserve">Provides flush fluid to seal                                  </t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELU - External leakage - utility medium </t>
+          <t xml:space="preserve">PDE - Parameter deviation        </t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear               </t>
+          <t xml:space="preserve">2.2 Corrosion             </t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal wear causing fluid leaks                               </t>
+          <t xml:space="preserve">Corrosion causing leaks or blockages                     </t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Seal integrity checked? [Y/N]&lt;br&gt;2. Leak monitoring established? [Y/N]&lt;br&gt;3. Replacement of worn seals? [Y/N]                                       </t>
+          <t xml:space="preserve">Corrosion inspections? [Y/N]; Protective coatings? [Y/N]; Repairs? [Y/N]                                                                                               </t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal Failure (*)           </t>
+          <t xml:space="preserve">Seal Piping Failure (*)     </t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevents lubricant and cooling fluid leakage                           </t>
+          <t xml:space="preserve">Provides flush fluid to seal                                  </t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation  </t>
+          <t xml:space="preserve">LOO - Leak of oil               </t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3985,490 +3985,386 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal deformation leading to packing or leakage              </t>
+          <t xml:space="preserve">Leak of seal flush fluid                               </t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Visual inspection for deformations? [Y/N]&lt;br&gt;2. Structural repairs performed? [Y/N]&lt;br&gt;3. Preventive maintenance scheduled? [Y/N]                  </t>
+          <t xml:space="preserve">Leak monitoring? [Y/N]; Repair leaks promptly? [Y/N]; Scheduled flush system inspections? [Y/N]                                                                       </t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive                       </t>
+          <t xml:space="preserve">Predictive            </t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal Failure (*)           </t>
+          <t xml:space="preserve">Filter Failure (*)          </t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevents lubricant and cooling fluid leakage                           </t>
+          <t xml:space="preserve">Removes contaminants from lube or flush fluids               </t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">SPO - Spurious operation   </t>
+          <t xml:space="preserve">PLU - Plugged/choked             </t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion            </t>
+          <t xml:space="preserve">5.1 Blockage              </t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion damaging seal surfaces                            </t>
+          <t xml:space="preserve">Flow obstruction blocks functional oil flow             </t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Corrosion monitoring? [Y/N]&lt;br&gt;2. Seal replacement if corroded? [Y/N]&lt;br&gt;3. Protective coatings applied? [Y/N]                                   </t>
+          <t xml:space="preserve">Inspect filter elements? [Y/N]; Clean or replace filters? [Y/N]; Monitoring differential pressure? [Y/N]                                                                </t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+          <t xml:space="preserve">Failure-Finding       </t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power Supply Failure (*)    </t>
+          <t xml:space="preserve">Filter Failure (*)          </t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplies electrical power to motor control and protection systems    </t>
+          <t xml:space="preserve">Removes contaminants from lube or flush fluids               </t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTS - Failure to start on demand </t>
+          <t xml:space="preserve">PDE - Parameter deviation        </t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.3 No power/voltage    </t>
+          <t xml:space="preserve">5.2 Contamination         </t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power failure preventing motor startup                    </t>
+          <t xml:space="preserve">Contamination reducing filter effectiveness              </t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Power supply tested regularly? [Y/N]&lt;br&gt;2. Wiring and connections inspected? [Y/N]&lt;br&gt;3. Repairs completed as needed? [Y/N]                       </t>
+          <t xml:space="preserve">Perform oil analysis? [Y/N]; Maintain filtration system? [Y/N]; Remove contamination sources? [Y/N]                                                                      </t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Power Supply Failure (*)    </t>
+          <t xml:space="preserve">Filter Failure (*)          </t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supplies electrical power to motor control and protection systems    </t>
+          <t xml:space="preserve">Removes contaminants from lube or flush fluids               </t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">PTF - Power/signal transmission failure </t>
+          <t xml:space="preserve">LOO - Low output                 </t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 Open circuit     </t>
+          <t xml:space="preserve">1.1 Leakage              </t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open circuit leading to signal loss                        </t>
+          <t xml:space="preserve">Leakage reducing filtration                             </t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Electrical continuity checked? [Y/N]&lt;br&gt;2. Power supply components replaced when faulty? [Y/N]&lt;br&gt;3. Monitoring for power anomalies? [Y/N]          </t>
+          <t xml:space="preserve">Check for filter housing leaks? [Y/N]; Repair leaks? [Y/N]; Inspect seal conditions? [Y/N]                                                                           </t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding                  </t>
+          <t xml:space="preserve">Corrective            </t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Insulation System Failure (*) </t>
+          <t xml:space="preserve">Filter Failure (*)          </t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides electrical insulation to prevent shorts and leakage         </t>
+          <t xml:space="preserve">Removes contaminants from lube or flush fluids               </t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOO - No output            </t>
+          <t xml:space="preserve">FWR - Failure while running      </t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.1 Short circuiting       </t>
+          <t xml:space="preserve">2.4 Wear                  </t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Short circuit causing motor failure                        </t>
+          <t xml:space="preserve">Wear causing filter failure                            </t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Insulation resistance tested? [Y/N]&lt;br&gt;2. Visual inspections for damage? [Y/N]&lt;br&gt;3. Repairs or rewinding performed promptly? [Y/N]                 </t>
+          <t xml:space="preserve">Scheduled filter inspections? [Y/N]; Monitor wear rate? [Y/N]; Timely filter replacement? [Y/N]                                                                       </t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding, Redesign         </t>
+          <t xml:space="preserve">Preventive            </t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Insulation System Failure (*) </t>
+          <t xml:space="preserve">Instrumentation Failure (*) </t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides electrical insulation to prevent shorts and leakage         </t>
+          <t xml:space="preserve">Monitors pump parameters                                     </t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating          </t>
+          <t>AIR - Abnormal instrument reading</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.7 Overheating           </t>
+          <t xml:space="preserve">3.4 Out of adjustment    </t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overheating causing insulation breakdown                   </t>
+          <t xml:space="preserve">Incorrect readings cause faulty control                   </t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Temperature sensors monitored? [Y/N]&lt;br&gt;2. Cooling system functioning? [Y/N]&lt;br&gt;3. Thermal protection maintained? [Y/N]                            </t>
+          <t xml:space="preserve">Sensor calibration? [Y/N]; Sensor replacement? [Y/N]; Alarm function test? [Y/N]                                                                                      </t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive, Preventive             </t>
+          <t xml:space="preserve">Failure-Finding       </t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Insulation System Failure (*) </t>
+          <t xml:space="preserve">Instrumentation Failure (*) </t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides electrical insulation to prevent shorts and leakage         </t>
+          <t xml:space="preserve">Monitors pump parameters                                     </t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation  </t>
+          <t xml:space="preserve">SHH - Spurious high alarm        </t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.4 Out of adjustment      </t>
+          <t xml:space="preserve">3.3 Faulty signal        </t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parameter deviation due to insulation degradation          </t>
+          <t xml:space="preserve">False alarms causing operational issues                  </t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Electrical parameters monitored? [Y/N]&lt;br&gt;2. Preventive maintenance scheduled? [Y/N]&lt;br&gt;3. Corrective actions performed? [Y/N]                     </t>
+          <t xml:space="preserve">Signal verification? [Y/N]; Communication checks? [Y/N]; Software updates? [Y/N]                                                                                     </t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding, Preventive       </t>
+          <t xml:space="preserve">Failure-Finding       </t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motor, Electric </t>
+          <t xml:space="preserve">Pump Centrifugal </t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
+          <t xml:space="preserve">Transfer process fluid by increasing pressure      </t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Terminal Connections Failure (*) </t>
+          <t xml:space="preserve">Instrumentation Failure (*) </t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Electrical connection points ensuring integrity of power delivery    </t>
+          <t xml:space="preserve">Monitors pump parameters                                     </t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">FTS - Failure to start on demand </t>
+          <t xml:space="preserve">PDE - Parameter deviation        </t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.2 Open circuit        </t>
+          <t xml:space="preserve">3.1 Control failure      </t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open circuit causing system start failure                 </t>
+          <t xml:space="preserve">Control/measurement failure impacting operation          </t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Terminal connections checked? [Y/N]&lt;br&gt;2. Tightening of connectors? [Y/N]&lt;br&gt;3. Repair or replacement of faulty terminals? [Y/N]                   </t>
+          <t xml:space="preserve">Controls system checks? [Y/N]; Sensor performance monitoring? [Y/N]; Fail-safe system tests? [Y/N]                                                                   </t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD                   </t>
+          <t xml:space="preserve">TBD                  </t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding                  </t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Motor, Electric </t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Terminal Connections Failure (*) </t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Electrical connection points ensuring integrity of power delivery    </t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PTF - Power/signal transmission failure </t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4.5 Earth/isolation fault </t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Earth fault causing operational failure                   </t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Insulation tests performed? [Y/N]&lt;br&gt;2. Connection integrity monitored? [Y/N]&lt;br&gt;3. Corrective maintenance done? [Y/N]                              </t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Failure-Finding                  </t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Motor, Electric </t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Convert electrical energy into mechanical energy  </t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Terminal Connections Failure (*) </t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Electrical connection points ensuring integrity of power delivery    </t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NOI - Noise                </t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1.5 Looseness             </t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Loose terminals causing noise                             </t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Noise level monitored? [Y/N]&lt;br&gt;2. Connectors checked and tightened? [Y/N]&lt;br&gt;3. Immediate repair on noise detection? [Y/N]                          </t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD                   </t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Failure-Finding                  </t>
+          <t xml:space="preserve">Failure-Finding       </t>
         </is>
       </c>
     </row>

--- a/outputs/EMS upgrade output.xlsx
+++ b/outputs/EMS upgrade output.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,47 +476,47 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder Head Failure          </t>
+          <t>Cylinders Failure</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides combustion chamber sealing, supports valves and gas exchange  </t>
+          <t xml:space="preserve">Provide combustion chamber for controlled combustion             </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation      </t>
+          <t xml:space="preserve">VIB - Vibration          </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion              </t>
+          <t xml:space="preserve">2.6 Fatigue                   </t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion reduces sealing efficiency causing compression loss   </t>
+          <t xml:space="preserve">Cracks causing abnormal vibration                    </t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder head inspected for corrosion? [Y/N]&lt;br&gt;Valve seats checked for corrosion? [Y/N]&lt;br&gt;Combustion chamber cleaned? [Y/N]                                                   </t>
+          <t xml:space="preserve">Inspect cylinder walls for cracks [Y/N]; Ultrasonic inspection [Y/N]; Monitor vibration signature [Y/N] </t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">605-01-40            </t>
+          <t xml:space="preserve">TBD                   </t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive               </t>
+          <t xml:space="preserve">Preventive             </t>
         </is>
       </c>
     </row>
@@ -528,47 +528,47 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder Head Failure          </t>
+          <t>Cylinders Failure</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides combustion chamber sealing, supports valves and gas exchange  </t>
+          <t xml:space="preserve">Provide combustion chamber for controlled combustion             </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation      </t>
+          <t xml:space="preserve">VIB - Vibration          </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage               </t>
+          <t xml:space="preserve">2.4 Wear                      </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cracks or fractures lead to leaks and compression loss          </t>
+          <t xml:space="preserve">Wear causing uneven combustion surfaces              </t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visual inspection for cracks? [Y/N]&lt;br&gt;NDT for fracture detection? [Y/N]&lt;br&gt;Performed valve and seat replacements? [Y/N]                                                       </t>
+          <t xml:space="preserve">Visual and dimensional inspection [Y/N]; Measure wear after overhaul [Y/N]; Replace liners as needed [Y/N] </t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">605-01-40            </t>
+          <t xml:space="preserve">TBD                   </t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive               </t>
+          <t xml:space="preserve">Predictive             </t>
         </is>
       </c>
     </row>
@@ -580,47 +580,47 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder Head Failure          </t>
+          <t>Cylinders Failure</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides combustion chamber sealing, supports valves and gas exchange  </t>
+          <t xml:space="preserve">Provide combustion chamber for controlled combustion             </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation      </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation            </t>
+          <t xml:space="preserve">2.2 Corrosion                 </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warping or distortion affects valve and chamber function        </t>
+          <t xml:space="preserve">Corrosion leading to loss of bore integrity           </t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimensional checks performed? [Y/N]&lt;br&gt;Valve guide and seat alignment checked? [Y/N]&lt;br&gt;Machining or replacement performed? [Y/N]                                           </t>
+          <t xml:space="preserve">Monitor cooling water chemistry [Y/N]; Inspect corrosion protection [Y/N]; Repair damaged lining [Y/N] </t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">605-01-40            </t>
+          <t xml:space="preserve">TBD                   </t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding          </t>
+          <t xml:space="preserve">Preventive             </t>
         </is>
       </c>
     </row>
@@ -632,47 +632,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder Head Failure          </t>
+          <t>Cylinders Failure</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides combustion chamber sealing, supports valves and gas exchange  </t>
+          <t xml:space="preserve">Provide combustion chamber for controlled combustion             </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation      </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">2.3 Erosion                   </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve seat wear causes leaks and pressure loss                   </t>
+          <t xml:space="preserve">Erosion causing volume loss and gas leakage           </t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valve seat wear measured? [Y/N]&lt;br&gt;Valve grinding or replacement performed? [Y/N]&lt;br&gt;Valve clearance adjusted? [Y/N]                                                           </t>
+          <t xml:space="preserve">Inspect cylinder lining erosion [Y/N]; Clean lubrication system [Y/N]; Replace worn parts [Y/N]          </t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">605-01-40            </t>
+          <t xml:space="preserve">TBD                   </t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive               </t>
+          <t xml:space="preserve">Preventive             </t>
         </is>
       </c>
     </row>
@@ -684,47 +684,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder Head Failure          </t>
+          <t>Cylinders Failure</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides combustion chamber sealing, supports valves and gas exchange  </t>
+          <t xml:space="preserve">Provide combustion chamber for controlled combustion             </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating             </t>
+          <t xml:space="preserve">NOI - Noise              </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation            </t>
+          <t xml:space="preserve">2.5 Breakage                  </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thermal distortion causes valve and head damage                 </t>
+          <t xml:space="preserve">Fragmentation noise from cracked cylinder              </t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooling system verified? [Y/N]&lt;br&gt;Temperature sensors calibrated? [Y/N]&lt;br&gt;Valve cooling water pressure checked? [Y/N]                                                       </t>
+          <t xml:space="preserve">Acoustic and visual inspection [Y/N]; Replace fractured parts [Y/N]; Vibration analysis [Y/N]           </t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t xml:space="preserve">605-01-40            </t>
+          <t xml:space="preserve">TBD                   </t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive               </t>
+          <t xml:space="preserve">Failure-Finding        </t>
         </is>
       </c>
     </row>
@@ -736,47 +736,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder Head Failure          </t>
+          <t>Cylinders Failure</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides combustion chamber sealing, supports valves and gas exchange  </t>
+          <t xml:space="preserve">Provide combustion chamber for controlled combustion             </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating             </t>
+          <t xml:space="preserve">NOI - Noise              </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                </t>
+          <t xml:space="preserve">5.3 External impact           </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thermal fatigue cracking damages components                      </t>
+          <t xml:space="preserve">Noise from external impacts or debris                  </t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thermal cycle monitoring? [Y/N]&lt;br&gt;Crack detection inspections? [Y/N]&lt;br&gt;Material replacement or repair? [Y/N]                                                                </t>
+          <t xml:space="preserve">Inspect for foreign objects [Y/N]; Clean air intake [Y/N]; Repair damage [Y/N]                        </t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">605-01-40            </t>
+          <t xml:space="preserve">TBD                   </t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive               </t>
+          <t xml:space="preserve">Preventive             </t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder Head Failure          </t>
+          <t>Cylinders Failure</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides combustion chamber sealing, supports valves and gas exchange  </t>
+          <t xml:space="preserve">Provide combustion chamber for controlled combustion             </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating             </t>
+          <t xml:space="preserve">LOO - Low output          </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion              </t>
+          <t xml:space="preserve">2.7 Overheating              </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosive damage accelerates material degradation              </t>
+          <t xml:space="preserve">Overheating causing deformation and compression loss </t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion inspections scheduled? [Y/N]&lt;br&gt;Protective coatings maintained? [Y/N]&lt;br&gt;Replacement of corroded parts? [Y/N]                                                    </t>
+          <t xml:space="preserve">Monitor cylinder temperature [Y/N]; Maintain cooling water system [Y/N]; Repair cooling faults [Y/N]    </t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">605-01-40            </t>
+          <t xml:space="preserve">TBD                   </t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive               </t>
+          <t xml:space="preserve">Predictive             </t>
         </is>
       </c>
     </row>
@@ -840,47 +840,47 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder Head Failure          </t>
+          <t>Cylinders Failure</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides combustion chamber sealing, supports valves and gas exchange  </t>
+          <t xml:space="preserve">Provide combustion chamber for controlled combustion             </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                   </t>
+          <t xml:space="preserve">LOO - Low output          </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage               </t>
+          <t xml:space="preserve">2.2 Corrosion                 </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Broken valves produce unusual noise                             </t>
+          <t xml:space="preserve">Corrosion causing gas leakage and loss of compression  </t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise monitoring performed? [Y/N]&lt;br&gt;Valve tightness checked? [Y/N]&lt;br&gt;Broken parts replaced? [Y/N]                                                                          </t>
+          <t xml:space="preserve">Inspect and mitigate corrosion [Y/N]; Repair cylinder lining [Y/N]; Use inhibitors [Y/N]               </t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">605-01-40            </t>
+          <t xml:space="preserve">TBD                   </t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding          </t>
+          <t xml:space="preserve">Preventive             </t>
         </is>
       </c>
     </row>
@@ -892,47 +892,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder Head Failure          </t>
+          <t>Pistons Failure *</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides combustion chamber sealing, supports valves and gas exchange  </t>
+          <t xml:space="preserve">Transmit combustion force to crankshaft via connecting rods       </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                   </t>
+          <t xml:space="preserve">VIB - Vibration          </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">2.4 Wear                      </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rough surfaces cause vibrating noise                            </t>
+          <t xml:space="preserve">Piston skirt wear causing vibration                    </t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear assessment conducted? [Y/N]&lt;br&gt;Operational noise analyzed? [Y/N]&lt;br&gt;Parts replaced upon wear? [Y/N]                                                                     </t>
+          <t xml:space="preserve">Regular piston skirt inspection [Y/N]; Measure clearances [Y/N]; Replace worn pistons [Y/N]           </t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve">605-01-40            </t>
+          <t xml:space="preserve">TBD                   </t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive               </t>
+          <t xml:space="preserve">Predictive             </t>
         </is>
       </c>
     </row>
@@ -944,47 +944,47 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder Head Failure          </t>
+          <t>Pistons Failure *</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides combustion chamber sealing, supports valves and gas exchange  </t>
+          <t xml:space="preserve">Transmit combustion force to crankshaft via connecting rods       </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running   </t>
+          <t xml:space="preserve">VIB - Vibration          </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">2.5 Breakage                  </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear weakens valve sealing                                      </t>
+          <t xml:space="preserve">Piston cracks causing abnormal vibration               </t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Condition monitoring active? [Y/N]&lt;br&gt;Valve clearance checked? [Y/N]&lt;br&gt;Scheduled preventive replacement performed? [Y/N]                                                    </t>
+          <t xml:space="preserve">Visual and ultrasonic testing [Y/N]; Replace cracked pistons [Y/N]; Monitor vibration trends [Y/N]     </t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">605-01-40            </t>
+          <t xml:space="preserve">TBD                   </t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive               </t>
+          <t xml:space="preserve">Failure-Finding        </t>
         </is>
       </c>
     </row>
@@ -996,47 +996,47 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder Head Failure          </t>
+          <t>Pistons Failure *</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides combustion chamber sealing, supports valves and gas exchange  </t>
+          <t xml:space="preserve">Transmit combustion force to crankshaft via connecting rods       </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running   </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage               </t>
+          <t xml:space="preserve">2.6 Fatigue                   </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cracks cause sudden failure                                    </t>
+          <t xml:space="preserve">Fatigue cracks weakening piston                         </t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Routine inspection and NDT scheduled? [Y/N]&lt;br&gt;Necessary repairs/replacements conducted? [Y/N]                                                                              </t>
+          <t xml:space="preserve">Fatigue testing [Y/N]; Schedule piston replacement [Y/N]; Use high quality material [Y/N]             </t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">605-01-40            </t>
+          <t xml:space="preserve">TBD                   </t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding          </t>
+          <t xml:space="preserve">Preventive             </t>
         </is>
       </c>
     </row>
@@ -1048,47 +1048,47 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder Liner Failure         </t>
+          <t>Pistons Failure *</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides cylinder wall and seal surface for piston                     </t>
+          <t xml:space="preserve">Transmit combustion force to crankshaft via connecting rods       </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation      </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion              </t>
+          <t xml:space="preserve">5.3 Contamination            </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion reduces sealing and liner durability                 </t>
+          <t xml:space="preserve">Foreign particles causing damage                        </t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inspect cylinder liner for corrosion? [Y/N]&lt;br&gt;Monitor water chemistry? [Y/N]&lt;br&gt;Replace liner if corrosion extensive? [Y/N]                                                </t>
+          <t xml:space="preserve">Maintain fuel/oil cleanliness [Y/N]; Inspect piston surface [Y/N]; Clean fuel system [Y/N]            </t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">606-01-40            </t>
+          <t xml:space="preserve">TBD                   </t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive               </t>
+          <t xml:space="preserve">Predictive             </t>
         </is>
       </c>
     </row>
@@ -1100,47 +1100,47 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder Liner Failure         </t>
+          <t>Pistons Failure *</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides cylinder wall and seal surface for piston                     </t>
+          <t xml:space="preserve">Transmit combustion force to crankshaft via connecting rods       </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation      </t>
+          <t xml:space="preserve">OHE - Overheating       </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">2.7 Overheating              </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear reduces sealing and compression                           </t>
+          <t xml:space="preserve">Thermal damage causing deformation or seizure          </t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear inspection scheduled? [Y/N]&lt;br&gt;Measure liner surface condition? [Y/N]&lt;br&gt;Replace liner on excessive wear? [Y/N]                                                         </t>
+          <t xml:space="preserve">Monitor piston temperature [Y/N]; Thermal imaging [Y/N]; Repair cooling system [Y/N]                 </t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">606-01-40            </t>
+          <t xml:space="preserve">TBD                   </t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding          </t>
+          <t xml:space="preserve">Predictive             </t>
         </is>
       </c>
     </row>
@@ -1152,47 +1152,47 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder Liner Failure         </t>
+          <t>Pistons Failure *</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides cylinder wall and seal surface for piston                     </t>
+          <t xml:space="preserve">Transmit combustion force to crankshaft via connecting rods       </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOO - Low output              </t>
+          <t xml:space="preserve">OHE - Overheating       </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage               </t>
+          <t xml:space="preserve">1.4 Deformation              </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cracks cause loss of function                                </t>
+          <t xml:space="preserve">Thermal deformation causing seizure                     </t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Conduct NDT crack detection? [Y/N]&lt;br&gt;Repair or replace cracked liner? [Y/N]&lt;br&gt;Monitor condition continuously? [Y/N]                                                        </t>
+          <t xml:space="preserve">Dimensional checks [Y/N]; Replace overheated pistons [Y/N]; Use heat-resistant materials [Y/N]        </t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">606-01-40            </t>
+          <t xml:space="preserve">TBD                   </t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding          </t>
+          <t xml:space="preserve">Failure-Finding        </t>
         </is>
       </c>
     </row>
@@ -1204,47 +1204,47 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder Liner Failure         </t>
+          <t>Pistons Failure *</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides cylinder wall and seal surface for piston                     </t>
+          <t xml:space="preserve">Transmit combustion force to crankshaft via connecting rods       </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOO - Low output              </t>
+          <t xml:space="preserve">LOO - Low output          </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation            </t>
+          <t xml:space="preserve">1.5 Looseness                </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deformation causes seal failure                               </t>
+          <t xml:space="preserve">Excess clearance reducing compression                  </t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimensional checks performed? [Y/N]&lt;br&gt;Repair or replace as needed? [Y/N]&lt;br&gt;Monitor related parameters? [Y/N]                                                               </t>
+          <t xml:space="preserve">Measure piston-to-cylinder clearance [Y/N]; Repair assembly [Y/N]; Replace worn parts [Y/N]           </t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">606-01-40            </t>
+          <t xml:space="preserve">TBD                   </t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding          </t>
+          <t xml:space="preserve">Preventive             </t>
         </is>
       </c>
     </row>
@@ -1256,47 +1256,47 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder Liner Failure         </t>
+          <t>Pistons Failure *</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides cylinder wall and seal surface for piston                     </t>
+          <t xml:space="preserve">Transmit combustion force to crankshaft via connecting rods       </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating             </t>
+          <t xml:space="preserve">LOO - Low output          </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">2.2 Corrosion                 </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat damage accelerates wear                                 </t>
+          <t xml:space="preserve">Corrosion causing sealing loss                          </t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Temperature sensors calibrated and monitored? [Y/N]&lt;br&gt;Wear assessment performed? [Y/N]&lt;br&gt;Cooling system maintained? [Y/N]                                                  </t>
+          <t xml:space="preserve">Regular oil analysis [Y/N]; Inspect piston surfaces [Y/N]; Use corrosion inhibitors [Y/N]              </t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">606-01-40            </t>
+          <t xml:space="preserve">TBD                   </t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive               </t>
+          <t xml:space="preserve">Predictive             </t>
         </is>
       </c>
     </row>
@@ -1308,47 +1308,47 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder Liner Failure         </t>
+          <t>DE Bearing Failure *</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides cylinder wall and seal surface for piston                     </t>
+          <t xml:space="preserve">Support crankshaft rotation and absorb radial/axial loads          </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating             </t>
+          <t xml:space="preserve">VIB - Vibration          </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation            </t>
+          <t xml:space="preserve">2.4 Wear                      </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thermal distortion impairs integrity                         </t>
+          <t xml:space="preserve">Bearing wear causing vibration and noise                </t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heat-induced deformation inspection? [Y/N]&lt;br&gt;Dimensional verification? [Y/N]&lt;br&gt;Repair or replace deformed parts? [Y/N]                                                    </t>
+          <t xml:space="preserve">Vibration analysis [Y/N]; Lubricant analysis [Y/N]; Bearing inspection [Y/N]                         </t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">606-01-40            </t>
+          <t xml:space="preserve">TBD                   </t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding          </t>
+          <t xml:space="preserve">Predictive             </t>
         </is>
       </c>
     </row>
@@ -1360,47 +1360,47 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder Liner Failure         </t>
+          <t>DE Bearing Failure *</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides cylinder wall and seal surface for piston                     </t>
+          <t xml:space="preserve">Support crankshaft rotation and absorb radial/axial loads          </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running   </t>
+          <t xml:space="preserve">VIB - Vibration          </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">1.3 Clearance / alignment    </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Progressive wear causes sealing loss                         </t>
+          <t xml:space="preserve">Misalignment causing abnormal vibration                </t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduled wear inspections? [Y/N]&lt;br&gt;Replacement on wear limits? [Y/N]&lt;br&gt;Lubrication condition monitored? [Y/N]                                                             </t>
+          <t xml:space="preserve">Alignment checks [Y/N]; Correct misalignments [Y/N]; Bearing replacement [Y/N]                        </t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">606-01-40            </t>
+          <t xml:space="preserve">TBD                   </t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive               </t>
+          <t xml:space="preserve">Preventive             </t>
         </is>
       </c>
     </row>
@@ -1412,47 +1412,47 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cylinder Liner Failure         </t>
+          <t>DE Bearing Failure *</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provides cylinder wall and seal surface for piston                     </t>
+          <t xml:space="preserve">Support crankshaft rotation and absorb radial/axial loads          </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running   </t>
+          <t xml:space="preserve">VIB - Vibration          </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                </t>
+          <t xml:space="preserve">2.6 Fatigue                   </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Repeated loading causes fatigue damage                      </t>
+          <t xml:space="preserve">Fatigue damage causing bearing failure                   </t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDT scheduled? [Y/N]&lt;br&gt;Replace upon crack detection? [Y/N]&lt;br&gt;Load monitoring maintained? [Y/N]                                                                             </t>
+          <t xml:space="preserve">Scheduled bearing fatigue inspections [Y/N]; Replace aged bearings [Y/N]; Use high-quality bearings [Y/N] </t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">606-01-40            </t>
+          <t xml:space="preserve">TBD                   </t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive               </t>
+          <t xml:space="preserve">Failure-Finding        </t>
         </is>
       </c>
     </row>
@@ -1464,41 +1464,49 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piston Failure                </t>
+          <t>DE Bearing Failure *</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts combustion pressure to mechanical force                       </t>
+          <t xml:space="preserve">Support crankshaft rotation and absorb radial/axial loads          </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
+          <t xml:space="preserve">LOO - Low output          </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                </t>
+          <t xml:space="preserve">2.4 Wear                      </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cracking causes abnormal vibration                          </t>
+          <t xml:space="preserve">Increased friction reduces output                        </t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibration monitoring continuous? [Y/N]&lt;br&gt;Visual inspection? [Y/N]&lt;br&gt;Replacement following fatigue detection? [Y/N]                                                           </t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t xml:space="preserve">Optimize lubrication [Y/N]; Replace worn bearings [Y/N]; Clean lubrication circuits [Y/N]             </t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive             </t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1508,41 +1516,49 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piston Failure                </t>
+          <t>DE Bearing Failure *</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts combustion pressure to mechanical force                       </t>
+          <t xml:space="preserve">Support crankshaft rotation and absorb radial/axial loads          </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation      </t>
+          <t xml:space="preserve">LOO - Low output          </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage               </t>
+          <t xml:space="preserve">5.2 Contamination            </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanical damage impairs performance                       </t>
+          <t xml:space="preserve">Oil contamination accelerates wear                       </t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visual inspection? [Y/N]&lt;br&gt;Dimensional measurements? [Y/N]&lt;br&gt;Part replacement when damaged? [Y/N]                                                                          </t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t xml:space="preserve">Oil cleanliness monitoring [Y/N]; Replace filters [Y/N]; Check seals [Y/N]                            </t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive             </t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1552,41 +1568,49 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piston Failure                </t>
+          <t>DE Bearing Failure *</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts combustion pressure to mechanical force                       </t>
+          <t xml:space="preserve">Support crankshaft rotation and absorb radial/axial loads          </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation      </t>
+          <t xml:space="preserve">OHE - Overheating       </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation            </t>
+          <t xml:space="preserve">2.7 Overheating              </t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deformation causes poor sealing                             </t>
+          <t xml:space="preserve">Overheating due to lubrication failure                   </t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visual deformation inspection? [Y/N]&lt;br&gt;Thermal stress assessment? [Y/N]&lt;br&gt;Repair or replace as needed? [Y/N]                                                              </t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t xml:space="preserve">Temperature monitoring [Y/N]; Oil supply checks [Y/N]; Cooling system maintenance [Y/N]               </t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive             </t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1596,41 +1620,49 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piston Failure                </t>
+          <t>DE Bearing Failure *</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts combustion pressure to mechanical force                       </t>
+          <t xml:space="preserve">Support crankshaft rotation and absorb radial/axial loads          </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating             </t>
+          <t xml:space="preserve">OHE - Overheating       </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">1.6 Sticking                 </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overheating degrades components                           </t>
+          <t xml:space="preserve">Lubrication loss causing seizure                         </t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Temperature monitored? [Y/N]&lt;br&gt;Lubrication system functioning? [Y/N]&lt;br&gt;Cooling system inspected? [Y/N]                                                                     </t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t xml:space="preserve">Oil level monitoring [Y/N]; Emergency lubrication checks [Y/N]; Lubrication system maintenance [Y/N] </t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding        </t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1640,41 +1672,49 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piston Failure                </t>
+          <t>NDE Bearing Failure *</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts combustion pressure to mechanical force                       </t>
+          <t xml:space="preserve">Support crankshaft rotation and absorb radial/axial loads          </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating             </t>
+          <t xml:space="preserve">VIB - Vibration          </t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking               </t>
+          <t xml:space="preserve">2.4 Wear                      </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seizure due to heat causes failure                         </t>
+          <t xml:space="preserve">Bearing wear causing vibration and noise                </t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lubrication flow verified? [Y/N]&lt;br&gt;Startup sequence controlled? [Y/N]&lt;br&gt;Cleaning maintained? [Y/N]                                                                          </t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t xml:space="preserve">Vibration monitoring [Y/N]; Bearing inspection [Y/N]; Lubricant quality check [Y/N]                   </t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive             </t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1684,41 +1724,49 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piston Failure                </t>
+          <t>NDE Bearing Failure *</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts combustion pressure to mechanical force                       </t>
+          <t xml:space="preserve">Support crankshaft rotation and absorb radial/axial loads          </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running   </t>
+          <t xml:space="preserve">VIB - Vibration          </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">1.3 Clearance / alignment    </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear causes sealing loss                                  </t>
+          <t xml:space="preserve">Misalignment causing abnormal vibrations               </t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear inspections? [Y/N]&lt;br&gt;Piston rings checked? [Y/N]&lt;br&gt;Preventive replacements? [Y/N]                                                                                     </t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t xml:space="preserve">Alignment correction [Y/N]; Bearing replacement [Y/N]; Lubrication review [Y/N]                      </t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive             </t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1728,41 +1776,49 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piston Failure                </t>
+          <t>NDE Bearing Failure *</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts combustion pressure to mechanical force                       </t>
+          <t xml:space="preserve">Support crankshaft rotation and absorb radial/axial loads          </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running   </t>
+          <t xml:space="preserve">VIB - Vibration          </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                </t>
+          <t xml:space="preserve">2.6 Fatigue                   </t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue cracking causes failure                            </t>
+          <t xml:space="preserve">Fatigue cracks leading to failure                       </t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduled NDT? [Y/N]&lt;br&gt;Replacement scheduled? [Y/N]&lt;br&gt;Wear debris trending active? [Y/N]                                                                                   </t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t xml:space="preserve">Fatigue checks [Y/N]; Material upgrades [Y/N]; Scheduled maintenance [Y/N]                           </t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding        </t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1772,41 +1828,49 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Piston Failure                </t>
+          <t>NDE Bearing Failure *</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts combustion pressure to mechanical force                       </t>
+          <t xml:space="preserve">Support crankshaft rotation and absorb radial/axial loads          </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise                  </t>
+          <t xml:space="preserve">LOO - Low output          </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 Miscellaneous external influence </t>
+          <t xml:space="preserve">2.4 Wear                      </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise due to piston slap or clearance                   </t>
+          <t xml:space="preserve">Increased friction reduces efficiency                   </t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Noise monitoring? [Y/N]&lt;br&gt;Clearance measurement? [Y/N]&lt;br&gt;Corrective action implemented? [Y/N]                                                                             </t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t xml:space="preserve">Lubrication monitoring [Y/N]; Bearing replacements [Y/N]; Oil condition checks [Y/N]                </t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive             </t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1816,41 +1880,49 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Connecting Rod Failure        </t>
+          <t>NDE Bearing Failure *</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmits force from piston to crankshaft                                  </t>
+          <t xml:space="preserve">Support crankshaft rotation and absorb radial/axial loads          </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
+          <t xml:space="preserve">LOO - Low output          </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation            </t>
+          <t xml:space="preserve">5.2 Contamination            </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bent or warped rod causes vibration                         </t>
+          <t xml:space="preserve">Contaminated oil accelerates wear                       </t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visual and dimensional inspections? [Y/N]&lt;br&gt;Vibration analysis? [Y/N]&lt;br&gt;Replacement of defective rods? [Y/N]                                                               </t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t xml:space="preserve">Oil cleanliness monitoring [Y/N]; Filter maintenance [Y/N]; Seal inspections [Y/N]                   </t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive             </t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1860,41 +1932,49 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Connecting Rod Failure        </t>
+          <t>NDE Bearing Failure *</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmits force from piston to crankshaft                                  </t>
+          <t xml:space="preserve">Support crankshaft rotation and absorb radial/axial loads          </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
+          <t xml:space="preserve">OHE - Overheating       </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                </t>
+          <t xml:space="preserve">2.7 Overheating              </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue cracks cause failure                                </t>
+          <t xml:space="preserve">Overheating due to lubrication failure                  </t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue crack detection by NDT? [Y/N]&lt;br&gt;Load history assessment? [Y/N]&lt;br&gt;Scheduled replacements? [Y/N]                                                                     </t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t xml:space="preserve">Temperature checks [Y/N]; Oil flow maintenance [Y/N]; Cooling system inspections [Y/N]               </t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive             </t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1904,41 +1984,49 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Connecting Rod Failure        </t>
+          <t>NDE Bearing Failure *</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmits force from piston to crankshaft                                  </t>
+          <t xml:space="preserve">Support crankshaft rotation and absorb radial/axial loads          </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
+          <t xml:space="preserve">OHE - Overheating       </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">1.6 Sticking                 </t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear at bearing interfaces causes vibration                 </t>
+          <t xml:space="preserve">Bearing seizure from lubrication loss                   </t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear inspection during maintenance? [Y/N]&lt;br&gt;Lubrication assessed? [Y/N]&lt;br&gt;Replacement as per wear limits? [Y/N]                                                           </t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t xml:space="preserve">Lubricant level monitoring [Y/N]; Emergency lubrication system checks [Y/N]; Alarm system test [Y/N] </t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding        </t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1948,41 +2036,49 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Connecting Rod Failure        </t>
+          <t>Lubricating Oil System Failure (*) *</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmits force from piston to crankshaft                                  </t>
+          <t xml:space="preserve">Supply clean lubricating oil for engine components                </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation      </t>
+          <t xml:space="preserve">LOO - Low output          </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">5.3 Contamination           </t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear causes performance degradation                         </t>
+          <t xml:space="preserve">Contamination reducing oil quality                      </t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear inspections planned? [Y/N]&lt;br&gt;Lubrication quality checks? [Y/N]&lt;br&gt;Replacement planned? [Y/N]                                                                         </t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t xml:space="preserve">Oil analysis [Y/N]; Filter replacement [Y/N]; Lubrication system flush [Y/N]                       </t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive             </t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1992,41 +2088,49 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Connecting Rod Failure        </t>
+          <t>Lubricating Oil System Failure (*) *</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmits force from piston to crankshaft                                  </t>
+          <t xml:space="preserve">Supply clean lubricating oil for engine components                </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation      </t>
+          <t xml:space="preserve">LOO - Low output          </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness              </t>
+          <t xml:space="preserve">1.1 Leakage                 </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bolt or fastener loosening reduces load transmission       </t>
+          <t xml:space="preserve">Oil leak causes pressure drop                            </t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torque checks and adjustments? [Y/N]&lt;br&gt;Fastener inspection? [Y/N]&lt;br&gt;Repair or replace loose fasteners? [Y/N]                                                             </t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t xml:space="preserve">Leak inspection [Y/N]; Seal replacement [Y/N]; Oil level monitoring [Y/N]                         </t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding        </t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2036,41 +2140,49 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Connecting Rod Failure        </t>
+          <t>Lubricating Oil System Failure (*) *</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmits force from piston to crankshaft                                  </t>
+          <t xml:space="preserve">Supply clean lubricating oil for engine components                </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FTS - Failure to start on demand</t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking             </t>
+          <t xml:space="preserve">5.2 Contamination           </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuck components impair function                            </t>
+          <t xml:space="preserve">Contaminated oil altering lubrication properties        </t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Function tests performed? [Y/N]&lt;br&gt;Lubrication verified? [Y/N]&lt;br&gt;Cleaning and repair scheduled? [Y/N]                                                                     </t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t xml:space="preserve">Oil sampling and testing [Y/N]; Reservoir cleaning [Y/N]; Water separation [Y/N]                  </t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive             </t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2080,41 +2192,49 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Connecting Rod Failure        </t>
+          <t>Lubricating Oil System Failure (*) *</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmits force from piston to crankshaft                                  </t>
+          <t xml:space="preserve">Supply clean lubricating oil for engine components                </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOO - Low output             </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">1.4 Deformation             </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear reduces load transfer capability                       </t>
+          <t xml:space="preserve">Damage causing pressure losses                           </t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear simulations? [Y/N]&lt;br&gt;Root cause analysis conducted? [Y/N]&lt;br&gt;Component replacement scheduled? [Y/N]                                                                  </t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t xml:space="preserve">Inspect pipelines and pumps [Y/N]; Pressure testing [Y/N]; Repair damaged sections [Y/N]          </t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive             </t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2124,41 +2244,49 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Connecting Rod Failure        </t>
+          <t>Lubricating Oil System Failure (*) *</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmits force from piston to crankshaft                                  </t>
+          <t xml:space="preserve">Supply clean lubricating oil for engine components                </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">LOO - Low output             </t>
+          <t xml:space="preserve">ELU - External leakage - utility medium </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness              </t>
+          <t xml:space="preserve">2.2 Corrosion           </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose connections reduce output                             </t>
+          <t xml:space="preserve">Corrosion causing oil leaks                              </t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Connection torque verification? [Y/N]&lt;br&gt;Maintenance tightening? [Y/N]&lt;br&gt;Inspection post-repair? [Y/N]                                                                  </t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t xml:space="preserve">Apply anti-corrosion measures [Y/N]; Inspect seals and pipes [Y/N]; Repair leaks [Y/N]             </t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive             </t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2168,41 +2296,49 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooling Water Pump Failure    </t>
+          <t>Lubricating Oil System Failure (*) *</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circulates engine cooling water                                            </t>
+          <t xml:space="preserve">Supply clean lubricating oil for engine components                </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation      </t>
+          <t xml:space="preserve">ELU - External leakage - utility medium </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.1 Leakage                </t>
+          <t xml:space="preserve">2.4 Wear                </t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leakage reduces coolant flow                                </t>
+          <t xml:space="preserve">Wear causing seal and pipe leaks                         </t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leak inspections? [Y/N]&lt;br&gt;Seal and gasket replacement? [Y/N]&lt;br&gt;Preventive maintenance scheduled? [Y/N]                                                                 </t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t xml:space="preserve">Seal condition monitoring [Y/N]; Lubricant replenishment [Y/N]; Replace worn seals [Y/N]          </t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive             </t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2212,41 +2348,49 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooling Water Pump Failure    </t>
+          <t>Lubricating Oil System Failure (*) *</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circulates engine cooling water                                            </t>
+          <t xml:space="preserve">Supply clean lubricating oil for engine components                </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation      </t>
+          <t xml:space="preserve">ELU - External leakage - utility medium </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">1.4 Deformation         </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear reduces pump flow and pressure                        </t>
+          <t xml:space="preserve">Mechanical damage leading to leaks                       </t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear inspection planned? [Y/N]&lt;br&gt;Flow rate recorded? [Y/N]&lt;br&gt;Timely overhaul? [Y/N]                                                                                      </t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t xml:space="preserve">Visual inspections [Y/N]; Non-destructive testing [Y/N]; Repair or replace damaged components [Y/N] </t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding        </t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2256,41 +2400,49 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooling Water Pump Failure    </t>
+          <t>Cooling Water System Failure (*) *</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circulates engine cooling water                                            </t>
+          <t xml:space="preserve">Remove heat from engine to maintain operating temperature         </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation            </t>
+          <t xml:space="preserve">2.4 Wear                   </t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Structural deformation causes vibration                     </t>
+          <t xml:space="preserve">Wear and fouling reduce cooling efficiency              </t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimensional checks? [Y/N]&lt;br&gt;Vibration facts analyzed? [Y/N]&lt;br&gt;Corrective repair? [Y/N]                                                                                   </t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t xml:space="preserve">Clean cooling system regularly [Y/N]; Replace worn parts [Y/N]; Flush cooling channels [Y/N]        </t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive             </t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2300,41 +2452,49 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooling Water Pump Failure    </t>
+          <t>Cooling Water System Failure (*) *</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circulates engine cooling water                                            </t>
+          <t xml:space="preserve">Remove heat from engine to maintain operating temperature         </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                </t>
+          <t xml:space="preserve">2.2 Corrosion              </t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue failure reduces reliability                        </t>
+          <t xml:space="preserve">Corrosion causing leaks or flow restrictions             </t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue monitoring? [Y/N]&lt;br&gt;Replacement scheduled? [Y/N]&lt;br&gt;Performance data checked? [Y/N]                                                                              </t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t xml:space="preserve">Monitor cooling water chemistry [Y/N]; Apply corrosion inhibitors [Y/N]; Repair leaks [Y/N]        </t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive             </t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2344,41 +2504,49 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cooling Water Pump Failure    </t>
+          <t>Cooling Water System Failure (*) *</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circulates engine cooling water                                            </t>
+          <t xml:space="preserve">Remove heat from engine to maintain operating temperature         </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running   </t>
+          <t xml:space="preserve">ELU - External leakage - utility medium </t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                </t>
+          <t xml:space="preserve">2.2 Corrosion          </t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partial or total failure during running                    </t>
+          <t xml:space="preserve">Corrosion causing external leaks                         </t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">NDT inspections scheduled? [Y/N]&lt;br&gt;Replacement plans made? [Y/N]&lt;br&gt;Performance monitoring ongoing? [Y/N]                                                                </t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t xml:space="preserve">Leak inspection [Y/N]; Seal and pipe replacement [Y/N]; Repair leaks promptly [Y/N]                 </t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding        </t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2388,41 +2556,49 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure            </t>
+          <t>Cooling Water System Failure (*) *</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supports crankshaft rotation at drive end                                 </t>
+          <t xml:space="preserve">Remove heat from engine to maintain operating temperature         </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration              </t>
+          <t xml:space="preserve">ELU - External leakage - utility medium </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">2.6 Fatigue            </t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing wear causes vibration                              </t>
+          <t xml:space="preserve">Fatigue cracks causing leaks                             </t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibration monitoring reports? [Y/N]&lt;br&gt;Lubrication inspection? [Y/N]&lt;br&gt;Timely bearing replacement? [Y/N]                                                                 </t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t xml:space="preserve">Non-destructive testing [Y/N]; Schedule repairs [Y/N]; Monitor system pressures [Y/N]             </t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding        </t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2432,41 +2608,49 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure            </t>
+          <t>Cooling Water System Failure (*) *</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supports crankshaft rotation at drive end                                 </t>
+          <t xml:space="preserve">Remove heat from engine to maintain operating temperature         </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation      </t>
+          <t xml:space="preserve">LOO - Low output          </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion              </t>
+          <t xml:space="preserve">5.1 Blockage/plugged       </t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion damages bearing surface                         </t>
+          <t xml:space="preserve">Blockage reducing coolant flow                            </t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosion inspections? [Y/N]&lt;br&gt;Oil analysis conducted? [Y/N]&lt;br&gt;Replacement based on condition? [Y/N]                                                                    </t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t xml:space="preserve">Replace filters [Y/N]; Clean passages [Y/N]; Monitor pressure drops [Y/N]                         </t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive             </t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2476,41 +2660,49 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure            </t>
+          <t>Fuel Injection Pump Failure (*) *</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supports crankshaft rotation at drive end                                 </t>
+          <t xml:space="preserve">Supplies fuel under pressure to cylinders                         </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running   </t>
+          <t xml:space="preserve">VIB - Vibration          </t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue                </t>
+          <t xml:space="preserve">2.4 Wear                   </t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue cracking causes early failure                   </t>
+          <t xml:space="preserve">Wear leading to vibration and uneven fuel flow           </t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scheduled NDT inspections? [Y/N]&lt;br&gt;Bearing replaced on detection? [Y/N]&lt;br&gt;Condition monitoring active? [Y/N]                                                           </t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t xml:space="preserve">Inspect pump internals [Y/N]; Vibration monitoring [Y/N]; Replace worn parts [Y/N]                </t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive             </t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2520,41 +2712,1557 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Converts chemical energy from fuel into mechanical rotational power                             </t>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">DE Bearing Failure            </t>
+          <t>Fuel Injection Pump Failure (*) *</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supports crankshaft rotation at drive end                                 </t>
+          <t xml:space="preserve">Supplies fuel under pressure to cylinders                         </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating           </t>
+          <t xml:space="preserve">VIB - Vibration          </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear                   </t>
+          <t xml:space="preserve">1.3 Clearance / alignment  </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overheating causes bearing damage                       </t>
+          <t xml:space="preserve">Misalignment causing abnormal vibration                  </t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Temperature sensor monitoring? [Y/N]&lt;br&gt;Lubrication flow checked? [Y/N]&lt;br&gt;Cooling system maintained? [Y/N]                                                               </t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t xml:space="preserve">Align pump components [Y/N]; Lubrication checks [Y/N]; Pump overhaul [Y/N]                      </t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive             </t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Fuel Injection Pump Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supplies fuel under pressure to cylinders                         </t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.5 Breakage              </t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fractures causing irregular fuel supply                  </t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Repair or replace fractured parts [Y/N]; Non-destructive testing [Y/N]; Inspections [Y/N]        </t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding        </t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Fuel Injection Pump Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supplies fuel under pressure to cylinders                         </t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.2 Contamination          </t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contamination impairing pump function                     </t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maintain fuel quality [Y/N]; Filter maintenance [Y/N]; Fuel system cleaning [Y/N]                </t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive             </t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Fuel Injection Pump Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supplies fuel under pressure to cylinders                         </t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOO - Low output          </t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5 Looseness             </t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loose components reducing fuel pressure                  </t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tighten pump assembly [Y/N]; Monitor fuel pressure [Y/N]; Replace worn parts [Y/N]              </t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive             </t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Turbocharger Failure (*)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Increase intake air pressure for better combustion               </t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIB - Vibration          </t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.6 Fatigue                </t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fatigue cracks causing vibration                          </t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vibration monitoring [Y/N]; Blade inspection [Y/N]; Scheduled overhauls [Y/N]                  </t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive             </t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Turbocharger Failure (*)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Increase intake air pressure for better combustion               </t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIB - Vibration          </t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.3 Clearance / alignment  </t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Misalignment causing abnormal vibration                  </t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Align turbocharger [Y/N]; Inspect bearings and shaft [Y/N]; Service lubrication [Y/N]          </t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive             </t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Turbocharger Failure (*)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Increase intake air pressure for better combustion               </t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOI - Noise              </t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.1 Cavitation             </t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cavitation causing noise and damage                       </t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inspect compressor blades [Y/N]; Water washing [Y/N]; Flow performance tests [Y/N]            </t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding        </t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Turbocharger Failure (*)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Increase intake air pressure for better combustion               </t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOI - Noise              </t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.3 External influences    </t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Noise from foreign object impact                           </t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intake filters cleaning [Y/N]; Foreign object prevention [Y/N]; Visual inspections [Y/N]      </t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding        </t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Turbocharger Failure (*)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Increase intake air pressure for better combustion               </t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OHE - Overheating       </t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.7 Overheating           </t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Excess heat damaging turbocharger components              </t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temperature monitoring [Y/N]; Cooling system checks [Y/N]; Alarm system maintenance [Y/N]     </t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive             </t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Turbocharger Failure (*)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Increase intake air pressure for better combustion               </t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OHE - Overheating       </t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.6 Sticking              </t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lubrication starvation causing seizure                     </t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lubricant supply inspection [Y/N]; Oil level monitoring [Y/N]; Emergency lubrication tests [Y/N] </t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding        </t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Exhaust System Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Direct combustion gases from engine to atmosphere safely         </t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion          </t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrosion causing exhaust leaks                            </t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inspect exhaust pipes and joints [Y/N]; Apply corrosion inhibitors [Y/N]; Repair or replace as needed [Y/N] </t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive             </t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Exhaust System Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Direct combustion gases from engine to atmosphere safely         </t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.3 Erosion            </t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erosion by hot gases causing damage                        </t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visual inspection [Y/N]; Surface repair [Y/N]; Cleaning [Y/N]                                    </t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding        </t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Exhaust System Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Direct combustion gases from engine to atmosphere safely         </t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4 Deformation        </t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thermal deformation causing leaks                          </t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thermal imaging [Y/N]; Structural evaluation [Y/N]; Repair and reinforcement [Y/N]              </t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive             </t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Exhaust System Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Direct combustion gases from engine to atmosphere safely         </t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOI - Noise              </t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.3 External influences  </t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Noise due to looseness or damage                           </t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check exhaust supports and mounts [Y/N]; Tighten or replace [Y/N]; Noise level monitoring [Y/N] </t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding        </t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Governor Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regulate engine speed and load                                    </t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSF - Control / signal failure </t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.1 Control failure       </t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inability to regulate engine speed                         </t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Calibration checks [Y/N]; Replace faulty components [Y/N]; Software updates [Y/N]               </t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding        </t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Governor Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regulate engine speed and load                                    </t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSF - Control / signal failure </t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.5 Software error       </t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Software faults impacting control                          </t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Software diagnostics [Y/N]; Firmware updates [Y/N]; Reset control unit [Y/N]                   </t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding        </t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Governor Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regulate engine speed and load                                    </t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FTS - Failure to start on demand </t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.4 Faulty power/voltage </t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrical supply failure preventing startup                </t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrical system check [Y/N]; Repair circuits [Y/N]; Power stabilization [Y/N]                </t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding        </t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Governor Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regulate engine speed and load                                    </t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FTR - Failure to regulate     </t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3.1 Control failure       </t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Control valve or actuator failure                           </t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valve inspection [Y/N]; Actuator maintenance [Y/N]; Controller tuning [Y/N]                    </t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive             </t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Fuel Filters Failure (*)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter out particulate contaminants from fuel                     </t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLU - Plugged / choked        </t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.1 Blockage/plugged     </t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter clogged reducing fuel flow                          </t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monitor pressure differential [Y/N]; Replace filter elements [Y/N]; Clean filter housing [Y/N] </t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive             </t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Fuel Filters Failure (*)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter out particulate contaminants from fuel                     </t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLU - Plugged / choked        </t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.2 Contamination       </t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contaminants blocking filter                              </t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fuel quality testing [Y/N]; Clean fuel system [Y/N]; Regular filter replacement [Y/N]          </t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive             </t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Fuel Filters Failure (*)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter out particulate contaminants from fuel                     </t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOO - Low output              </t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.1 Blockage/plugged     </t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reduced fuel pressure due to clogged filter               </t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fuel pressure monitoring [Y/N]; Filter replacements [Y/N]; Line flushing [Y/N]                </t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive             </t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Fuel Filters Failure (*)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filter out particulate contaminants from fuel                     </t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOO - Low output              </t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6.1 No cause found      </t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unknown cause for low fuel flow                           </t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fuel system diagnostic [Y/N]; Filter integrity test [Y/N]; Fuel sample analysis [Y/N]        </t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding        </t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Starting System Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide mechanical/electrical starter functions                   </t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FTS - Failure to start on demand </t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.2 Open circuit       </t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Electrical faults cause no start                           </t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Continuity tests [Y/N]; Wiring replacement [Y/N]; Starter and battery checks [Y/N]            </t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding        </t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Starting System Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide mechanical/electrical starter functions                   </t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FTS - Failure to start on demand </t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mechanical starter failure causing no start            </t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mechanical inspection [Y/N]; Air pressure checks [Y/N]; Replace worn parts [Y/N]            </t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding        </t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Starting System Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide mechanical/electrical starter functions                   </t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FTS - Failure to start on demand </t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.6 Sticking          </t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Starter pinion or valve sticking                           </t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lubrication checks [Y/N]; Cleaning and maintenance [Y/N]; Replace faulty parts [Y/N]        </t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding        </t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Starting System Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide mechanical/electrical starter functions                   </t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FTS - Failure to start on demand </t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4.5 Earth/isolation fault </t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Insulation fault causing starter failure                 </t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Insulation resistance testing [Y/N]; Repair ground faults [Y/N]; Verify protective devices [Y/N] </t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding        </t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Oil Pump Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Circulate lubricating oil through engine                          </t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOO - Low output              </t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.1 Leakage            </t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oil leaks causing pressure drop                            </t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inspect seals [Y/N]; Repair leaks [Y/N]; Monitor oil levels [Y/N]                            </t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding        </t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Oil Pump Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Circulate lubricating oil through engine                          </t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDE - Parameter deviation    </t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4 Deformation        </t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pump deformation causes flow problems                      </t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visual inspections [Y/N]; Pressure tests [Y/N]; Pump overhaul [Y/N]                        </t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive             </t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Oil Pump Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Circulate lubricating oil through engine                          </t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIB - Vibration              </t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.6 Fatigue            </t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fatigue cracks causing pump failure                        </t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vibration monitoring [Y/N]; Scheduled maintenance [Y/N]; Use superior materials [Y/N]       </t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive             </t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engine, Diesel </t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Converts fuel energy to mechanical power          </t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Oil Pump Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Circulate lubricating oil through engine                          </t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LOO - Low output             </t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.2 Contamination      </t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oil contamination causing pump inefficiency               </t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oil analysis [Y/N]; Filter maintenance [Y/N]; Pump cleaning [Y/N]                           </t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD                   </t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive             </t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
